--- a/Base de Dados.xlsx
+++ b/Base de Dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Estudos\Desdobramento - Sigma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC44A962-8CC4-4F20-815E-3A69F0DC296D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C095EF3-1BFA-4608-9A0A-E8FE96D14733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{052EBD17-0308-4E6D-95A6-CA02714B48B2}"/>
   </bookViews>
@@ -17,15 +17,28 @@
     <sheet name="Equipamentos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base de Dados'!$A$1:$H$278</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base de Dados'!$A$1:$J$219</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Equipamentos!$A$2:$A$77</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="829">
   <si>
     <t>Bias MÃ¡ximo</t>
   </si>
@@ -1722,21 +1735,9 @@
     <t>20 - 200</t>
   </si>
   <si>
-    <t>17 - 0</t>
-  </si>
-  <si>
     <t>1,01 - 60</t>
   </si>
   <si>
-    <t>0,89 - 0</t>
-  </si>
-  <si>
-    <t>10 - 0</t>
-  </si>
-  <si>
-    <t>0,9 - 0</t>
-  </si>
-  <si>
     <t>3 - 28</t>
   </si>
   <si>
@@ -1749,9 +1750,6 @@
     <t>46 - 174</t>
   </si>
   <si>
-    <t>115 - 0</t>
-  </si>
-  <si>
     <t>3,5 - 77</t>
   </si>
   <si>
@@ -1845,9 +1843,6 @@
     <t>39 - 308</t>
   </si>
   <si>
-    <t>0,7 - 1,2</t>
-  </si>
-  <si>
     <t>0,67 - 1,17</t>
   </si>
   <si>
@@ -2286,9 +2281,6 @@
     <t>PTUI</t>
   </si>
   <si>
-    <t>1,0 - 15,0</t>
-  </si>
-  <si>
     <t>sodio urinario</t>
   </si>
   <si>
@@ -2304,9 +2296,6 @@
     <t>URUI</t>
   </si>
   <si>
-    <t>12,0 - 20,0</t>
-  </si>
-  <si>
     <t>BIOQ_1 ISE_1_1</t>
   </si>
   <si>
@@ -2518,6 +2507,24 @@
   </si>
   <si>
     <t>Equipamentos</t>
+  </si>
+  <si>
+    <t>39 - 259</t>
+  </si>
+  <si>
+    <t>1 - 15</t>
+  </si>
+  <si>
+    <t>12 - 20</t>
+  </si>
+  <si>
+    <t>0 - 17</t>
+  </si>
+  <si>
+    <t>0 - 0,89</t>
+  </si>
+  <si>
+    <t>0 - 115</t>
   </si>
 </sst>
 </file>
@@ -3001,14 +3008,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3072,6 +3076,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}" name="Equipamentos" displayName="Equipamentos" ref="A1:A78" totalsRowShown="0">
   <autoFilter ref="A1:A78" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A78">
+    <sortCondition ref="A1:A78"/>
+  </sortState>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{1B9AEB56-1EBB-4F60-AF89-FB7F0CA8B355}" name="Equipamentos"/>
   </tableColumns>
@@ -3400,6 +3407,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.140625" style="1"/>
     <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="2"/>
@@ -3408,12 +3416,12 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>690</v>
-      </c>
-      <c r="B1" t="s">
-        <v>689</v>
-      </c>
-      <c r="C1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
@@ -3461,7 +3469,7 @@
         <v>26.8</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -3490,36 +3498,36 @@
         <v>75</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>550</v>
+        <v>640</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="B4" s="1">
-        <v>0.19400000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="C4" s="1">
-        <v>5.6000000000000001E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="H4" s="2">
         <v>7</v>
       </c>
-      <c r="E4" t="s">
-        <v>738</v>
-      </c>
-      <c r="F4" t="s">
-        <v>731</v>
-      </c>
-      <c r="G4" s="2">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2">
-        <v>99</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>728</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -3606,12 +3614,12 @@
         <v>0.3</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="B8" s="1">
         <v>6.0999999999999999E-2</v>
@@ -3664,7 +3672,7 @@
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>554</v>
+        <v>608</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -3698,7 +3706,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="B11" s="1">
         <v>0.18</v>
@@ -3727,7 +3735,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="B12" s="1">
         <v>0.2</v>
@@ -3776,7 +3784,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="B14" s="1">
         <v>0.2</v>
@@ -3878,12 +3886,12 @@
         <v>193</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>561</v>
+        <v>610</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="B18" s="1">
         <v>0.19400000000000001</v>
@@ -3895,19 +3903,19 @@
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="F18" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="G18" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2">
-        <v>650</v>
+        <v>99</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -3970,36 +3978,36 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="B21" s="1">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C21" s="1">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>255</v>
+        <v>40</v>
       </c>
       <c r="F21" t="s">
-        <v>256</v>
+        <v>41</v>
       </c>
       <c r="G21" s="2">
-        <v>2.5</v>
+        <v>28</v>
       </c>
       <c r="H21" s="2">
-        <v>4.5</v>
+        <v>100</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="B22" s="1">
         <v>0.3</v>
@@ -4017,13 +4025,13 @@
         <v>53</v>
       </c>
       <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
         <v>17</v>
       </c>
-      <c r="H22" s="2">
-        <v>0</v>
-      </c>
       <c r="I22" s="3" t="s">
-        <v>565</v>
+        <v>826</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -4081,7 +4089,7 @@
         <v>60</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -4104,13 +4112,13 @@
         <v>62</v>
       </c>
       <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
         <v>0.89</v>
       </c>
-      <c r="H25" s="2">
-        <v>0</v>
-      </c>
       <c r="I25" s="3" t="s">
-        <v>567</v>
+        <v>827</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -4139,7 +4147,7 @@
         <v>60</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -4168,7 +4176,7 @@
         <v>60</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -4191,13 +4199,13 @@
         <v>71</v>
       </c>
       <c r="G28" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H28" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -4220,13 +4228,13 @@
         <v>74</v>
       </c>
       <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
         <v>0.9</v>
       </c>
-      <c r="H29" s="2">
-        <v>0</v>
-      </c>
       <c r="I29" s="3" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -4255,7 +4263,7 @@
         <v>28</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -4284,12 +4292,12 @@
         <v>24.9</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="B32" s="1">
         <v>0.3</v>
@@ -4307,18 +4315,18 @@
         <v>93</v>
       </c>
       <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
         <v>115</v>
       </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
       <c r="I32" s="3" t="s">
-        <v>574</v>
+        <v>828</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="B33" s="1">
         <v>0.22</v>
@@ -4336,13 +4344,13 @@
         <v>95</v>
       </c>
       <c r="G33" s="2">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2">
         <v>115</v>
       </c>
-      <c r="H33" s="2">
-        <v>0</v>
-      </c>
       <c r="I33" s="3" t="s">
-        <v>574</v>
+        <v>828</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -4371,7 +4379,7 @@
         <v>304</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -4400,7 +4408,7 @@
         <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -4555,7 +4563,7 @@
         <v>77</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -4584,7 +4592,7 @@
         <v>0.78</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -4653,36 +4661,36 @@
         <v>5</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>708</v>
+        <v>693</v>
       </c>
       <c r="B47" s="1">
-        <v>0.13</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="C47" s="1">
-        <v>6.5000000000000002E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="D47" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>276</v>
+        <v>731</v>
       </c>
       <c r="F47" t="s">
-        <v>277</v>
+        <v>724</v>
       </c>
       <c r="G47" s="2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H47" s="2">
-        <v>99</v>
+        <v>650</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>577</v>
+        <v>723</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -4711,7 +4719,7 @@
         <v>15</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>578</v>
+        <v>625</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -4740,7 +4748,7 @@
         <v>10</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -4769,12 +4777,12 @@
         <v>0.9</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="B51" s="1">
         <v>0.155</v>
@@ -4798,7 +4806,7 @@
         <v>39</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -4827,7 +4835,7 @@
         <v>35</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -4856,7 +4864,7 @@
         <v>28.5</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -4885,7 +4893,7 @@
         <v>34</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -4914,7 +4922,7 @@
         <v>25</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -4943,7 +4951,7 @@
         <v>6.9</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -4972,36 +4980,36 @@
         <v>225</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>587</v>
+        <v>636</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="B58" s="1">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="C58" s="1">
-        <v>0.125</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>736</v>
+        <v>147</v>
       </c>
       <c r="F58" t="s">
-        <v>732</v>
+        <v>148</v>
       </c>
       <c r="G58" s="2">
-        <v>100</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H58" s="2">
-        <v>300</v>
+        <v>9.6</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>733</v>
+        <v>582</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -5030,7 +5038,7 @@
         <v>1.4</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -5059,7 +5067,7 @@
         <v>14.3</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -5088,7 +5096,7 @@
         <v>50</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -5117,7 +5125,7 @@
         <v>130</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>608</v>
+        <v>637</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -5215,7 +5223,7 @@
         <v>9</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -5244,7 +5252,7 @@
         <v>0.9</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -5296,7 +5304,7 @@
         <v>3.8</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -5325,7 +5333,7 @@
         <v>60</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -5377,12 +5385,12 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="B73" s="1">
         <v>0.25</v>
@@ -5391,27 +5399,27 @@
         <v>0.125</v>
       </c>
       <c r="D73" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E73" t="s">
-        <v>386</v>
+        <v>730</v>
       </c>
       <c r="F73" t="s">
-        <v>387</v>
+        <v>726</v>
       </c>
       <c r="G73" s="2">
-        <v>1.7</v>
+        <v>100</v>
       </c>
       <c r="H73" s="2">
-        <v>2.2999999999999998</v>
+        <v>300</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>595</v>
+        <v>727</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B74" s="1">
         <v>0.13</v>
@@ -5435,12 +5443,12 @@
         <v>107</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="B75" s="1">
         <v>0.1</v>
@@ -5452,10 +5460,10 @@
         <v>7</v>
       </c>
       <c r="E75" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="F75" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="G75" s="2">
         <v>110</v>
@@ -5464,7 +5472,7 @@
         <v>250</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -5493,7 +5501,7 @@
         <v>500</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -5522,7 +5530,7 @@
         <v>0.7</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -5551,7 +5559,7 @@
         <v>41</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>599</v>
+        <v>671</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -5580,7 +5588,7 @@
         <v>360</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>600</v>
+        <v>674</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -5609,7 +5617,7 @@
         <v>150</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>600</v>
+        <v>675</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -5638,7 +5646,7 @@
         <v>170</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -5667,7 +5675,7 @@
         <v>36</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -5696,7 +5704,7 @@
         <v>22.45</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -5725,36 +5733,36 @@
         <v>20.29</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>722</v>
+        <v>696</v>
       </c>
       <c r="B85" s="1">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="C85" s="1">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="D85" t="s">
         <v>10</v>
       </c>
       <c r="E85" t="s">
-        <v>526</v>
+        <v>217</v>
       </c>
       <c r="F85" t="s">
-        <v>527</v>
+        <v>218</v>
       </c>
       <c r="G85" s="2">
-        <v>16.600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="H85" s="2">
-        <v>48.5</v>
+        <v>1.17</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -5783,12 +5791,12 @@
         <v>120</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>607</v>
+        <v>682</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B87" s="1">
         <v>0.3</v>
@@ -5800,19 +5808,19 @@
         <v>7</v>
       </c>
       <c r="E87" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="F87" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="G87" s="2">
-        <v>0.7</v>
+        <v>39</v>
       </c>
       <c r="H87" s="2">
-        <v>1.2</v>
+        <v>259</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>606</v>
+        <v>823</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -5864,7 +5872,7 @@
         <v>200</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -5893,7 +5901,7 @@
         <v>0.1</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -5922,7 +5930,7 @@
         <v>0.6</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -5951,7 +5959,7 @@
         <v>138</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -5980,7 +5988,7 @@
         <v>12</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -6005,31 +6013,31 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="B95" s="1">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C95" s="1">
-        <v>7.4999999999999997E-2</v>
+        <v>0.1</v>
       </c>
       <c r="D95" t="s">
         <v>10</v>
       </c>
       <c r="E95" t="s">
-        <v>8</v>
+        <v>255</v>
       </c>
       <c r="F95" t="s">
-        <v>9</v>
+        <v>256</v>
       </c>
       <c r="G95" s="2">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="H95" s="2">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -6058,7 +6066,7 @@
         <v>500</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6087,12 +6095,12 @@
         <v>1.2</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>616</v>
+        <v>573</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="B98" s="1">
         <v>0.3</v>
@@ -6116,7 +6124,7 @@
         <v>345</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -6145,12 +6153,12 @@
         <v>199</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>619</v>
+        <v>595</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B100" s="1">
         <v>0.3</v>
@@ -6162,10 +6170,10 @@
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="F100" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="G100" s="2">
         <v>40</v>
@@ -6174,7 +6182,7 @@
         <v>150</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -6182,28 +6190,28 @@
         <v>702</v>
       </c>
       <c r="B101" s="1">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="C101" s="1">
-        <v>0.1</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="D101" t="s">
         <v>10</v>
       </c>
       <c r="E101" t="s">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="F101" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="G101" s="2">
-        <v>0.67</v>
+        <v>70</v>
       </c>
       <c r="H101" s="2">
-        <v>1.17</v>
+        <v>99</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -6232,7 +6240,7 @@
         <v>134.80000000000001</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -6281,7 +6289,7 @@
         <v>115</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -6310,7 +6318,7 @@
         <v>129</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
@@ -6339,7 +6347,7 @@
         <v>3</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -6384,7 +6392,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="B109" s="1">
         <v>0.12</v>
@@ -6393,7 +6401,7 @@
         <v>0.06</v>
       </c>
       <c r="D109" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="E109" t="s">
         <v>276</v>
@@ -6408,7 +6416,7 @@
         <v>99</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -6437,12 +6445,12 @@
         <v>60</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="B111" s="1">
         <v>0.15</v>
@@ -6466,7 +6474,7 @@
         <v>500</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -6495,7 +6503,7 @@
         <v>0.89</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -6524,7 +6532,7 @@
         <v>200</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -6667,7 +6675,7 @@
         <v>5.6</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -6725,7 +6733,7 @@
         <v>0.9</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -6754,7 +6762,7 @@
         <v>60</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -6823,7 +6831,7 @@
         <v>0.9</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -6852,7 +6860,7 @@
         <v>0.9</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -6910,7 +6918,7 @@
         <v>5</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -6962,7 +6970,7 @@
         <v>350</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -7051,7 +7059,7 @@
         <v>6.8</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
@@ -7080,7 +7088,7 @@
         <v>1600</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
@@ -7106,7 +7114,7 @@
         <v>1011</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
@@ -7132,7 +7140,7 @@
         <v>786</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
@@ -7158,7 +7166,7 @@
         <v>85</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
@@ -7184,7 +7192,7 @@
         <v>201</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
@@ -7213,7 +7221,7 @@
         <v>300</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
@@ -7242,7 +7250,7 @@
         <v>24.9</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
@@ -7311,7 +7319,7 @@
         <v>22.4</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
@@ -7380,33 +7388,33 @@
         <v>27</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="B149" s="1">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="C149" s="1">
-        <v>0.06</v>
+        <v>0.125</v>
       </c>
       <c r="D149" t="s">
         <v>10</v>
       </c>
       <c r="E149" t="s">
-        <v>434</v>
+        <v>386</v>
       </c>
       <c r="F149" t="s">
-        <v>435</v>
+        <v>387</v>
       </c>
       <c r="G149" s="2">
-        <v>6.4</v>
+        <v>1.7</v>
       </c>
       <c r="H149" s="2">
-        <v>8.3000000000000007</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>642</v>
@@ -7438,7 +7446,7 @@
         <v>40</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>643</v>
+        <v>670</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
@@ -7467,7 +7475,7 @@
         <v>8.6</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
@@ -7496,36 +7504,36 @@
         <v>152</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>645</v>
+        <v>594</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="B153" s="1">
         <v>0.3</v>
       </c>
       <c r="C153" s="1">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="D153" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E153" t="s">
-        <v>40</v>
+        <v>740</v>
       </c>
       <c r="F153" t="s">
-        <v>41</v>
+        <v>739</v>
       </c>
       <c r="G153" s="2">
-        <v>28</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H153" s="2">
-        <v>100</v>
+        <v>13.8</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>646</v>
+        <v>741</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
@@ -7554,7 +7562,7 @@
         <v>1.2</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -7562,57 +7570,57 @@
         <v>710</v>
       </c>
       <c r="B155" s="1">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C155" s="1">
-        <v>7.4999999999999997E-2</v>
+        <v>0.05</v>
       </c>
       <c r="D155" t="s">
         <v>10</v>
       </c>
       <c r="E155" t="s">
-        <v>147</v>
+        <v>417</v>
       </c>
       <c r="F155" t="s">
-        <v>148</v>
+        <v>418</v>
       </c>
       <c r="G155" s="2">
-        <v>8.1999999999999993</v>
+        <v>3.5</v>
       </c>
       <c r="H155" s="2">
-        <v>9.6</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B156" s="1">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C156" s="1">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
       </c>
       <c r="E156" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="F156" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G156" s="2">
-        <v>4.0999999999999996</v>
+        <v>17</v>
       </c>
       <c r="H156" s="2">
-        <v>13.8</v>
+        <v>164</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
@@ -7641,7 +7649,7 @@
         <v>2.5</v>
       </c>
       <c r="I157" s="3" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
@@ -7690,7 +7698,7 @@
         <v>10</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -7719,7 +7727,7 @@
         <v>10</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
@@ -7748,7 +7756,7 @@
         <v>46</v>
       </c>
       <c r="I161" s="3" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
@@ -7777,7 +7785,7 @@
         <v>65</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
@@ -7806,7 +7814,7 @@
         <v>1.99</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
@@ -7835,7 +7843,7 @@
         <v>0.9</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
@@ -7864,7 +7872,7 @@
         <v>25</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>653</v>
+        <v>590</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
@@ -7893,65 +7901,59 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>716</v>
+        <v>430</v>
       </c>
       <c r="B167" s="1">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="C167" s="1">
-        <v>0.05</v>
+        <v>0.125</v>
       </c>
       <c r="D167" t="s">
-        <v>10</v>
+        <v>431</v>
       </c>
       <c r="E167" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="F167" t="s">
-        <v>418</v>
-      </c>
-      <c r="G167" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="H167" s="2">
-        <v>5.0999999999999996</v>
+        <v>433</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>655</v>
+        <v>557</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B168" s="1">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="C168" s="1">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="D168" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E168" t="s">
-        <v>748</v>
+        <v>434</v>
       </c>
       <c r="F168" t="s">
-        <v>749</v>
+        <v>435</v>
       </c>
       <c r="G168" s="2">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="H168" s="2">
-        <v>164</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>750</v>
+        <v>653</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
@@ -8000,7 +8002,7 @@
         <v>40</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
@@ -8029,7 +8031,7 @@
         <v>15</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
@@ -8058,30 +8060,36 @@
         <v>17.7</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>430</v>
+        <v>711</v>
       </c>
       <c r="B173" s="1">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="C173" s="1">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="D173" t="s">
-        <v>431</v>
+        <v>7</v>
       </c>
       <c r="E173" t="s">
-        <v>432</v>
+        <v>745</v>
       </c>
       <c r="F173" t="s">
-        <v>433</v>
+        <v>746</v>
+      </c>
+      <c r="G173" s="2">
+        <v>1</v>
+      </c>
+      <c r="H173" s="2">
+        <v>15</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>557</v>
+        <v>824</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
@@ -8110,36 +8118,36 @@
         <v>199</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>659</v>
+        <v>595</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B175" s="1">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="C175" s="1">
-        <v>0.2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="D175" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E175" t="s">
-        <v>751</v>
+        <v>471</v>
       </c>
       <c r="F175" t="s">
-        <v>752</v>
+        <v>472</v>
       </c>
       <c r="G175" s="2">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="H175" s="2">
-        <v>15</v>
-      </c>
-      <c r="I175" s="4" t="s">
-        <v>753</v>
+        <v>145</v>
+      </c>
+      <c r="I175" s="3" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
@@ -8168,7 +8176,7 @@
         <v>0.72</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
@@ -8197,7 +8205,7 @@
         <v>0.06</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
@@ -8289,7 +8297,7 @@
         <v>9.99</v>
       </c>
       <c r="I181" s="3" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
@@ -8318,7 +8326,7 @@
         <v>0.8</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
@@ -8347,7 +8355,7 @@
         <v>13.49</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
@@ -8376,7 +8384,7 @@
         <v>0.9</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -8425,7 +8433,7 @@
         <v>568.9</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
@@ -8454,7 +8462,7 @@
         <v>76.7</v>
       </c>
       <c r="I187" s="3" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
@@ -8479,60 +8487,60 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="B189" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="C189" s="1">
         <v>0.05</v>
       </c>
-      <c r="C189" s="1">
-        <v>2.5000000000000001E-2</v>
-      </c>
       <c r="D189" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E189" t="s">
-        <v>471</v>
+        <v>747</v>
       </c>
       <c r="F189" t="s">
-        <v>472</v>
+        <v>748</v>
       </c>
       <c r="G189" s="2">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="H189" s="2">
-        <v>145</v>
+        <v>301</v>
       </c>
       <c r="I189" s="3" t="s">
-        <v>667</v>
+        <v>749</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="B190" s="1">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="C190" s="1">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="D190" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E190" t="s">
-        <v>754</v>
+        <v>526</v>
       </c>
       <c r="F190" t="s">
-        <v>755</v>
+        <v>527</v>
       </c>
       <c r="G190" s="2">
-        <v>18</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="H190" s="2">
-        <v>301</v>
+        <v>48.5</v>
       </c>
       <c r="I190" s="3" t="s">
-        <v>756</v>
+        <v>677</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
@@ -8561,7 +8569,7 @@
         <v>225</v>
       </c>
       <c r="I191" s="3" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
@@ -8619,7 +8627,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
@@ -8648,7 +8656,7 @@
         <v>0.95</v>
       </c>
       <c r="I194" s="3" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
@@ -8677,7 +8685,7 @@
         <v>200</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
@@ -8706,7 +8714,7 @@
         <v>1.68</v>
       </c>
       <c r="I196" s="3" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
@@ -8735,7 +8743,7 @@
         <v>12.1</v>
       </c>
       <c r="I197" s="3" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
@@ -8764,7 +8772,7 @@
         <v>39</v>
       </c>
       <c r="I198" s="3" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
@@ -8793,7 +8801,7 @@
         <v>740</v>
       </c>
       <c r="I199" s="3" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
@@ -8822,7 +8830,7 @@
         <v>740</v>
       </c>
       <c r="I200" s="3" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
@@ -8851,12 +8859,12 @@
         <v>308</v>
       </c>
       <c r="I201" s="3" t="s">
-        <v>676</v>
+        <v>600</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="B202" s="1">
         <v>0.12</v>
@@ -8880,7 +8888,7 @@
         <v>5.2</v>
       </c>
       <c r="I202" s="3" t="s">
-        <v>677</v>
+        <v>553</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
@@ -8909,7 +8917,7 @@
         <v>77</v>
       </c>
       <c r="I203" s="3" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
@@ -8938,7 +8946,7 @@
         <v>2.99</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
@@ -8967,7 +8975,7 @@
         <v>0.79</v>
       </c>
       <c r="I205" s="3" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
@@ -8996,7 +9004,7 @@
         <v>1.75</v>
       </c>
       <c r="I206" s="3" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
@@ -9025,7 +9033,7 @@
         <v>60</v>
       </c>
       <c r="I207" s="3" t="s">
-        <v>680</v>
+        <v>639</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
@@ -9054,7 +9062,7 @@
         <v>7.6</v>
       </c>
       <c r="I208" s="3" t="s">
-        <v>681</v>
+        <v>554</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
@@ -9083,7 +9091,7 @@
         <v>4.2</v>
       </c>
       <c r="I209" s="3" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
@@ -9112,7 +9120,7 @@
         <v>350</v>
       </c>
       <c r="I210" s="3" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
@@ -9141,7 +9149,7 @@
         <v>1600</v>
       </c>
       <c r="I211" s="3" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -9170,12 +9178,12 @@
         <v>200</v>
       </c>
       <c r="I212" s="3" t="s">
-        <v>683</v>
+        <v>564</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="B213" s="1">
         <v>0.221</v>
@@ -9187,10 +9195,10 @@
         <v>7</v>
       </c>
       <c r="E213" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="F213" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="G213" s="2">
         <v>12</v>
@@ -9198,8 +9206,8 @@
       <c r="H213" s="2">
         <v>20</v>
       </c>
-      <c r="I213" s="4" t="s">
-        <v>759</v>
+      <c r="I213" s="3" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
@@ -9228,7 +9236,7 @@
         <v>150</v>
       </c>
       <c r="I214" s="3" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -9257,7 +9265,7 @@
         <v>0.9</v>
       </c>
       <c r="I215" s="3" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
@@ -9286,7 +9294,7 @@
         <v>771</v>
       </c>
       <c r="I216" s="3" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -9315,7 +9323,7 @@
         <v>100</v>
       </c>
       <c r="I217" s="3" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
@@ -9344,7 +9352,7 @@
         <v>79.3</v>
       </c>
       <c r="I218" s="3" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
@@ -9373,7 +9381,7 @@
         <v>285</v>
       </c>
       <c r="I219" s="3" t="s">
-        <v>688</v>
+        <v>614</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
@@ -9401,62 +9409,278 @@
       <c r="H224"/>
       <c r="I224"/>
     </row>
-    <row r="225" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="226" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="227" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="228" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="229" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="230" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="231" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="232" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="233" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="234" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="235" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="236" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="237" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="238" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="239" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="240" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="241" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="242" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="243" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="244" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="245" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="246" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="247" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="248" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="249" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="250" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="251" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="252" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="253" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="254" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="255" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="256" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="257" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="258" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="259" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="260" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="261" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="262" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="263" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="264" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="265" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="266" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="267" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="268" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="269" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="270" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="271" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="272" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="273" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="274" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="275" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="276" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="277" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="278" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G225"/>
+      <c r="H225"/>
+      <c r="I225"/>
+    </row>
+    <row r="226" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G226"/>
+      <c r="H226"/>
+      <c r="I226"/>
+    </row>
+    <row r="227" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G227"/>
+      <c r="H227"/>
+      <c r="I227"/>
+    </row>
+    <row r="228" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G228"/>
+      <c r="H228"/>
+      <c r="I228"/>
+    </row>
+    <row r="229" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G229"/>
+      <c r="H229"/>
+      <c r="I229"/>
+    </row>
+    <row r="230" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G230"/>
+      <c r="H230"/>
+      <c r="I230"/>
+    </row>
+    <row r="231" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G231"/>
+      <c r="H231"/>
+      <c r="I231"/>
+    </row>
+    <row r="232" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G232"/>
+      <c r="H232"/>
+      <c r="I232"/>
+    </row>
+    <row r="233" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G233"/>
+      <c r="H233"/>
+      <c r="I233"/>
+    </row>
+    <row r="234" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G234"/>
+      <c r="H234"/>
+      <c r="I234"/>
+    </row>
+    <row r="235" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G235"/>
+      <c r="H235"/>
+      <c r="I235"/>
+    </row>
+    <row r="236" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G236"/>
+      <c r="H236"/>
+      <c r="I236"/>
+    </row>
+    <row r="237" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G237"/>
+      <c r="H237"/>
+      <c r="I237"/>
+    </row>
+    <row r="238" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G238"/>
+      <c r="H238"/>
+      <c r="I238"/>
+    </row>
+    <row r="239" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G239"/>
+      <c r="H239"/>
+      <c r="I239"/>
+    </row>
+    <row r="240" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G240"/>
+      <c r="H240"/>
+      <c r="I240"/>
+    </row>
+    <row r="241" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G241"/>
+      <c r="H241"/>
+      <c r="I241"/>
+    </row>
+    <row r="242" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G242"/>
+      <c r="H242"/>
+      <c r="I242"/>
+    </row>
+    <row r="243" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G243"/>
+      <c r="H243"/>
+      <c r="I243"/>
+    </row>
+    <row r="244" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G244"/>
+      <c r="H244"/>
+      <c r="I244"/>
+    </row>
+    <row r="245" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G245"/>
+      <c r="H245"/>
+      <c r="I245"/>
+    </row>
+    <row r="246" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G246"/>
+      <c r="H246"/>
+      <c r="I246"/>
+    </row>
+    <row r="247" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G247"/>
+      <c r="H247"/>
+      <c r="I247"/>
+    </row>
+    <row r="248" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G248"/>
+      <c r="H248"/>
+      <c r="I248"/>
+    </row>
+    <row r="249" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G249"/>
+      <c r="H249"/>
+      <c r="I249"/>
+    </row>
+    <row r="250" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G250"/>
+      <c r="H250"/>
+      <c r="I250"/>
+    </row>
+    <row r="251" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G251"/>
+      <c r="H251"/>
+      <c r="I251"/>
+    </row>
+    <row r="252" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G252"/>
+      <c r="H252"/>
+      <c r="I252"/>
+    </row>
+    <row r="253" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G253"/>
+      <c r="H253"/>
+      <c r="I253"/>
+    </row>
+    <row r="254" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G254"/>
+      <c r="H254"/>
+      <c r="I254"/>
+    </row>
+    <row r="255" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G255"/>
+      <c r="H255"/>
+      <c r="I255"/>
+    </row>
+    <row r="256" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G256"/>
+      <c r="H256"/>
+      <c r="I256"/>
+    </row>
+    <row r="257" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G257"/>
+      <c r="H257"/>
+      <c r="I257"/>
+    </row>
+    <row r="258" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G258"/>
+      <c r="H258"/>
+      <c r="I258"/>
+    </row>
+    <row r="259" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G259"/>
+      <c r="H259"/>
+      <c r="I259"/>
+    </row>
+    <row r="260" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G260"/>
+      <c r="H260"/>
+      <c r="I260"/>
+    </row>
+    <row r="261" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G261"/>
+      <c r="H261"/>
+      <c r="I261"/>
+    </row>
+    <row r="262" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G262"/>
+      <c r="H262"/>
+      <c r="I262"/>
+    </row>
+    <row r="263" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G263"/>
+      <c r="H263"/>
+      <c r="I263"/>
+    </row>
+    <row r="264" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G264"/>
+      <c r="H264"/>
+      <c r="I264"/>
+    </row>
+    <row r="265" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G265"/>
+      <c r="H265"/>
+      <c r="I265"/>
+    </row>
+    <row r="266" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G266"/>
+      <c r="H266"/>
+      <c r="I266"/>
+    </row>
+    <row r="267" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G267"/>
+      <c r="H267"/>
+      <c r="I267"/>
+    </row>
+    <row r="268" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G268"/>
+      <c r="H268"/>
+      <c r="I268"/>
+    </row>
+    <row r="269" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G269"/>
+      <c r="H269"/>
+      <c r="I269"/>
+    </row>
+    <row r="270" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G270"/>
+      <c r="H270"/>
+      <c r="I270"/>
+    </row>
+    <row r="271" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G271"/>
+      <c r="H271"/>
+      <c r="I271"/>
+    </row>
+    <row r="272" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G272"/>
+      <c r="H272"/>
+      <c r="I272"/>
+    </row>
+    <row r="273" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G273"/>
+      <c r="H273"/>
+      <c r="I273"/>
+    </row>
+    <row r="274" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G274"/>
+      <c r="H274"/>
+      <c r="I274"/>
+    </row>
+    <row r="275" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G275"/>
+      <c r="H275"/>
+      <c r="I275"/>
+    </row>
+    <row r="276" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G276"/>
+      <c r="H276"/>
+      <c r="I276"/>
+    </row>
+    <row r="277" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G277"/>
+      <c r="H277"/>
+      <c r="I277"/>
+    </row>
+    <row r="278" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G278"/>
+      <c r="H278"/>
+      <c r="I278"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H278" xr:uid="{F9E839D1-D9BB-491F-96EB-30E6182BBB70}"/>
+  <autoFilter ref="A1:J219" xr:uid="{F9E839D1-D9BB-491F-96EB-30E6182BBB70}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -9471,377 +9695,377 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>772</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>780</v>
+        <v>817</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>825</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>209</v>
+        <v>818</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>826</v>
+        <v>752</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>765</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>380</v>
+        <v>758</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>781</v>
+        <v>821</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>829</v>
+        <v>774</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>801</v>
+        <v>778</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>802</v>
+        <v>779</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>803</v>
+        <v>780</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>804</v>
+        <v>781</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>805</v>
+        <v>782</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>806</v>
+        <v>783</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>807</v>
+        <v>784</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>808</v>
+        <v>785</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>809</v>
+        <v>786</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>815</v>
+        <v>790</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>820</v>
+        <v>285</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>285</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>150</v>
+        <v>819</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>828</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
@@ -9856,7 +10080,7 @@
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
     </row>
   </sheetData>

--- a/Base de Dados.xlsx
+++ b/Base de Dados.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Estudos\Desdobramento - Sigma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C095EF3-1BFA-4608-9A0A-E8FE96D14733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBFE60D-5841-4C86-ADAA-DF14842F9BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{052EBD17-0308-4E6D-95A6-CA02714B48B2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{052EBD17-0308-4E6D-95A6-CA02714B48B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Base de Dados" sheetId="1" r:id="rId1"/>
     <sheet name="Equipamentos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base de Dados'!$A$1:$J$219</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Equipamentos!$A$2:$A$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base de Dados'!$A$1:$I$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Equipamentos!$A$2:$A$80</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="917">
   <si>
     <t>Bias MÃ¡ximo</t>
   </si>
@@ -1330,12 +1330,6 @@
     <t>PRL</t>
   </si>
   <si>
-    <t>Proteina Urinaria</t>
-  </si>
-  <si>
-    <t>LÃ­quor</t>
-  </si>
-  <si>
     <t>proteina</t>
   </si>
   <si>
@@ -1798,9 +1792,6 @@
     <t>0 - 50</t>
   </si>
   <si>
-    <t>0 - 9</t>
-  </si>
-  <si>
     <t>0,3 - 3,8</t>
   </si>
   <si>
@@ -1819,9 +1810,6 @@
     <t>0 - 500</t>
   </si>
   <si>
-    <t>0 - 0,7</t>
-  </si>
-  <si>
     <t>76 - 152</t>
   </si>
   <si>
@@ -1852,12 +1840,6 @@
     <t>0 - 200</t>
   </si>
   <si>
-    <t>0 - 0,1</t>
-  </si>
-  <si>
-    <t>0 - 0,6</t>
-  </si>
-  <si>
     <t>5 - 138</t>
   </si>
   <si>
@@ -1975,9 +1957,6 @@
     <t>14 - 46</t>
   </si>
   <si>
-    <t>15 - 65</t>
-  </si>
-  <si>
     <t>0,1 - 1,99</t>
   </si>
   <si>
@@ -2011,9 +1990,6 @@
     <t>0 - 9,99</t>
   </si>
   <si>
-    <t>0 - 0,8</t>
-  </si>
-  <si>
     <t>0 - 13,49</t>
   </si>
   <si>
@@ -2056,9 +2032,6 @@
     <t>5 - 41</t>
   </si>
   <si>
-    <t>0 - 2,99</t>
-  </si>
-  <si>
     <t>0 - 0,79</t>
   </si>
   <si>
@@ -2518,20 +2491,311 @@
     <t>12 - 20</t>
   </si>
   <si>
-    <t>0 - 17</t>
-  </si>
-  <si>
     <t>0 - 0,89</t>
   </si>
   <si>
-    <t>0 - 115</t>
+    <t>XN-10 - 1A - 54513</t>
+  </si>
+  <si>
+    <t>XN-10 - 2A- 54515</t>
+  </si>
+  <si>
+    <t>XN-10 - 3A - 54516</t>
+  </si>
+  <si>
+    <t>XN-10 - 4A - 54517</t>
+  </si>
+  <si>
+    <t>XN-10 - 1B - 54998</t>
+  </si>
+  <si>
+    <t>XN-10 - 2B - 55000</t>
+  </si>
+  <si>
+    <t>XN-10 - 3B - 55001</t>
+  </si>
+  <si>
+    <t>XN-10 - 4B - 55002</t>
+  </si>
+  <si>
+    <t>C-513 - 0022</t>
+  </si>
+  <si>
+    <t>C-513 - 0024</t>
+  </si>
+  <si>
+    <t>C-513 - 0030</t>
+  </si>
+  <si>
+    <t>RBC</t>
+  </si>
+  <si>
+    <t>WBC</t>
+  </si>
+  <si>
+    <t>NEA</t>
+  </si>
+  <si>
+    <t>LYA</t>
+  </si>
+  <si>
+    <t>MOA</t>
+  </si>
+  <si>
+    <t>EOA</t>
+  </si>
+  <si>
+    <t>BAA</t>
+  </si>
+  <si>
+    <t>PLTF</t>
+  </si>
+  <si>
+    <t>IPF</t>
+  </si>
+  <si>
+    <t>RETR</t>
+  </si>
+  <si>
+    <t>IRF</t>
+  </si>
+  <si>
+    <t>HGB</t>
+  </si>
+  <si>
+    <t>RETHE</t>
+  </si>
+  <si>
+    <t>IG</t>
+  </si>
+  <si>
+    <t>NRBCA</t>
+  </si>
+  <si>
+    <t>HCT</t>
+  </si>
+  <si>
+    <t>VCM</t>
+  </si>
+  <si>
+    <t>HCM</t>
+  </si>
+  <si>
+    <t>CHCM</t>
+  </si>
+  <si>
+    <t>RDW</t>
+  </si>
+  <si>
+    <t>VPM</t>
+  </si>
+  <si>
+    <t>HbA1C</t>
+  </si>
+  <si>
+    <t>PLT</t>
+  </si>
+  <si>
+    <t>hemacias</t>
+  </si>
+  <si>
+    <t>leucocitos</t>
+  </si>
+  <si>
+    <t>neutrofilos</t>
+  </si>
+  <si>
+    <t>linfocitos</t>
+  </si>
+  <si>
+    <t>monocitos</t>
+  </si>
+  <si>
+    <t>eosinofilos</t>
+  </si>
+  <si>
+    <t>basofilos</t>
+  </si>
+  <si>
+    <t>ipf</t>
+  </si>
+  <si>
+    <t>retr</t>
+  </si>
+  <si>
+    <t>irf</t>
+  </si>
+  <si>
+    <t>hemoglobina</t>
+  </si>
+  <si>
+    <t>rethe</t>
+  </si>
+  <si>
+    <t>ig</t>
+  </si>
+  <si>
+    <t>eritroblasto</t>
+  </si>
+  <si>
+    <t>hematocrito</t>
+  </si>
+  <si>
+    <t>vcm</t>
+  </si>
+  <si>
+    <t>hcm</t>
+  </si>
+  <si>
+    <t>chcm</t>
+  </si>
+  <si>
+    <t>rdw</t>
+  </si>
+  <si>
+    <t>plaqueta</t>
+  </si>
+  <si>
+    <t>plaqueta fluorescente</t>
+  </si>
+  <si>
+    <t>vpm</t>
+  </si>
+  <si>
+    <t>hemoglobina glicada</t>
+  </si>
+  <si>
+    <t>Zona cinza</t>
+  </si>
+  <si>
+    <t>0,9 - 1,10</t>
+  </si>
+  <si>
+    <t>0,9 - 0,99</t>
+  </si>
+  <si>
+    <t>0 - 114</t>
+  </si>
+  <si>
+    <t>0 - 33</t>
+  </si>
+  <si>
+    <t>0 - 6,99</t>
+  </si>
+  <si>
+    <t>7 - 10</t>
+  </si>
+  <si>
+    <t>0 - 13,99</t>
+  </si>
+  <si>
+    <t>14 - 20</t>
+  </si>
+  <si>
+    <t>10 - 40</t>
+  </si>
+  <si>
+    <t>0 - 8,99</t>
+  </si>
+  <si>
+    <t>9 - 10,99</t>
+  </si>
+  <si>
+    <t>0,9 - 1,09</t>
+  </si>
+  <si>
+    <t>0 - 0,49</t>
+  </si>
+  <si>
+    <t>0,5 - 0,99</t>
+  </si>
+  <si>
+    <t>0 - 0,69</t>
+  </si>
+  <si>
+    <t>0,7 - 0,99</t>
+  </si>
+  <si>
+    <t>10 - 15</t>
+  </si>
+  <si>
+    <t>0 - 0,59</t>
+  </si>
+  <si>
+    <t>0,6 - 0,99</t>
+  </si>
+  <si>
+    <t>INTRISEC</t>
+  </si>
+  <si>
+    <t>7 - 9,99</t>
+  </si>
+  <si>
+    <t>170 - 370</t>
+  </si>
+  <si>
+    <t>90 - 210</t>
+  </si>
+  <si>
+    <t>KAPPA</t>
+  </si>
+  <si>
+    <t>LAMBDA</t>
+  </si>
+  <si>
+    <t>0 - 3,49</t>
+  </si>
+  <si>
+    <t>3,5 - 5,0</t>
+  </si>
+  <si>
+    <t>17,3 - 74,1</t>
+  </si>
+  <si>
+    <t>2 - 2,49</t>
+  </si>
+  <si>
+    <t>Proteina (Líquor)</t>
+  </si>
+  <si>
+    <t>15 - 45</t>
+  </si>
+  <si>
+    <t>0 - 1,99</t>
+  </si>
+  <si>
+    <t>2 - 3</t>
+  </si>
+  <si>
+    <t>0,8 - 0,99</t>
+  </si>
+  <si>
+    <t>13,50 - 16,49</t>
+  </si>
+  <si>
+    <t>0,90 - 1,09</t>
+  </si>
+  <si>
+    <t>1 - 2,99</t>
+  </si>
+  <si>
+    <t>0,80 - 0,99</t>
+  </si>
+  <si>
+    <t>TTG - IgA</t>
+  </si>
+  <si>
+    <t>TTG - IgG</t>
+  </si>
+  <si>
+    <t>5,7 - 6,4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2665,6 +2929,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2964,7 +3233,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -3007,16 +3276,32 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -3048,6 +3333,7 @@
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="42" xr:uid="{065BB332-9816-4247-9C33-9F32D21DBFDD}"/>
     <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Ruim" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Saída" xfId="10" builtinId="21" customBuiltin="1"/>
@@ -3074,10 +3360,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}" name="Equipamentos" displayName="Equipamentos" ref="A1:A78" totalsRowShown="0">
-  <autoFilter ref="A1:A78" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A78">
-    <sortCondition ref="A1:A78"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}" name="Equipamentos" displayName="Equipamentos" ref="A1:A89" totalsRowShown="0">
+  <autoFilter ref="A1:A89" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A89">
+    <sortCondition ref="A1:A89"/>
   </sortState>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{1B9AEB56-1EBB-4F60-AF89-FB7F0CA8B355}" name="Equipamentos"/>
@@ -3403,23 +3689,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9E839D1-D9BB-491F-96EB-30E6182BBB70}">
-  <dimension ref="A1:I278"/>
+  <dimension ref="A1:J278"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9.140625" style="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="2"/>
     <col min="9" max="9" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>684</v>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>675</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -3440,11 +3728,14 @@
         <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+        <v>547</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>249</v>
       </c>
       <c r="B2" s="1">
@@ -3469,11 +3760,11 @@
         <v>26.8</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>379</v>
       </c>
       <c r="B3" s="1">
@@ -3498,12 +3789,12 @@
         <v>75</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>689</v>
+        <v>634</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>680</v>
       </c>
       <c r="B4" s="1">
         <v>0.15</v>
@@ -3527,11 +3818,11 @@
         <v>7</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="1">
@@ -3556,11 +3847,11 @@
         <v>46</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="1">
@@ -3585,11 +3876,11 @@
         <v>0.99</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B7" s="1">
@@ -3614,12 +3905,12 @@
         <v>0.3</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>692</v>
+        <v>570</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>683</v>
       </c>
       <c r="B8" s="1">
         <v>6.0999999999999999E-2</v>
@@ -3643,11 +3934,11 @@
         <v>5.2</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>240</v>
       </c>
       <c r="B9" s="1">
@@ -3672,11 +3963,11 @@
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B10" s="1">
@@ -3701,12 +3992,12 @@
         <v>39.200000000000003</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>717</v>
+        <v>553</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>708</v>
       </c>
       <c r="B11" s="1">
         <v>0.18</v>
@@ -3730,12 +4021,12 @@
         <v>200</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>718</v>
+        <v>554</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>709</v>
       </c>
       <c r="B12" s="1">
         <v>0.2</v>
@@ -3750,11 +4041,11 @@
         <v>29</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B13" s="1">
@@ -3779,12 +4070,12 @@
         <v>155</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>719</v>
+        <v>556</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>710</v>
       </c>
       <c r="B14" s="1">
         <v>0.2</v>
@@ -3799,11 +4090,11 @@
         <v>33</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="1">
@@ -3828,11 +4119,11 @@
         <v>5.8</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="1">
@@ -3857,11 +4148,11 @@
         <v>2.71</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>246</v>
       </c>
       <c r="B17" s="1">
@@ -3886,12 +4177,12 @@
         <v>193</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>690</v>
+        <v>604</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>681</v>
       </c>
       <c r="B18" s="1">
         <v>0.19400000000000001</v>
@@ -3903,10 +4194,10 @@
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="F18" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="G18" s="2">
         <v>15</v>
@@ -3915,11 +4206,11 @@
         <v>99</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="1">
@@ -3944,11 +4235,11 @@
         <v>54</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>45</v>
       </c>
       <c r="B20" s="1">
@@ -3973,12 +4264,12 @@
         <v>1.07</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>694</v>
+        <v>561</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>685</v>
       </c>
       <c r="B21" s="1">
         <v>0.3</v>
@@ -4002,12 +4293,12 @@
         <v>100</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>686</v>
+        <v>559</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>677</v>
       </c>
       <c r="B22" s="1">
         <v>0.3</v>
@@ -4028,14 +4319,14 @@
         <v>0</v>
       </c>
       <c r="H22" s="2">
-        <v>17</v>
+        <v>9.99</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B23" s="1">
@@ -4060,11 +4351,11 @@
         <v>0.99</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="1">
@@ -4089,11 +4380,11 @@
         <v>60</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B25" s="1">
@@ -4118,11 +4409,14 @@
         <v>0.89</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+        <v>817</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>63</v>
       </c>
       <c r="B26" s="1">
@@ -4147,11 +4441,11 @@
         <v>60</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>66</v>
       </c>
       <c r="B27" s="1">
@@ -4176,11 +4470,11 @@
         <v>60</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B28" s="1">
@@ -4202,14 +4496,14 @@
         <v>0</v>
       </c>
       <c r="H28" s="2">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>72</v>
       </c>
       <c r="B29" s="1">
@@ -4231,14 +4525,17 @@
         <v>0</v>
       </c>
       <c r="H29" s="2">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+        <v>817</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>75</v>
       </c>
       <c r="B30" s="1">
@@ -4263,11 +4560,11 @@
         <v>28</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>78</v>
       </c>
       <c r="B31" s="1">
@@ -4292,12 +4589,12 @@
         <v>24.9</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>687</v>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>678</v>
       </c>
       <c r="B32" s="1">
         <v>0.3</v>
@@ -4318,15 +4615,15 @@
         <v>0</v>
       </c>
       <c r="H32" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>688</v>
+        <v>878</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>679</v>
       </c>
       <c r="B33" s="1">
         <v>0.22</v>
@@ -4347,14 +4644,14 @@
         <v>0</v>
       </c>
       <c r="H33" s="2">
-        <v>115</v>
+        <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>81</v>
       </c>
       <c r="B34" s="1">
@@ -4379,11 +4676,11 @@
         <v>304</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
         <v>84</v>
       </c>
       <c r="B35" s="1">
@@ -4408,11 +4705,11 @@
         <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B36" s="1">
@@ -4427,12 +4724,21 @@
       <c r="E36" t="s">
         <v>89</v>
       </c>
+      <c r="G36" s="2">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>6.99</v>
+      </c>
       <c r="I36" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+        <v>880</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>90</v>
       </c>
       <c r="B37" s="1">
@@ -4447,12 +4753,21 @@
       <c r="E37" t="s">
         <v>91</v>
       </c>
+      <c r="G37" s="2">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>6.99</v>
+      </c>
       <c r="I37" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+        <v>880</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B38" s="1">
@@ -4471,11 +4786,11 @@
         <v>100</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B39" s="1">
@@ -4494,11 +4809,11 @@
         <v>103</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
         <v>104</v>
       </c>
       <c r="B40" s="1">
@@ -4513,12 +4828,21 @@
       <c r="E40" t="s">
         <v>105</v>
       </c>
+      <c r="G40" s="2">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2">
+        <v>6.99</v>
+      </c>
       <c r="I40" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+        <v>880</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
         <v>106</v>
       </c>
       <c r="B41" s="1">
@@ -4533,12 +4857,21 @@
       <c r="E41" t="s">
         <v>107</v>
       </c>
+      <c r="G41" s="2">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2">
+        <v>6.99</v>
+      </c>
       <c r="I41" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+        <v>880</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
         <v>108</v>
       </c>
       <c r="B42" s="1">
@@ -4563,11 +4896,11 @@
         <v>77</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>111</v>
       </c>
       <c r="B43" s="1">
@@ -4592,11 +4925,11 @@
         <v>0.78</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B44" s="1">
@@ -4612,11 +4945,11 @@
         <v>115</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B45" s="1">
@@ -4632,11 +4965,11 @@
         <v>117</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
         <v>303</v>
       </c>
       <c r="B46" s="1">
@@ -4661,12 +4994,12 @@
         <v>5</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>693</v>
+        <v>617</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>684</v>
       </c>
       <c r="B47" s="1">
         <v>0.19400000000000001</v>
@@ -4678,10 +5011,10 @@
         <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="F47" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
@@ -4690,11 +5023,11 @@
         <v>650</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
         <v>321</v>
       </c>
       <c r="B48" s="1">
@@ -4719,11 +5052,11 @@
         <v>15</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
         <v>124</v>
       </c>
       <c r="B49" s="1">
@@ -4748,11 +5081,11 @@
         <v>10</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
         <v>127</v>
       </c>
       <c r="B50" s="1">
@@ -4777,12 +5110,12 @@
         <v>0.9</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>720</v>
+        <v>573</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>711</v>
       </c>
       <c r="B51" s="1">
         <v>0.155</v>
@@ -4806,11 +5139,11 @@
         <v>39</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
         <v>132</v>
       </c>
       <c r="B52" s="1">
@@ -4835,11 +5168,11 @@
         <v>35</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
         <v>135</v>
       </c>
       <c r="B53" s="1">
@@ -4864,11 +5197,11 @@
         <v>28.5</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
         <v>138</v>
       </c>
       <c r="B54" s="1">
@@ -4893,11 +5226,11 @@
         <v>34</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
         <v>141</v>
       </c>
       <c r="B55" s="1">
@@ -4922,11 +5255,11 @@
         <v>25</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
         <v>144</v>
       </c>
       <c r="B56" s="1">
@@ -4951,11 +5284,11 @@
         <v>6.9</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
         <v>369</v>
       </c>
       <c r="B57" s="1">
@@ -4980,12 +5313,12 @@
         <v>225</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>704</v>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>695</v>
       </c>
       <c r="B58" s="1">
         <v>0.15</v>
@@ -5009,11 +5342,11 @@
         <v>9.6</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
         <v>149</v>
       </c>
       <c r="B59" s="1">
@@ -5038,11 +5371,11 @@
         <v>1.4</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
         <v>153</v>
       </c>
       <c r="B60" s="1">
@@ -5067,11 +5400,11 @@
         <v>14.3</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
         <v>156</v>
       </c>
       <c r="B61" s="1">
@@ -5096,11 +5429,11 @@
         <v>50</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
         <v>371</v>
       </c>
       <c r="B62" s="1">
@@ -5125,11 +5458,11 @@
         <v>130</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
         <v>160</v>
       </c>
       <c r="B63" s="1">
@@ -5147,12 +5480,21 @@
       <c r="F63" t="s">
         <v>162</v>
       </c>
+      <c r="G63" s="2">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2">
+        <v>13.99</v>
+      </c>
       <c r="I63" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+        <v>882</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
         <v>163</v>
       </c>
       <c r="B64" s="1">
@@ -5170,12 +5512,21 @@
       <c r="F64" t="s">
         <v>162</v>
       </c>
+      <c r="G64" s="2">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2">
+        <v>9.99</v>
+      </c>
       <c r="I64" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+        <v>649</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B65" s="1">
@@ -5193,12 +5544,21 @@
       <c r="F65" t="s">
         <v>162</v>
       </c>
+      <c r="G65" s="2">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2">
+        <v>9.99</v>
+      </c>
       <c r="I65" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+        <v>649</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B66" s="1">
@@ -5220,14 +5580,17 @@
         <v>0</v>
       </c>
       <c r="H66" s="2">
-        <v>9</v>
+        <v>8.99</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+        <v>885</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
         <v>170</v>
       </c>
       <c r="B67" s="1">
@@ -5249,14 +5612,17 @@
         <v>0</v>
       </c>
       <c r="H67" s="2">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+        <v>817</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
         <v>173</v>
       </c>
       <c r="B68" s="1">
@@ -5274,12 +5640,21 @@
       <c r="F68" t="s">
         <v>173</v>
       </c>
+      <c r="G68" s="2">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2">
+        <v>6.99</v>
+      </c>
       <c r="I68" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+        <v>880</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
         <v>175</v>
       </c>
       <c r="B69" s="1">
@@ -5304,11 +5679,11 @@
         <v>3.8</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
         <v>177</v>
       </c>
       <c r="B70" s="1">
@@ -5333,11 +5708,11 @@
         <v>60</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
         <v>180</v>
       </c>
       <c r="B71" s="1">
@@ -5355,12 +5730,18 @@
       <c r="F71" t="s">
         <v>182</v>
       </c>
+      <c r="G71" s="2">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2">
+        <v>0.99</v>
+      </c>
       <c r="I71" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
         <v>183</v>
       </c>
       <c r="B72" s="1">
@@ -5385,12 +5766,12 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>703</v>
+        <v>586</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>694</v>
       </c>
       <c r="B73" s="1">
         <v>0.25</v>
@@ -5402,10 +5783,10 @@
         <v>7</v>
       </c>
       <c r="E73" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="F73" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="G73" s="2">
         <v>100</v>
@@ -5414,12 +5795,12 @@
         <v>300</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>706</v>
+        <v>718</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>697</v>
       </c>
       <c r="B74" s="1">
         <v>0.13</v>
@@ -5443,12 +5824,12 @@
         <v>107</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>705</v>
+        <v>588</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>696</v>
       </c>
       <c r="B75" s="1">
         <v>0.1</v>
@@ -5460,10 +5841,10 @@
         <v>7</v>
       </c>
       <c r="E75" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="F75" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="G75" s="2">
         <v>110</v>
@@ -5472,11 +5853,11 @@
         <v>250</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
         <v>190</v>
       </c>
       <c r="B76" s="1">
@@ -5498,14 +5879,17 @@
         <v>0</v>
       </c>
       <c r="H76" s="2">
-        <v>500</v>
+        <v>0.49</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+        <v>888</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
         <v>193</v>
       </c>
       <c r="B77" s="1">
@@ -5527,15 +5911,18 @@
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>502</v>
+        <v>890</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="B78" s="1">
         <v>0.4</v>
@@ -5547,10 +5934,10 @@
         <v>10</v>
       </c>
       <c r="E78" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F78" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G78" s="2">
         <v>5</v>
@@ -5559,12 +5946,12 @@
         <v>41</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>514</v>
+        <v>663</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>512</v>
       </c>
       <c r="B79" s="1">
         <v>0.2</v>
@@ -5576,10 +5963,10 @@
         <v>10</v>
       </c>
       <c r="E79" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F79" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G79" s="2">
         <v>200</v>
@@ -5588,12 +5975,12 @@
         <v>360</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>517</v>
+        <v>665</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>515</v>
       </c>
       <c r="B80" s="1">
         <v>0.16</v>
@@ -5605,10 +5992,10 @@
         <v>10</v>
       </c>
       <c r="E80" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F80" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G80" s="2">
         <v>50</v>
@@ -5617,11 +6004,11 @@
         <v>150</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
         <v>202</v>
       </c>
       <c r="B81" s="1">
@@ -5646,11 +6033,11 @@
         <v>170</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
         <v>205</v>
       </c>
       <c r="B82" s="1">
@@ -5675,11 +6062,11 @@
         <v>36</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
         <v>208</v>
       </c>
       <c r="B83" s="1">
@@ -5695,7 +6082,7 @@
         <v>210</v>
       </c>
       <c r="F83" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G83" s="2">
         <v>5.27</v>
@@ -5704,11 +6091,11 @@
         <v>22.45</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
         <v>211</v>
       </c>
       <c r="B84" s="1">
@@ -5733,12 +6120,12 @@
         <v>20.29</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>696</v>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>687</v>
       </c>
       <c r="B85" s="1">
         <v>0.2</v>
@@ -5762,12 +6149,12 @@
         <v>1.17</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>543</v>
+        <v>597</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>541</v>
       </c>
       <c r="B86" s="1">
         <v>0.25</v>
@@ -5779,10 +6166,10 @@
         <v>10</v>
       </c>
       <c r="E86" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F86" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G86" s="2">
         <v>80</v>
@@ -5791,12 +6178,12 @@
         <v>120</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>695</v>
+        <v>673</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>686</v>
       </c>
       <c r="B87" s="1">
         <v>0.3</v>
@@ -5808,10 +6195,10 @@
         <v>7</v>
       </c>
       <c r="E87" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="F87" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="G87" s="2">
         <v>39</v>
@@ -5820,11 +6207,11 @@
         <v>259</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
         <v>221</v>
       </c>
       <c r="B88" s="1">
@@ -5842,12 +6229,21 @@
       <c r="F88" t="s">
         <v>221</v>
       </c>
+      <c r="G88" s="2">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2">
+        <v>9.99</v>
+      </c>
       <c r="I88" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+        <v>649</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
         <v>223</v>
       </c>
       <c r="B89" s="1">
@@ -5872,11 +6268,11 @@
         <v>200</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
         <v>226</v>
       </c>
       <c r="B90" s="1">
@@ -5898,14 +6294,17 @@
         <v>0</v>
       </c>
       <c r="H90" s="2">
-        <v>0.1</v>
+        <v>0.69</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+        <v>890</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
         <v>229</v>
       </c>
       <c r="B91" s="1">
@@ -5927,14 +6326,17 @@
         <v>0</v>
       </c>
       <c r="H91" s="2">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+        <v>893</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
         <v>232</v>
       </c>
       <c r="B92" s="1">
@@ -5959,11 +6361,11 @@
         <v>138</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
         <v>235</v>
       </c>
       <c r="B93" s="1">
@@ -5988,11 +6390,11 @@
         <v>12</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
         <v>238</v>
       </c>
       <c r="B94" s="1">
@@ -6007,13 +6409,25 @@
       <c r="E94" t="s">
         <v>239</v>
       </c>
+      <c r="F94" t="s">
+        <v>895</v>
+      </c>
+      <c r="G94" s="2">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2">
+        <v>6.99</v>
+      </c>
       <c r="I94" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>698</v>
+        <v>880</v>
+      </c>
+      <c r="J94" s="6" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>689</v>
       </c>
       <c r="B95" s="1">
         <v>0.2</v>
@@ -6037,11 +6451,11 @@
         <v>4.5</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
         <v>243</v>
       </c>
       <c r="B96" s="1">
@@ -6066,11 +6480,11 @@
         <v>500</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
         <v>121</v>
       </c>
       <c r="B97" s="1">
@@ -6095,12 +6509,12 @@
         <v>1.2</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>685</v>
+        <v>571</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>676</v>
       </c>
       <c r="B98" s="1">
         <v>0.3</v>
@@ -6124,11 +6538,11 @@
         <v>345</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
         <v>199</v>
       </c>
       <c r="B99" s="1">
@@ -6153,12 +6567,12 @@
         <v>199</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>697</v>
+        <v>591</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>688</v>
       </c>
       <c r="B100" s="1">
         <v>0.3</v>
@@ -6170,10 +6584,10 @@
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="F100" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="G100" s="2">
         <v>40</v>
@@ -6182,12 +6596,12 @@
         <v>150</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>702</v>
+        <v>729</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>693</v>
       </c>
       <c r="B101" s="1">
         <v>0.13</v>
@@ -6211,11 +6625,11 @@
         <v>99</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
         <v>260</v>
       </c>
       <c r="B102" s="1">
@@ -6240,11 +6654,11 @@
         <v>134.80000000000001</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
         <v>262</v>
       </c>
       <c r="B103" s="1">
@@ -6260,11 +6674,11 @@
         <v>263</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
         <v>264</v>
       </c>
       <c r="B104" s="1">
@@ -6289,11 +6703,11 @@
         <v>115</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
         <v>252</v>
       </c>
       <c r="B105" s="1">
@@ -6318,11 +6732,11 @@
         <v>129</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
         <v>270</v>
       </c>
       <c r="B106" s="1">
@@ -6347,11 +6761,11 @@
         <v>3</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
         <v>272</v>
       </c>
       <c r="B107" s="1">
@@ -6366,12 +6780,21 @@
       <c r="E107" t="s">
         <v>273</v>
       </c>
+      <c r="G107" s="2">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2">
+        <v>6.99</v>
+      </c>
       <c r="I107" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+        <v>880</v>
+      </c>
+      <c r="J107" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
         <v>274</v>
       </c>
       <c r="B108" s="1">
@@ -6386,13 +6809,22 @@
       <c r="E108" t="s">
         <v>275</v>
       </c>
+      <c r="G108" s="2">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2">
+        <v>6.99</v>
+      </c>
       <c r="I108" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>700</v>
+        <v>880</v>
+      </c>
+      <c r="J108" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>691</v>
       </c>
       <c r="B109" s="1">
         <v>0.12</v>
@@ -6401,7 +6833,7 @@
         <v>0.06</v>
       </c>
       <c r="D109" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="E109" t="s">
         <v>276</v>
@@ -6416,11 +6848,11 @@
         <v>99</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
         <v>268</v>
       </c>
       <c r="B110" s="1">
@@ -6445,12 +6877,12 @@
         <v>60</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>701</v>
+        <v>611</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>692</v>
       </c>
       <c r="B111" s="1">
         <v>0.15</v>
@@ -6474,11 +6906,11 @@
         <v>500</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
         <v>278</v>
       </c>
       <c r="B112" s="1">
@@ -6503,11 +6935,11 @@
         <v>0.89</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="A113" s="4" t="s">
         <v>281</v>
       </c>
       <c r="B113" s="1">
@@ -6532,11 +6964,11 @@
         <v>200</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="A114" s="4" t="s">
         <v>284</v>
       </c>
       <c r="D114" t="s">
@@ -6546,11 +6978,11 @@
         <v>286</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="A115" s="4" t="s">
         <v>287</v>
       </c>
       <c r="B115" s="1">
@@ -6566,11 +6998,11 @@
         <v>289</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="A116" s="4" t="s">
         <v>287</v>
       </c>
       <c r="B116" s="1">
@@ -6586,11 +7018,11 @@
         <v>289</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="A117" s="4" t="s">
         <v>290</v>
       </c>
       <c r="B117" s="1">
@@ -6606,11 +7038,11 @@
         <v>291</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="A118" s="4" t="s">
         <v>292</v>
       </c>
       <c r="B118" s="1">
@@ -6626,11 +7058,11 @@
         <v>293</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="A119" s="4" t="s">
         <v>294</v>
       </c>
       <c r="B119" s="1">
@@ -6646,12 +7078,12 @@
         <v>295</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>548</v>
+      <c r="A120" s="4" t="s">
+        <v>546</v>
       </c>
       <c r="B120" s="1">
         <v>0.05</v>
@@ -6675,11 +7107,11 @@
         <v>5.6</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="A121" s="4" t="s">
         <v>296</v>
       </c>
       <c r="B121" s="1">
@@ -6704,12 +7136,12 @@
         <v>0.99</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>547</v>
+      <c r="A122" s="4" t="s">
+        <v>545</v>
       </c>
       <c r="B122" s="1">
         <v>0.186</v>
@@ -6733,11 +7165,11 @@
         <v>0.9</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="A123" s="4" t="s">
         <v>306</v>
       </c>
       <c r="B123" s="1">
@@ -6762,11 +7194,11 @@
         <v>60</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="A124" s="4" t="s">
         <v>308</v>
       </c>
       <c r="B124" s="1">
@@ -6782,11 +7214,11 @@
         <v>309</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="A125" s="4" t="s">
         <v>310</v>
       </c>
       <c r="B125" s="1">
@@ -6802,11 +7234,11 @@
         <v>312</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="A126" s="4" t="s">
         <v>313</v>
       </c>
       <c r="B126" s="1">
@@ -6831,11 +7263,11 @@
         <v>0.9</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="A127" s="4" t="s">
         <v>316</v>
       </c>
       <c r="B127" s="1">
@@ -6860,11 +7292,11 @@
         <v>0.9</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="A128" s="4" t="s">
         <v>319</v>
       </c>
       <c r="B128" s="1">
@@ -6889,11 +7321,11 @@
         <v>0.99</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
         <v>411</v>
       </c>
       <c r="B129" s="1">
@@ -6918,11 +7350,11 @@
         <v>5</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
         <v>324</v>
       </c>
       <c r="B130" s="1">
@@ -6941,11 +7373,11 @@
         <v>326</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
         <v>348</v>
       </c>
       <c r="B131" s="1">
@@ -6970,11 +7402,11 @@
         <v>350</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
         <v>331</v>
       </c>
       <c r="B132" s="1">
@@ -6990,11 +7422,11 @@
         <v>332</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
         <v>333</v>
       </c>
       <c r="B133" s="1">
@@ -7010,11 +7442,11 @@
         <v>334</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
         <v>335</v>
       </c>
       <c r="B134" s="1">
@@ -7030,11 +7462,11 @@
         <v>336</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
         <v>337</v>
       </c>
       <c r="B135" s="1">
@@ -7059,11 +7491,11 @@
         <v>6.8</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
         <v>351</v>
       </c>
       <c r="B136" s="1">
@@ -7088,11 +7520,11 @@
         <v>1600</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
         <v>340</v>
       </c>
       <c r="B137" s="1">
@@ -7114,11 +7546,11 @@
         <v>1011</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
         <v>342</v>
       </c>
       <c r="B138" s="1">
@@ -7140,11 +7572,11 @@
         <v>786</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
         <v>344</v>
       </c>
       <c r="B139" s="1">
@@ -7166,11 +7598,11 @@
         <v>85</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
         <v>346</v>
       </c>
       <c r="B140" s="1">
@@ -7192,11 +7624,11 @@
         <v>201</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
         <v>354</v>
       </c>
       <c r="B141" s="1">
@@ -7221,11 +7653,11 @@
         <v>300</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
         <v>357</v>
       </c>
       <c r="B142" s="1">
@@ -7250,11 +7682,11 @@
         <v>24.9</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
         <v>359</v>
       </c>
       <c r="B143" s="1">
@@ -7269,12 +7701,21 @@
       <c r="E143" t="s">
         <v>360</v>
       </c>
+      <c r="G143" s="2">
+        <v>0</v>
+      </c>
+      <c r="H143" s="2">
+        <v>6.99</v>
+      </c>
       <c r="I143" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+        <v>880</v>
+      </c>
+      <c r="J143" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
         <v>327</v>
       </c>
       <c r="B144" s="1">
@@ -7289,12 +7730,21 @@
       <c r="E144" t="s">
         <v>328</v>
       </c>
+      <c r="F144" t="s">
+        <v>899</v>
+      </c>
+      <c r="G144" s="2">
+        <v>170</v>
+      </c>
+      <c r="H144" s="2">
+        <v>370</v>
+      </c>
       <c r="I144" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
         <v>361</v>
       </c>
       <c r="B145" s="1">
@@ -7319,11 +7769,11 @@
         <v>22.4</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
         <v>364</v>
       </c>
       <c r="B146" s="1">
@@ -7338,12 +7788,21 @@
       <c r="E146" t="s">
         <v>365</v>
       </c>
+      <c r="G146" s="2">
+        <v>0</v>
+      </c>
+      <c r="H146" s="2">
+        <v>6.99</v>
+      </c>
       <c r="I146" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+        <v>880</v>
+      </c>
+      <c r="J146" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
         <v>329</v>
       </c>
       <c r="B147" s="1">
@@ -7358,12 +7817,21 @@
       <c r="E147" t="s">
         <v>330</v>
       </c>
+      <c r="F147" t="s">
+        <v>900</v>
+      </c>
+      <c r="G147" s="2">
+        <v>90</v>
+      </c>
+      <c r="H147" s="2">
+        <v>210</v>
+      </c>
       <c r="I147" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
         <v>366</v>
       </c>
       <c r="B148" s="1">
@@ -7388,12 +7856,12 @@
         <v>27</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>708</v>
+        <v>629</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>699</v>
       </c>
       <c r="B149" s="1">
         <v>0.25</v>
@@ -7417,12 +7885,12 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>499</v>
+        <v>636</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>497</v>
       </c>
       <c r="B150" s="1">
         <v>0.3</v>
@@ -7434,10 +7902,10 @@
         <v>10</v>
       </c>
       <c r="E150" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F150" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G150" s="2">
         <v>5</v>
@@ -7446,11 +7914,11 @@
         <v>40</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
         <v>374</v>
       </c>
       <c r="B151" s="1">
@@ -7475,11 +7943,11 @@
         <v>8.6</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
         <v>196</v>
       </c>
       <c r="B152" s="1">
@@ -7504,12 +7972,12 @@
         <v>152</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>707</v>
+        <v>590</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>698</v>
       </c>
       <c r="B153" s="1">
         <v>0.3</v>
@@ -7521,10 +7989,10 @@
         <v>7</v>
       </c>
       <c r="E153" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="F153" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="G153" s="2">
         <v>4.0999999999999996</v>
@@ -7533,11 +8001,11 @@
         <v>13.8</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
         <v>383</v>
       </c>
       <c r="B154" s="1">
@@ -7562,12 +8030,12 @@
         <v>1.2</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>710</v>
+        <v>635</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>701</v>
       </c>
       <c r="B155" s="1">
         <v>0.1</v>
@@ -7591,12 +8059,12 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>709</v>
+        <v>642</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>700</v>
       </c>
       <c r="B156" s="1">
         <v>0.1</v>
@@ -7608,10 +8076,10 @@
         <v>7</v>
       </c>
       <c r="E156" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="F156" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="G156" s="2">
         <v>17</v>
@@ -7620,11 +8088,11 @@
         <v>164</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
         <v>388</v>
       </c>
       <c r="B157" s="1">
@@ -7649,11 +8117,11 @@
         <v>2.5</v>
       </c>
       <c r="I157" s="3" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
         <v>391</v>
       </c>
       <c r="B158" s="1">
@@ -7668,12 +8136,21 @@
       <c r="E158" t="s">
         <v>392</v>
       </c>
+      <c r="G158" s="2">
+        <v>0</v>
+      </c>
+      <c r="H158" s="2">
+        <v>3.49</v>
+      </c>
       <c r="I158" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+        <v>901</v>
+      </c>
+      <c r="J158" s="6" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
         <v>393</v>
       </c>
       <c r="B159" s="1">
@@ -7695,14 +8172,14 @@
         <v>0</v>
       </c>
       <c r="H159" s="2">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
         <v>396</v>
       </c>
       <c r="B160" s="1">
@@ -7724,14 +8201,14 @@
         <v>0</v>
       </c>
       <c r="H160" s="2">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
         <v>399</v>
       </c>
       <c r="B161" s="1">
@@ -7756,11 +8233,11 @@
         <v>46</v>
       </c>
       <c r="I161" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
         <v>402</v>
       </c>
       <c r="B162" s="1">
@@ -7779,17 +8256,17 @@
         <v>404</v>
       </c>
       <c r="G162" s="2">
-        <v>15</v>
+        <v>17.3</v>
       </c>
       <c r="H162" s="2">
-        <v>65</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
         <v>405</v>
       </c>
       <c r="B163" s="1">
@@ -7814,11 +8291,14 @@
         <v>1.99</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+        <v>639</v>
+      </c>
+      <c r="J163" s="6" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
         <v>408</v>
       </c>
       <c r="B164" s="1">
@@ -7840,14 +8320,17 @@
         <v>0</v>
       </c>
       <c r="H164" s="2">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+        <v>817</v>
+      </c>
+      <c r="J164" s="6" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
         <v>186</v>
       </c>
       <c r="B165" s="1">
@@ -7872,11 +8355,11 @@
         <v>25</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
         <v>414</v>
       </c>
       <c r="B166" s="1">
@@ -7901,12 +8384,12 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>430</v>
+        <v>641</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>905</v>
       </c>
       <c r="B167" s="1">
         <v>0.25</v>
@@ -7915,21 +8398,27 @@
         <v>0.125</v>
       </c>
       <c r="D167" t="s">
+        <v>7</v>
+      </c>
+      <c r="E167" t="s">
+        <v>430</v>
+      </c>
+      <c r="F167" t="s">
         <v>431</v>
       </c>
-      <c r="E167" t="s">
-        <v>432</v>
-      </c>
-      <c r="F167" t="s">
-        <v>433</v>
+      <c r="G167" s="2">
+        <v>15</v>
+      </c>
+      <c r="H167" s="2">
+        <v>45</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>712</v>
+        <v>906</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>703</v>
       </c>
       <c r="B168" s="1">
         <v>0.12</v>
@@ -7941,10 +8430,10 @@
         <v>10</v>
       </c>
       <c r="E168" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F168" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G168" s="2">
         <v>6.4</v>
@@ -7953,11 +8442,11 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
         <v>419</v>
       </c>
       <c r="B169" s="1">
@@ -7972,12 +8461,21 @@
       <c r="E169" t="s">
         <v>420</v>
       </c>
+      <c r="G169" s="2">
+        <v>0</v>
+      </c>
+      <c r="H169" s="2">
+        <v>1.99</v>
+      </c>
       <c r="I169" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+        <v>907</v>
+      </c>
+      <c r="J169" s="8" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
         <v>421</v>
       </c>
       <c r="B170" s="1">
@@ -8002,11 +8500,11 @@
         <v>40</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
         <v>424</v>
       </c>
       <c r="B171" s="1">
@@ -8031,11 +8529,11 @@
         <v>15</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
         <v>427</v>
       </c>
       <c r="B172" s="1">
@@ -8060,12 +8558,12 @@
         <v>17.7</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>711</v>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>702</v>
       </c>
       <c r="B173" s="1">
         <v>0.4</v>
@@ -8077,10 +8575,10 @@
         <v>7</v>
       </c>
       <c r="E173" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="F173" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="G173" s="2">
         <v>1</v>
@@ -8089,11 +8587,11 @@
         <v>15</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
         <v>199</v>
       </c>
       <c r="B174" s="1">
@@ -8118,12 +8616,12 @@
         <v>199</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>714</v>
+        <v>591</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>705</v>
       </c>
       <c r="B175" s="1">
         <v>0.05</v>
@@ -8135,10 +8633,10 @@
         <v>10</v>
       </c>
       <c r="E175" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F175" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G175" s="2">
         <v>136</v>
@@ -8147,12 +8645,12 @@
         <v>145</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>436</v>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>434</v>
       </c>
       <c r="B176" s="1">
         <v>0.2</v>
@@ -8164,10 +8662,10 @@
         <v>10</v>
       </c>
       <c r="E176" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F176" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="G176" s="2">
         <v>0.01</v>
@@ -8176,12 +8674,12 @@
         <v>0.72</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>439</v>
+        <v>647</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="B177" s="1">
         <v>0.17</v>
@@ -8193,10 +8691,10 @@
         <v>10</v>
       </c>
       <c r="E177" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F177" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G177" s="2">
         <v>0</v>
@@ -8205,12 +8703,12 @@
         <v>0.06</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>442</v>
+        <v>648</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>440</v>
       </c>
       <c r="B178" s="1">
         <v>0.42</v>
@@ -8222,18 +8720,18 @@
         <v>16</v>
       </c>
       <c r="E178" t="s">
+        <v>441</v>
+      </c>
+      <c r="F178" t="s">
+        <v>442</v>
+      </c>
+      <c r="I178" s="3" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="F178" t="s">
-        <v>444</v>
-      </c>
-      <c r="I178" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>445</v>
       </c>
       <c r="B179" s="1">
         <v>0.3</v>
@@ -8245,15 +8743,24 @@
         <v>16</v>
       </c>
       <c r="E179" t="s">
-        <v>446</v>
+        <v>444</v>
+      </c>
+      <c r="G179" s="2">
+        <v>0</v>
+      </c>
+      <c r="H179" s="2">
+        <v>6.99</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>447</v>
+        <v>880</v>
+      </c>
+      <c r="J179" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>445</v>
       </c>
       <c r="B180" s="1">
         <v>0.3</v>
@@ -8265,15 +8772,24 @@
         <v>16</v>
       </c>
       <c r="E180" t="s">
-        <v>448</v>
+        <v>446</v>
+      </c>
+      <c r="G180" s="2">
+        <v>0</v>
+      </c>
+      <c r="H180" s="2">
+        <v>6.99</v>
       </c>
       <c r="I180" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>449</v>
+        <v>880</v>
+      </c>
+      <c r="J180" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>447</v>
       </c>
       <c r="B181" s="1">
         <v>0.23</v>
@@ -8282,13 +8798,13 @@
         <v>0.115</v>
       </c>
       <c r="D181" t="s">
+        <v>448</v>
+      </c>
+      <c r="E181" t="s">
+        <v>449</v>
+      </c>
+      <c r="F181" t="s">
         <v>450</v>
-      </c>
-      <c r="E181" t="s">
-        <v>451</v>
-      </c>
-      <c r="F181" t="s">
-        <v>452</v>
       </c>
       <c r="G181" s="2">
         <v>0</v>
@@ -8297,12 +8813,12 @@
         <v>9.99</v>
       </c>
       <c r="I181" s="3" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>453</v>
+        <v>649</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>451</v>
       </c>
       <c r="B182" s="1">
         <v>0.222</v>
@@ -8311,27 +8827,30 @@
         <v>0.111</v>
       </c>
       <c r="D182" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E182" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F182" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G182" s="2">
         <v>0</v>
       </c>
       <c r="H182" s="2">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>456</v>
+        <v>664</v>
+      </c>
+      <c r="J182" s="6" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>454</v>
       </c>
       <c r="B183" s="1">
         <v>0.3</v>
@@ -8343,10 +8862,10 @@
         <v>10</v>
       </c>
       <c r="E183" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F183" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G183" s="2">
         <v>0</v>
@@ -8355,12 +8874,15 @@
         <v>13.49</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>459</v>
+        <v>650</v>
+      </c>
+      <c r="J183" s="6" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>457</v>
       </c>
       <c r="B184" s="1">
         <v>0.3</v>
@@ -8372,24 +8894,27 @@
         <v>10</v>
       </c>
       <c r="E184" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F184" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G184" s="2">
         <v>0</v>
       </c>
       <c r="H184" s="2">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>462</v>
+        <v>817</v>
+      </c>
+      <c r="J184" s="6" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>460</v>
       </c>
       <c r="B185" s="1">
         <v>0.3</v>
@@ -8401,15 +8926,24 @@
         <v>16</v>
       </c>
       <c r="E185" t="s">
-        <v>463</v>
+        <v>461</v>
+      </c>
+      <c r="G185" s="2">
+        <v>0</v>
+      </c>
+      <c r="H185" s="2">
+        <v>6.99</v>
       </c>
       <c r="I185" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>464</v>
+        <v>880</v>
+      </c>
+      <c r="J185" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>462</v>
       </c>
       <c r="B186" s="1">
         <v>0.16</v>
@@ -8421,10 +8955,10 @@
         <v>12</v>
       </c>
       <c r="E186" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F186" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G186" s="2">
         <v>34.5</v>
@@ -8433,12 +8967,12 @@
         <v>568.9</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>466</v>
+        <v>651</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>464</v>
       </c>
       <c r="B187" s="1">
         <v>0.16</v>
@@ -8450,10 +8984,10 @@
         <v>10</v>
       </c>
       <c r="E187" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F187" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G187" s="2">
         <v>20.6</v>
@@ -8462,12 +8996,12 @@
         <v>76.7</v>
       </c>
       <c r="I187" s="3" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>469</v>
+        <v>652</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>467</v>
       </c>
       <c r="B188" s="1">
         <v>0.3</v>
@@ -8479,15 +9013,24 @@
         <v>16</v>
       </c>
       <c r="E188" t="s">
-        <v>470</v>
+        <v>468</v>
+      </c>
+      <c r="G188" s="2">
+        <v>0</v>
+      </c>
+      <c r="H188" s="2">
+        <v>6.99</v>
       </c>
       <c r="I188" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>713</v>
+        <v>880</v>
+      </c>
+      <c r="J188" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>704</v>
       </c>
       <c r="B189" s="1">
         <v>0.1</v>
@@ -8499,10 +9042,10 @@
         <v>7</v>
       </c>
       <c r="E189" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="F189" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="G189" s="2">
         <v>18</v>
@@ -8511,12 +9054,12 @@
         <v>301</v>
       </c>
       <c r="I189" s="3" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>716</v>
+        <v>740</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>707</v>
       </c>
       <c r="B190" s="1">
         <v>0.18</v>
@@ -8528,10 +9071,10 @@
         <v>10</v>
       </c>
       <c r="E190" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F190" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G190" s="2">
         <v>16.600000000000001</v>
@@ -8540,12 +9083,12 @@
         <v>48.5</v>
       </c>
       <c r="I190" s="3" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>473</v>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>471</v>
       </c>
       <c r="B191" s="1">
         <v>0.16</v>
@@ -8557,10 +9100,10 @@
         <v>10</v>
       </c>
       <c r="E191" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F191" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G191" s="2">
         <v>40.200000000000003</v>
@@ -8569,12 +9112,12 @@
         <v>225</v>
       </c>
       <c r="I191" s="3" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>476</v>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>474</v>
       </c>
       <c r="B192" s="1">
         <v>0.186</v>
@@ -8586,10 +9129,10 @@
         <v>16</v>
       </c>
       <c r="E192" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F192" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G192" s="2">
         <v>0</v>
@@ -8598,12 +9141,12 @@
         <v>0.99</v>
       </c>
       <c r="I192" s="3" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>479</v>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>477</v>
       </c>
       <c r="B193" s="1">
         <v>0.15</v>
@@ -8615,10 +9158,10 @@
         <v>10</v>
       </c>
       <c r="E193" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F193" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G193" s="2">
         <v>2.04</v>
@@ -8627,12 +9170,12 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>482</v>
+        <v>655</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>480</v>
       </c>
       <c r="B194" s="1">
         <v>0.24</v>
@@ -8644,10 +9187,10 @@
         <v>10</v>
       </c>
       <c r="E194" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F194" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G194" s="2">
         <v>0.31</v>
@@ -8656,12 +9199,12 @@
         <v>0.95</v>
       </c>
       <c r="I194" s="3" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>485</v>
+        <v>656</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>483</v>
       </c>
       <c r="B195" s="1">
         <v>0.15</v>
@@ -8673,10 +9216,10 @@
         <v>10</v>
       </c>
       <c r="E195" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F195" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G195" s="2">
         <v>80</v>
@@ -8685,12 +9228,12 @@
         <v>200</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>488</v>
+        <v>657</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>486</v>
       </c>
       <c r="B196" s="1">
         <v>0.12</v>
@@ -8702,10 +9245,10 @@
         <v>10</v>
       </c>
       <c r="E196" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F196" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G196" s="2">
         <v>0.77</v>
@@ -8714,12 +9257,12 @@
         <v>1.68</v>
       </c>
       <c r="I196" s="3" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>491</v>
+        <v>658</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>489</v>
       </c>
       <c r="B197" s="1">
         <v>0.15</v>
@@ -8731,10 +9274,10 @@
         <v>10</v>
       </c>
       <c r="E197" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F197" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G197" s="2">
         <v>4.5</v>
@@ -8743,12 +9286,12 @@
         <v>12.1</v>
       </c>
       <c r="I197" s="3" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>494</v>
+        <v>659</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>492</v>
       </c>
       <c r="B198" s="1">
         <v>0.192</v>
@@ -8760,10 +9303,10 @@
         <v>12</v>
       </c>
       <c r="E198" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F198" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G198" s="2">
         <v>13</v>
@@ -8772,12 +9315,12 @@
         <v>39</v>
       </c>
       <c r="I198" s="3" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>496</v>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>494</v>
       </c>
       <c r="B199" s="1">
         <v>0.35</v>
@@ -8789,10 +9332,10 @@
         <v>10</v>
       </c>
       <c r="E199" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F199" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G199" s="2">
         <v>193</v>
@@ -8801,12 +9344,12 @@
         <v>740</v>
       </c>
       <c r="I199" s="3" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>496</v>
+        <v>661</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>494</v>
       </c>
       <c r="B200" s="1">
         <v>0.2</v>
@@ -8818,10 +9361,10 @@
         <v>10</v>
       </c>
       <c r="E200" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F200" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G200" s="2">
         <v>193</v>
@@ -8830,11 +9373,11 @@
         <v>740</v>
       </c>
       <c r="I200" s="3" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
         <v>215</v>
       </c>
       <c r="B201" s="1">
@@ -8859,12 +9402,12 @@
         <v>308</v>
       </c>
       <c r="I201" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>691</v>
+        <v>596</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>682</v>
       </c>
       <c r="B202" s="1">
         <v>0.12</v>
@@ -8888,12 +9431,12 @@
         <v>5.2</v>
       </c>
       <c r="I202" s="3" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>505</v>
+        <v>551</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>503</v>
       </c>
       <c r="B203" s="1">
         <v>0.2</v>
@@ -8905,10 +9448,10 @@
         <v>16</v>
       </c>
       <c r="E203" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F203" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G203" s="2">
         <v>3.5</v>
@@ -8917,12 +9460,12 @@
         <v>77</v>
       </c>
       <c r="I203" s="3" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>508</v>
+        <v>568</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>506</v>
       </c>
       <c r="B204" s="1">
         <v>0.23</v>
@@ -8931,27 +9474,30 @@
         <v>0.115</v>
       </c>
       <c r="D204" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E204" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F204" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G204" s="2">
         <v>0</v>
       </c>
       <c r="H204" s="2">
-        <v>2.99</v>
+        <v>0.99</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>511</v>
+        <v>550</v>
+      </c>
+      <c r="J204" s="6" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>509</v>
       </c>
       <c r="B205" s="1">
         <v>0.153</v>
@@ -8960,13 +9506,13 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="D205" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E205" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F205" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G205" s="2">
         <v>0</v>
@@ -8975,11 +9521,14 @@
         <v>0.79</v>
       </c>
       <c r="I205" s="3" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
+        <v>664</v>
+      </c>
+      <c r="J205" s="6" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="s">
         <v>97</v>
       </c>
       <c r="B206" s="1">
@@ -9004,11 +9553,11 @@
         <v>1.75</v>
       </c>
       <c r="I206" s="3" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
         <v>376</v>
       </c>
       <c r="B207" s="1">
@@ -9033,11 +9582,11 @@
         <v>60</v>
       </c>
       <c r="I207" s="3" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B208" s="1">
@@ -9062,12 +9611,12 @@
         <v>7.6</v>
       </c>
       <c r="I208" s="3" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>520</v>
+        <v>552</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="s">
+        <v>518</v>
       </c>
       <c r="B209" s="1">
         <v>0.11</v>
@@ -9079,10 +9628,10 @@
         <v>10</v>
       </c>
       <c r="E209" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F209" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G209" s="2">
         <v>0.27</v>
@@ -9091,12 +9640,12 @@
         <v>4.2</v>
       </c>
       <c r="I209" s="3" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>522</v>
+        <v>667</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>520</v>
       </c>
       <c r="B210" s="1">
         <v>0.3</v>
@@ -9108,24 +9657,27 @@
         <v>16</v>
       </c>
       <c r="E210" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F210" t="s">
-        <v>348</v>
+        <v>914</v>
       </c>
       <c r="G210" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H210" s="2">
-        <v>350</v>
+        <v>6.99</v>
       </c>
       <c r="I210" s="3" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>524</v>
+        <v>880</v>
+      </c>
+      <c r="J210" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="s">
+        <v>522</v>
       </c>
       <c r="B211" s="1">
         <v>0.3</v>
@@ -9137,23 +9689,26 @@
         <v>16</v>
       </c>
       <c r="E211" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F211" t="s">
-        <v>351</v>
+        <v>915</v>
       </c>
       <c r="G211" s="2">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="H211" s="2">
-        <v>1600</v>
+        <v>6.99</v>
       </c>
       <c r="I211" s="3" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
+        <v>880</v>
+      </c>
+      <c r="J211" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B212" s="1">
@@ -9178,12 +9733,12 @@
         <v>200</v>
       </c>
       <c r="I212" s="3" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>715</v>
+        <v>562</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>706</v>
       </c>
       <c r="B213" s="1">
         <v>0.221</v>
@@ -9195,10 +9750,10 @@
         <v>7</v>
       </c>
       <c r="E213" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="F213" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="G213" s="2">
         <v>12</v>
@@ -9207,12 +9762,12 @@
         <v>20</v>
       </c>
       <c r="I213" s="3" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>528</v>
+        <v>816</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>526</v>
       </c>
       <c r="B214" s="1">
         <v>0.3</v>
@@ -9224,10 +9779,10 @@
         <v>10</v>
       </c>
       <c r="E214" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F214" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G214" s="2">
         <v>0</v>
@@ -9236,12 +9791,12 @@
         <v>150</v>
       </c>
       <c r="I214" s="3" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>531</v>
+        <v>669</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
+        <v>529</v>
       </c>
       <c r="B215" s="1">
         <v>0.3</v>
@@ -9253,24 +9808,27 @@
         <v>10</v>
       </c>
       <c r="E215" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F215" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G215" s="2">
         <v>0</v>
       </c>
       <c r="H215" s="2">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I215" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>534</v>
+        <v>817</v>
+      </c>
+      <c r="J215" s="6" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>532</v>
       </c>
       <c r="B216" s="1">
         <v>0.2</v>
@@ -9282,10 +9840,10 @@
         <v>12</v>
       </c>
       <c r="E216" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F216" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G216" s="2">
         <v>197</v>
@@ -9294,12 +9852,12 @@
         <v>771</v>
       </c>
       <c r="I216" s="3" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>537</v>
+        <v>670</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
+        <v>535</v>
       </c>
       <c r="B217" s="1">
         <v>0.25</v>
@@ -9311,10 +9869,10 @@
         <v>12</v>
       </c>
       <c r="E217" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F217" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G217" s="2">
         <v>20</v>
@@ -9323,12 +9881,12 @@
         <v>100</v>
       </c>
       <c r="I217" s="3" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>540</v>
+        <v>671</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>538</v>
       </c>
       <c r="B218" s="1">
         <v>0.3</v>
@@ -9340,10 +9898,10 @@
         <v>10</v>
       </c>
       <c r="E218" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F218" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G218" s="2">
         <v>19.899999999999999</v>
@@ -9352,11 +9910,11 @@
         <v>79.3</v>
       </c>
       <c r="I218" s="3" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A219" s="4" t="s">
         <v>257</v>
       </c>
       <c r="B219" s="1">
@@ -9381,190 +9939,760 @@
         <v>285</v>
       </c>
       <c r="I219" s="3" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G220"/>
-      <c r="H220"/>
-      <c r="I220"/>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G221"/>
-      <c r="H221"/>
-      <c r="I221"/>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G222"/>
-      <c r="H222"/>
-      <c r="I222"/>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G223"/>
-      <c r="H223"/>
-      <c r="I223"/>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G224"/>
-      <c r="H224"/>
-      <c r="I224"/>
-    </row>
-    <row r="225" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G225"/>
-      <c r="H225"/>
-      <c r="I225"/>
-    </row>
-    <row r="226" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G226"/>
-      <c r="H226"/>
-      <c r="I226"/>
-    </row>
-    <row r="227" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G227"/>
-      <c r="H227"/>
-      <c r="I227"/>
-    </row>
-    <row r="228" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G228"/>
-      <c r="H228"/>
-      <c r="I228"/>
-    </row>
-    <row r="229" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G229"/>
-      <c r="H229"/>
-      <c r="I229"/>
-    </row>
-    <row r="230" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G230"/>
-      <c r="H230"/>
-      <c r="I230"/>
-    </row>
-    <row r="231" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G231"/>
-      <c r="H231"/>
-      <c r="I231"/>
-    </row>
-    <row r="232" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G232"/>
-      <c r="H232"/>
-      <c r="I232"/>
-    </row>
-    <row r="233" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G233"/>
-      <c r="H233"/>
-      <c r="I233"/>
-    </row>
-    <row r="234" spans="7:9" x14ac:dyDescent="0.25">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="B220" s="5">
+        <v>5.5E-2</v>
+      </c>
+      <c r="C220" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E220" t="s">
+        <v>852</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="G220" s="2">
+        <v>4</v>
+      </c>
+      <c r="H220" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="I220" s="3" t="str">
+        <f>_xlfn.CONCAT(G220, " - ", H220)</f>
+        <v>4 - 5,5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A221" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="B221" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="C221" s="5">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E221" t="s">
+        <v>853</v>
+      </c>
+      <c r="F221" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="G221" s="2">
+        <v>4</v>
+      </c>
+      <c r="H221" s="2">
+        <v>12</v>
+      </c>
+      <c r="I221" s="3" t="str">
+        <f t="shared" ref="I221:I242" si="0">_xlfn.CONCAT(G221, " - ", H221)</f>
+        <v>4 - 12</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="B222" s="5">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="C222" s="5">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E222" t="s">
+        <v>854</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="G222" s="2">
+        <v>1.48</v>
+      </c>
+      <c r="H222">
+        <v>7.7</v>
+      </c>
+      <c r="I222" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1,48 - 7,7</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="B223" s="5">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="C223" s="5">
+        <v>6.3E-2</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E223" t="s">
+        <v>855</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="G223" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="H223" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="I223" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>0,74 - 5,5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="B224" s="5">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="C224" s="5">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E224" t="s">
+        <v>856</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="G224" s="2">
+        <v>0.37</v>
+      </c>
+      <c r="H224" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I224" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>0,37 - 1,5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="B225" s="5">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="C225" s="5">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E225" t="s">
+        <v>857</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="G225" s="2">
+        <v>0</v>
+      </c>
+      <c r="H225" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I225" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>0 - 0,55</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="B226" s="5">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="C226" s="5">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E226" t="s">
+        <v>858</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="G226" s="2">
+        <v>0</v>
+      </c>
+      <c r="H226" s="2">
+        <v>200</v>
+      </c>
+      <c r="I226" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>0 - 200</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="B227" s="5">
+        <v>0.13439999999999999</v>
+      </c>
+      <c r="C227" s="5">
+        <v>6.7199999999999996E-2</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E227" t="s">
+        <v>872</v>
+      </c>
+      <c r="F227" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="G227" s="2">
+        <v>130</v>
+      </c>
+      <c r="H227" s="2">
+        <v>550</v>
+      </c>
+      <c r="I227" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>130 - 550</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="B228" s="5">
+        <v>0.14979999999999999</v>
+      </c>
+      <c r="C228" s="5">
+        <v>7.4899999999999994E-2</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E228" t="s">
+        <v>859</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="G228" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="H228" s="2">
+        <v>11.2</v>
+      </c>
+      <c r="I228" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>0,9 - 11,2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="B229" s="5">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="C229" s="5">
+        <v>0.108</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E229" t="s">
+        <v>860</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="G229" s="2">
+        <v>0.59</v>
+      </c>
+      <c r="H229" s="2">
+        <v>2.37</v>
+      </c>
+      <c r="I229" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>0,59 - 2,37</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="B230" s="5">
+        <v>0.627</v>
+      </c>
+      <c r="C230" s="5">
+        <v>0.20069999999999999</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E230" t="s">
+        <v>861</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="G230" s="2">
+        <v>1.57</v>
+      </c>
+      <c r="H230" s="2">
+        <v>16.88</v>
+      </c>
+      <c r="I230" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1,57 - 16,88</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="B231" s="5">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="C231" s="5">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E231" t="s">
+        <v>862</v>
+      </c>
+      <c r="F231" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="G231" s="2">
+        <v>13</v>
+      </c>
+      <c r="H231" s="2">
+        <v>18</v>
+      </c>
+      <c r="I231" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>13 - 18</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="B232" s="5">
+        <v>7.5200000000000003E-2</v>
+      </c>
+      <c r="C232" s="5">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E232" t="s">
+        <v>863</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="G232" s="2">
+        <v>30.6</v>
+      </c>
+      <c r="H232" s="2">
+        <v>36.6</v>
+      </c>
+      <c r="I232" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>30,6 - 36,6</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="B233" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="C233" s="5">
+        <v>5.74E-2</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E233" t="s">
+        <v>864</v>
+      </c>
+      <c r="F233" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="G233" s="2">
+        <v>0</v>
+      </c>
+      <c r="H233" s="2">
+        <v>3</v>
+      </c>
+      <c r="I233" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>0 - 3</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="B234" s="5">
+        <v>0.2979</v>
+      </c>
+      <c r="C234" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E234" t="s">
+        <v>865</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>843</v>
+      </c>
       <c r="G234"/>
       <c r="H234"/>
-      <c r="I234"/>
-    </row>
-    <row r="235" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G235"/>
-      <c r="H235"/>
-      <c r="I235"/>
-    </row>
-    <row r="236" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G236"/>
-      <c r="H236"/>
-      <c r="I236"/>
-    </row>
-    <row r="237" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G237"/>
-      <c r="H237"/>
-      <c r="I237"/>
-    </row>
-    <row r="238" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G238"/>
-      <c r="H238"/>
-      <c r="I238"/>
-    </row>
-    <row r="239" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G239"/>
-      <c r="H239"/>
-      <c r="I239"/>
-    </row>
-    <row r="240" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G240"/>
-      <c r="H240"/>
-      <c r="I240"/>
-    </row>
-    <row r="241" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G241"/>
-      <c r="H241"/>
-      <c r="I241"/>
-    </row>
-    <row r="242" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G242"/>
-      <c r="H242"/>
-      <c r="I242"/>
-    </row>
-    <row r="243" spans="7:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="B235" s="5">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="C235" s="5">
+        <v>2.3E-2</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E235" t="s">
+        <v>866</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="G235" s="2">
+        <v>36</v>
+      </c>
+      <c r="H235" s="2">
+        <v>54</v>
+      </c>
+      <c r="I235" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>36 - 54</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="B236" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="C236" s="5">
+        <v>1.6E-2</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E236" t="s">
+        <v>867</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="G236" s="2">
+        <v>80</v>
+      </c>
+      <c r="H236" s="2">
+        <v>98</v>
+      </c>
+      <c r="I236" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>80 - 98</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="B237" s="5">
+        <v>5.5E-2</v>
+      </c>
+      <c r="C237" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E237" t="s">
+        <v>868</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="G237" s="2">
+        <v>26.8</v>
+      </c>
+      <c r="H237" s="2">
+        <v>32.9</v>
+      </c>
+      <c r="I237" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>26,8 - 32,9</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="B238" s="5">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="C238" s="5">
+        <v>1.6E-2</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E238" t="s">
+        <v>869</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="G238" s="2">
+        <v>30</v>
+      </c>
+      <c r="H238" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="I238" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>30 - 36,5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="B239" s="5">
+        <v>4.5600000000000002E-2</v>
+      </c>
+      <c r="C239" s="5">
+        <v>1.17E-2</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E239" t="s">
+        <v>870</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="G239" s="2">
+        <v>11</v>
+      </c>
+      <c r="H239" s="2">
+        <v>16</v>
+      </c>
+      <c r="I239" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>11 - 16</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="B240" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="C240" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E240" t="s">
+        <v>871</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="G240" s="2">
+        <v>130</v>
+      </c>
+      <c r="H240" s="2">
+        <v>550</v>
+      </c>
+      <c r="I240" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>130 - 550</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="B241" s="5">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="C241" s="5">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E241" t="s">
+        <v>873</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="G241" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="H241" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="I241" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>6,8 - 12,6</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="B242" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="C242" s="5">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E242" t="s">
+        <v>874</v>
+      </c>
+      <c r="F242" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="G242" s="2">
+        <v>0</v>
+      </c>
+      <c r="H242" s="2">
+        <v>5.69</v>
+      </c>
+      <c r="I242" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>0 - 5,69</v>
+      </c>
+      <c r="J242" s="6" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G243"/>
       <c r="H243"/>
       <c r="I243"/>
     </row>
-    <row r="244" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G244"/>
       <c r="H244"/>
       <c r="I244"/>
     </row>
-    <row r="245" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G245"/>
       <c r="H245"/>
       <c r="I245"/>
     </row>
-    <row r="246" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G246"/>
       <c r="H246"/>
       <c r="I246"/>
     </row>
-    <row r="247" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G247"/>
       <c r="H247"/>
       <c r="I247"/>
     </row>
-    <row r="248" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G248"/>
       <c r="H248"/>
       <c r="I248"/>
     </row>
-    <row r="249" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G249"/>
       <c r="H249"/>
       <c r="I249"/>
     </row>
-    <row r="250" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G250"/>
       <c r="H250"/>
       <c r="I250"/>
     </row>
-    <row r="251" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G251"/>
       <c r="H251"/>
       <c r="I251"/>
     </row>
-    <row r="252" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G252"/>
       <c r="H252"/>
       <c r="I252"/>
     </row>
-    <row r="253" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G253"/>
       <c r="H253"/>
       <c r="I253"/>
     </row>
-    <row r="254" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G254"/>
       <c r="H254"/>
       <c r="I254"/>
     </row>
-    <row r="255" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G255"/>
       <c r="H255"/>
       <c r="I255"/>
     </row>
-    <row r="256" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G256"/>
       <c r="H256"/>
       <c r="I256"/>
@@ -9680,14 +10808,14 @@
       <c r="I278"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J219" xr:uid="{F9E839D1-D9BB-491F-96EB-30E6182BBB70}"/>
+  <autoFilter ref="A1:I219" xr:uid="{F9E839D1-D9BB-491F-96EB-30E6182BBB70}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4341AA7A-BE9E-402B-8B8E-1C6E7BF75419}">
-  <dimension ref="A1:A78"/>
+  <dimension ref="A1:A89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -9695,17 +10823,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -9715,37 +10843,37 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -9755,332 +10883,387 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>774</v>
+        <v>826</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>775</v>
+        <v>827</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>776</v>
+        <v>828</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>793</v>
+        <v>766</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>794</v>
+        <v>768</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>795</v>
+        <v>769</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>796</v>
+        <v>770</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>797</v>
+        <v>771</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>798</v>
+        <v>772</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>799</v>
+        <v>773</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>800</v>
+        <v>774</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>801</v>
+        <v>775</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>802</v>
+        <v>777</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>789</v>
+        <v>778</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>803</v>
+        <v>779</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>804</v>
+        <v>793</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>808</v>
+        <v>797</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>809</v>
+        <v>798</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>810</v>
+        <v>781</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>285</v>
+        <v>801</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>150</v>
+        <v>802</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>819</v>
+        <v>803</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>820</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>792</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>814</v>
+        <v>782</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>815</v>
+        <v>804</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>51</v>
+        <v>783</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>88</v>
+        <v>805</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>816</v>
+        <v>806</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>825</v>
       </c>
     </row>
   </sheetData>

--- a/Base de Dados.xlsx
+++ b/Base de Dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Estudos\Desdobramento - Sigma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBFE60D-5841-4C86-ADAA-DF14842F9BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C32138-2ED3-4766-AA47-DB79382415D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{052EBD17-0308-4E6D-95A6-CA02714B48B2}"/>
   </bookViews>
@@ -10596,7 +10596,7 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="B242" s="5">
         <v>0.05</v>

--- a/Base de Dados.xlsx
+++ b/Base de Dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Estudos\Desdobramento - Sigma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C32138-2ED3-4766-AA47-DB79382415D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F688004-7524-4CD3-A7AB-AC87897FC74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{052EBD17-0308-4E6D-95A6-CA02714B48B2}"/>
   </bookViews>
@@ -1678,9 +1678,6 @@
     <t>HBsAg</t>
   </si>
   <si>
-    <t>HbA1c</t>
-  </si>
-  <si>
     <t>IR</t>
   </si>
   <si>
@@ -2789,6 +2786,9 @@
   </si>
   <si>
     <t>5,7 - 6,4</t>
+  </si>
+  <si>
+    <t>HbA1c (D10)</t>
   </si>
 </sst>
 </file>
@@ -3704,10 +3704,10 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -3728,10 +3728,10 @@
         <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -3760,7 +3760,7 @@
         <v>26.8</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -3789,12 +3789,12 @@
         <v>75</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B4" s="1">
         <v>0.15</v>
@@ -3818,7 +3818,7 @@
         <v>7</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3847,7 +3847,7 @@
         <v>46</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -3876,7 +3876,7 @@
         <v>0.99</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -3905,12 +3905,12 @@
         <v>0.3</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B8" s="1">
         <v>6.0999999999999999E-2</v>
@@ -3934,7 +3934,7 @@
         <v>5.2</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -3963,7 +3963,7 @@
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -3992,12 +3992,12 @@
         <v>39.200000000000003</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B11" s="1">
         <v>0.18</v>
@@ -4021,12 +4021,12 @@
         <v>200</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B12" s="1">
         <v>0.2</v>
@@ -4041,7 +4041,7 @@
         <v>29</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -4070,12 +4070,12 @@
         <v>155</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B14" s="1">
         <v>0.2</v>
@@ -4090,7 +4090,7 @@
         <v>33</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -4119,7 +4119,7 @@
         <v>5.8</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -4148,7 +4148,7 @@
         <v>2.71</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -4177,12 +4177,12 @@
         <v>193</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B18" s="1">
         <v>0.19400000000000001</v>
@@ -4194,10 +4194,10 @@
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F18" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G18" s="2">
         <v>15</v>
@@ -4206,7 +4206,7 @@
         <v>99</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -4235,7 +4235,7 @@
         <v>54</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -4264,12 +4264,12 @@
         <v>1.07</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B21" s="1">
         <v>0.3</v>
@@ -4293,12 +4293,12 @@
         <v>100</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B22" s="1">
         <v>0.3</v>
@@ -4322,7 +4322,7 @@
         <v>9.99</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -4351,7 +4351,7 @@
         <v>0.99</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -4380,7 +4380,7 @@
         <v>60</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -4409,10 +4409,10 @@
         <v>0.89</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -4441,7 +4441,7 @@
         <v>60</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -4470,7 +4470,7 @@
         <v>60</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -4499,7 +4499,7 @@
         <v>9.99</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -4528,10 +4528,10 @@
         <v>0.89</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -4560,7 +4560,7 @@
         <v>28</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -4589,12 +4589,12 @@
         <v>24.9</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B32" s="1">
         <v>0.3</v>
@@ -4618,12 +4618,12 @@
         <v>114</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B33" s="1">
         <v>0.22</v>
@@ -4647,7 +4647,7 @@
         <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -4676,7 +4676,7 @@
         <v>304</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -4705,7 +4705,7 @@
         <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -4731,10 +4731,10 @@
         <v>6.99</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J36" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -4760,10 +4760,10 @@
         <v>6.99</v>
       </c>
       <c r="I37" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J37" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -4786,7 +4786,7 @@
         <v>100</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -4809,7 +4809,7 @@
         <v>103</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -4835,10 +4835,10 @@
         <v>6.99</v>
       </c>
       <c r="I40" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J40" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -4864,10 +4864,10 @@
         <v>6.99</v>
       </c>
       <c r="I41" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J41" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -4896,7 +4896,7 @@
         <v>77</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -4925,7 +4925,7 @@
         <v>0.78</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -4945,7 +4945,7 @@
         <v>115</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -4965,7 +4965,7 @@
         <v>117</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -4994,12 +4994,12 @@
         <v>5</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B47" s="1">
         <v>0.19400000000000001</v>
@@ -5011,10 +5011,10 @@
         <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F47" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
@@ -5023,7 +5023,7 @@
         <v>650</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -5052,7 +5052,7 @@
         <v>15</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -5081,7 +5081,7 @@
         <v>10</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -5110,12 +5110,12 @@
         <v>0.9</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B51" s="1">
         <v>0.155</v>
@@ -5139,7 +5139,7 @@
         <v>39</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -5168,7 +5168,7 @@
         <v>35</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -5197,7 +5197,7 @@
         <v>28.5</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -5226,7 +5226,7 @@
         <v>34</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -5255,7 +5255,7 @@
         <v>25</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -5284,7 +5284,7 @@
         <v>6.9</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -5313,12 +5313,12 @@
         <v>225</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B58" s="1">
         <v>0.15</v>
@@ -5342,7 +5342,7 @@
         <v>9.6</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -5371,7 +5371,7 @@
         <v>1.4</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -5400,7 +5400,7 @@
         <v>14.3</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -5429,7 +5429,7 @@
         <v>50</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -5458,7 +5458,7 @@
         <v>130</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -5487,10 +5487,10 @@
         <v>13.99</v>
       </c>
       <c r="I63" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="J63" s="6" t="s">
         <v>882</v>
-      </c>
-      <c r="J63" s="6" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -5519,10 +5519,10 @@
         <v>9.99</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -5551,10 +5551,10 @@
         <v>9.99</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -5583,10 +5583,10 @@
         <v>8.99</v>
       </c>
       <c r="I66" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="J66" s="6" t="s">
         <v>885</v>
-      </c>
-      <c r="J66" s="6" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -5615,10 +5615,10 @@
         <v>0.89</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -5647,10 +5647,10 @@
         <v>6.99</v>
       </c>
       <c r="I68" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J68" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J68" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -5679,7 +5679,7 @@
         <v>3.8</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -5708,7 +5708,7 @@
         <v>60</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -5737,7 +5737,7 @@
         <v>0.99</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -5766,12 +5766,12 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B73" s="1">
         <v>0.25</v>
@@ -5783,10 +5783,10 @@
         <v>7</v>
       </c>
       <c r="E73" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F73" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G73" s="2">
         <v>100</v>
@@ -5795,12 +5795,12 @@
         <v>300</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B74" s="1">
         <v>0.13</v>
@@ -5824,12 +5824,12 @@
         <v>107</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B75" s="1">
         <v>0.1</v>
@@ -5841,10 +5841,10 @@
         <v>7</v>
       </c>
       <c r="E75" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F75" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G75" s="2">
         <v>110</v>
@@ -5853,7 +5853,7 @@
         <v>250</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -5882,10 +5882,10 @@
         <v>0.49</v>
       </c>
       <c r="I76" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="J76" s="6" t="s">
         <v>888</v>
-      </c>
-      <c r="J76" s="6" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -5914,10 +5914,10 @@
         <v>0.69</v>
       </c>
       <c r="I77" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="J77" s="6" t="s">
         <v>890</v>
-      </c>
-      <c r="J77" s="6" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -5946,7 +5946,7 @@
         <v>41</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -5975,7 +5975,7 @@
         <v>360</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -6004,7 +6004,7 @@
         <v>150</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -6033,7 +6033,7 @@
         <v>170</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -6062,7 +6062,7 @@
         <v>36</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -6091,7 +6091,7 @@
         <v>22.45</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -6120,12 +6120,12 @@
         <v>20.29</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B85" s="1">
         <v>0.2</v>
@@ -6149,7 +6149,7 @@
         <v>1.17</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -6178,12 +6178,12 @@
         <v>120</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B87" s="1">
         <v>0.3</v>
@@ -6195,10 +6195,10 @@
         <v>7</v>
       </c>
       <c r="E87" t="s">
+        <v>723</v>
+      </c>
+      <c r="F87" t="s">
         <v>724</v>
-      </c>
-      <c r="F87" t="s">
-        <v>725</v>
       </c>
       <c r="G87" s="2">
         <v>39</v>
@@ -6207,7 +6207,7 @@
         <v>259</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -6236,10 +6236,10 @@
         <v>9.99</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J88" s="8" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -6268,7 +6268,7 @@
         <v>200</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -6297,10 +6297,10 @@
         <v>0.69</v>
       </c>
       <c r="I90" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="J90" s="6" t="s">
         <v>890</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -6329,10 +6329,10 @@
         <v>0.59</v>
       </c>
       <c r="I91" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="J91" s="6" t="s">
         <v>893</v>
-      </c>
-      <c r="J91" s="6" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -6361,7 +6361,7 @@
         <v>138</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -6390,7 +6390,7 @@
         <v>12</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -6410,7 +6410,7 @@
         <v>239</v>
       </c>
       <c r="F94" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
@@ -6419,15 +6419,15 @@
         <v>6.99</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B95" s="1">
         <v>0.2</v>
@@ -6451,7 +6451,7 @@
         <v>4.5</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -6480,7 +6480,7 @@
         <v>500</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6509,12 +6509,12 @@
         <v>1.2</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B98" s="1">
         <v>0.3</v>
@@ -6538,7 +6538,7 @@
         <v>345</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -6567,12 +6567,12 @@
         <v>199</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B100" s="1">
         <v>0.3</v>
@@ -6584,10 +6584,10 @@
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="F100" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G100" s="2">
         <v>40</v>
@@ -6596,12 +6596,12 @@
         <v>150</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B101" s="1">
         <v>0.13</v>
@@ -6625,7 +6625,7 @@
         <v>99</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -6654,7 +6654,7 @@
         <v>134.80000000000001</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -6674,7 +6674,7 @@
         <v>263</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -6703,7 +6703,7 @@
         <v>115</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -6732,7 +6732,7 @@
         <v>129</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -6761,7 +6761,7 @@
         <v>3</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -6787,10 +6787,10 @@
         <v>6.99</v>
       </c>
       <c r="I107" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J107" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J107" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -6816,15 +6816,15 @@
         <v>6.99</v>
       </c>
       <c r="I108" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J108" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J108" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B109" s="1">
         <v>0.12</v>
@@ -6833,7 +6833,7 @@
         <v>0.06</v>
       </c>
       <c r="D109" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E109" t="s">
         <v>276</v>
@@ -6848,7 +6848,7 @@
         <v>99</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -6877,12 +6877,12 @@
         <v>60</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B111" s="1">
         <v>0.15</v>
@@ -6906,7 +6906,7 @@
         <v>500</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -6935,7 +6935,7 @@
         <v>0.89</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -6964,7 +6964,7 @@
         <v>200</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -6978,7 +6978,7 @@
         <v>286</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -6998,7 +6998,7 @@
         <v>289</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -7018,7 +7018,7 @@
         <v>289</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -7038,7 +7038,7 @@
         <v>291</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -7058,7 +7058,7 @@
         <v>293</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -7078,12 +7078,12 @@
         <v>295</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>546</v>
+        <v>916</v>
       </c>
       <c r="B120" s="1">
         <v>0.05</v>
@@ -7107,7 +7107,7 @@
         <v>5.6</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -7136,7 +7136,7 @@
         <v>0.99</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -7165,7 +7165,7 @@
         <v>0.9</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -7194,7 +7194,7 @@
         <v>60</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -7214,7 +7214,7 @@
         <v>309</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -7234,7 +7234,7 @@
         <v>312</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -7263,7 +7263,7 @@
         <v>0.9</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -7292,7 +7292,7 @@
         <v>0.9</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -7321,7 +7321,7 @@
         <v>0.99</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -7350,7 +7350,7 @@
         <v>5</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -7373,7 +7373,7 @@
         <v>326</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -7402,7 +7402,7 @@
         <v>350</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -7422,7 +7422,7 @@
         <v>332</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -7442,7 +7442,7 @@
         <v>334</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -7462,7 +7462,7 @@
         <v>336</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -7491,7 +7491,7 @@
         <v>6.8</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -7520,7 +7520,7 @@
         <v>1600</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -7546,7 +7546,7 @@
         <v>1011</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -7572,7 +7572,7 @@
         <v>786</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -7598,7 +7598,7 @@
         <v>85</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -7624,7 +7624,7 @@
         <v>201</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -7653,7 +7653,7 @@
         <v>300</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -7682,7 +7682,7 @@
         <v>24.9</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -7708,10 +7708,10 @@
         <v>6.99</v>
       </c>
       <c r="I143" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J143" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J143" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -7731,7 +7731,7 @@
         <v>328</v>
       </c>
       <c r="F144" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G144" s="2">
         <v>170</v>
@@ -7740,7 +7740,7 @@
         <v>370</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -7769,7 +7769,7 @@
         <v>22.4</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -7795,10 +7795,10 @@
         <v>6.99</v>
       </c>
       <c r="I146" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J146" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J146" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -7818,7 +7818,7 @@
         <v>330</v>
       </c>
       <c r="F147" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G147" s="2">
         <v>90</v>
@@ -7827,7 +7827,7 @@
         <v>210</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -7856,12 +7856,12 @@
         <v>27</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B149" s="1">
         <v>0.25</v>
@@ -7885,7 +7885,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -7914,7 +7914,7 @@
         <v>40</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -7943,7 +7943,7 @@
         <v>8.6</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -7972,12 +7972,12 @@
         <v>152</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B153" s="1">
         <v>0.3</v>
@@ -7989,10 +7989,10 @@
         <v>7</v>
       </c>
       <c r="E153" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F153" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G153" s="2">
         <v>4.0999999999999996</v>
@@ -8001,7 +8001,7 @@
         <v>13.8</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -8030,12 +8030,12 @@
         <v>1.2</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B155" s="1">
         <v>0.1</v>
@@ -8059,12 +8059,12 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B156" s="1">
         <v>0.1</v>
@@ -8076,10 +8076,10 @@
         <v>7</v>
       </c>
       <c r="E156" t="s">
+        <v>732</v>
+      </c>
+      <c r="F156" t="s">
         <v>733</v>
-      </c>
-      <c r="F156" t="s">
-        <v>734</v>
       </c>
       <c r="G156" s="2">
         <v>17</v>
@@ -8088,7 +8088,7 @@
         <v>164</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -8117,7 +8117,7 @@
         <v>2.5</v>
       </c>
       <c r="I157" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -8143,10 +8143,10 @@
         <v>3.49</v>
       </c>
       <c r="I158" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="J158" s="6" t="s">
         <v>901</v>
-      </c>
-      <c r="J158" s="6" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -8175,7 +8175,7 @@
         <v>9.99</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -8204,7 +8204,7 @@
         <v>9.99</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -8233,7 +8233,7 @@
         <v>46</v>
       </c>
       <c r="I161" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -8262,7 +8262,7 @@
         <v>74.099999999999994</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -8291,10 +8291,10 @@
         <v>1.99</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="J163" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -8323,10 +8323,10 @@
         <v>0.89</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J164" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -8355,7 +8355,7 @@
         <v>25</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -8384,12 +8384,12 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B167" s="1">
         <v>0.25</v>
@@ -8413,12 +8413,12 @@
         <v>45</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B168" s="1">
         <v>0.12</v>
@@ -8442,7 +8442,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -8468,10 +8468,10 @@
         <v>1.99</v>
       </c>
       <c r="I169" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="J169" s="8" t="s">
         <v>907</v>
-      </c>
-      <c r="J169" s="8" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -8500,7 +8500,7 @@
         <v>40</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -8529,7 +8529,7 @@
         <v>15</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -8558,12 +8558,12 @@
         <v>17.7</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B173" s="1">
         <v>0.4</v>
@@ -8575,10 +8575,10 @@
         <v>7</v>
       </c>
       <c r="E173" t="s">
+        <v>735</v>
+      </c>
+      <c r="F173" t="s">
         <v>736</v>
-      </c>
-      <c r="F173" t="s">
-        <v>737</v>
       </c>
       <c r="G173" s="2">
         <v>1</v>
@@ -8587,7 +8587,7 @@
         <v>15</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -8616,12 +8616,12 @@
         <v>199</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B175" s="1">
         <v>0.05</v>
@@ -8645,7 +8645,7 @@
         <v>145</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -8674,7 +8674,7 @@
         <v>0.72</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -8703,7 +8703,7 @@
         <v>0.06</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -8726,7 +8726,7 @@
         <v>442</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -8752,10 +8752,10 @@
         <v>6.99</v>
       </c>
       <c r="I179" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J179" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J179" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -8781,10 +8781,10 @@
         <v>6.99</v>
       </c>
       <c r="I180" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J180" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J180" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -8813,7 +8813,7 @@
         <v>9.99</v>
       </c>
       <c r="I181" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -8842,10 +8842,10 @@
         <v>0.79</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J182" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -8874,10 +8874,10 @@
         <v>13.49</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="J183" s="6" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -8906,10 +8906,10 @@
         <v>0.89</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J184" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -8935,10 +8935,10 @@
         <v>6.99</v>
       </c>
       <c r="I185" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J185" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J185" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
@@ -8967,7 +8967,7 @@
         <v>568.9</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
@@ -8996,7 +8996,7 @@
         <v>76.7</v>
       </c>
       <c r="I187" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -9022,15 +9022,15 @@
         <v>6.99</v>
       </c>
       <c r="I188" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J188" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J188" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B189" s="1">
         <v>0.1</v>
@@ -9042,10 +9042,10 @@
         <v>7</v>
       </c>
       <c r="E189" t="s">
+        <v>737</v>
+      </c>
+      <c r="F189" t="s">
         <v>738</v>
-      </c>
-      <c r="F189" t="s">
-        <v>739</v>
       </c>
       <c r="G189" s="2">
         <v>18</v>
@@ -9054,12 +9054,12 @@
         <v>301</v>
       </c>
       <c r="I189" s="3" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B190" s="1">
         <v>0.18</v>
@@ -9083,7 +9083,7 @@
         <v>48.5</v>
       </c>
       <c r="I190" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
@@ -9112,7 +9112,7 @@
         <v>225</v>
       </c>
       <c r="I191" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
@@ -9141,7 +9141,7 @@
         <v>0.99</v>
       </c>
       <c r="I192" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
@@ -9170,7 +9170,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
@@ -9199,7 +9199,7 @@
         <v>0.95</v>
       </c>
       <c r="I194" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
@@ -9228,7 +9228,7 @@
         <v>200</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
@@ -9257,7 +9257,7 @@
         <v>1.68</v>
       </c>
       <c r="I196" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
@@ -9286,7 +9286,7 @@
         <v>12.1</v>
       </c>
       <c r="I197" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
@@ -9315,7 +9315,7 @@
         <v>39</v>
       </c>
       <c r="I198" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
@@ -9344,7 +9344,7 @@
         <v>740</v>
       </c>
       <c r="I199" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
@@ -9373,7 +9373,7 @@
         <v>740</v>
       </c>
       <c r="I200" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
@@ -9402,12 +9402,12 @@
         <v>308</v>
       </c>
       <c r="I201" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B202" s="1">
         <v>0.12</v>
@@ -9431,7 +9431,7 @@
         <v>5.2</v>
       </c>
       <c r="I202" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
@@ -9460,7 +9460,7 @@
         <v>77</v>
       </c>
       <c r="I203" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -9489,10 +9489,10 @@
         <v>0.99</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="J204" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -9521,10 +9521,10 @@
         <v>0.79</v>
       </c>
       <c r="I205" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J205" s="6" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
@@ -9553,7 +9553,7 @@
         <v>1.75</v>
       </c>
       <c r="I206" s="3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
@@ -9582,7 +9582,7 @@
         <v>60</v>
       </c>
       <c r="I207" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
@@ -9611,7 +9611,7 @@
         <v>7.6</v>
       </c>
       <c r="I208" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
@@ -9640,7 +9640,7 @@
         <v>4.2</v>
       </c>
       <c r="I209" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
@@ -9660,7 +9660,7 @@
         <v>521</v>
       </c>
       <c r="F210" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G210" s="2">
         <v>0</v>
@@ -9669,10 +9669,10 @@
         <v>6.99</v>
       </c>
       <c r="I210" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J210" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J210" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
@@ -9692,7 +9692,7 @@
         <v>523</v>
       </c>
       <c r="F211" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G211" s="2">
         <v>0</v>
@@ -9701,10 +9701,10 @@
         <v>6.99</v>
       </c>
       <c r="I211" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J211" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J211" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -9733,12 +9733,12 @@
         <v>200</v>
       </c>
       <c r="I212" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B213" s="1">
         <v>0.221</v>
@@ -9750,10 +9750,10 @@
         <v>7</v>
       </c>
       <c r="E213" t="s">
+        <v>740</v>
+      </c>
+      <c r="F213" t="s">
         <v>741</v>
-      </c>
-      <c r="F213" t="s">
-        <v>742</v>
       </c>
       <c r="G213" s="2">
         <v>12</v>
@@ -9762,7 +9762,7 @@
         <v>20</v>
       </c>
       <c r="I213" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -9791,7 +9791,7 @@
         <v>150</v>
       </c>
       <c r="I214" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
@@ -9820,10 +9820,10 @@
         <v>0.89</v>
       </c>
       <c r="I215" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J215" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
@@ -9852,7 +9852,7 @@
         <v>771</v>
       </c>
       <c r="I216" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -9881,7 +9881,7 @@
         <v>100</v>
       </c>
       <c r="I217" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -9910,7 +9910,7 @@
         <v>79.3</v>
       </c>
       <c r="I218" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -9939,12 +9939,12 @@
         <v>285</v>
       </c>
       <c r="I219" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B220" s="5">
         <v>5.5E-2</v>
@@ -9956,10 +9956,10 @@
         <v>311</v>
       </c>
       <c r="E220" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G220" s="2">
         <v>4</v>
@@ -9974,7 +9974,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B221" s="5">
         <v>0.12</v>
@@ -9986,10 +9986,10 @@
         <v>311</v>
       </c>
       <c r="E221" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G221" s="2">
         <v>4</v>
@@ -10004,7 +10004,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B222" s="5">
         <v>0.17499999999999999</v>
@@ -10016,10 +10016,10 @@
         <v>311</v>
       </c>
       <c r="E222" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G222" s="2">
         <v>1.48</v>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B223" s="5">
         <v>0.17599999999999999</v>
@@ -10046,10 +10046,10 @@
         <v>311</v>
       </c>
       <c r="E223" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G223" s="2">
         <v>0.74</v>
@@ -10064,7 +10064,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B224" s="5">
         <v>0.27900000000000003</v>
@@ -10076,10 +10076,10 @@
         <v>311</v>
       </c>
       <c r="E224" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G224" s="2">
         <v>0.37</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B225" s="5">
         <v>0.29699999999999999</v>
@@ -10106,10 +10106,10 @@
         <v>311</v>
       </c>
       <c r="E225" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G225" s="2">
         <v>0</v>
@@ -10124,7 +10124,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B226" s="5">
         <v>0.27300000000000002</v>
@@ -10136,10 +10136,10 @@
         <v>311</v>
       </c>
       <c r="E226" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G226" s="2">
         <v>0</v>
@@ -10154,7 +10154,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B227" s="5">
         <v>0.13439999999999999</v>
@@ -10166,10 +10166,10 @@
         <v>311</v>
       </c>
       <c r="E227" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G227" s="2">
         <v>130</v>
@@ -10184,7 +10184,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B228" s="5">
         <v>0.14979999999999999</v>
@@ -10196,10 +10196,10 @@
         <v>311</v>
       </c>
       <c r="E228" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G228" s="2">
         <v>0.9</v>
@@ -10214,7 +10214,7 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B229" s="5">
         <v>0.22800000000000001</v>
@@ -10226,10 +10226,10 @@
         <v>311</v>
       </c>
       <c r="E229" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G229" s="2">
         <v>0.59</v>
@@ -10244,7 +10244,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B230" s="5">
         <v>0.627</v>
@@ -10256,10 +10256,10 @@
         <v>311</v>
       </c>
       <c r="E230" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G230" s="2">
         <v>1.57</v>
@@ -10274,7 +10274,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B231" s="5">
         <v>5.8000000000000003E-2</v>
@@ -10286,10 +10286,10 @@
         <v>311</v>
       </c>
       <c r="E231" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G231" s="2">
         <v>13</v>
@@ -10304,7 +10304,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B232" s="5">
         <v>7.5200000000000003E-2</v>
@@ -10316,10 +10316,10 @@
         <v>311</v>
       </c>
       <c r="E232" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G232" s="2">
         <v>30.6</v>
@@ -10334,7 +10334,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B233" s="5">
         <v>0.15</v>
@@ -10346,10 +10346,10 @@
         <v>311</v>
       </c>
       <c r="E233" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G233" s="2">
         <v>0</v>
@@ -10364,7 +10364,7 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B234" s="5">
         <v>0.2979</v>
@@ -10376,17 +10376,17 @@
         <v>311</v>
       </c>
       <c r="E234" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G234"/>
       <c r="H234"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B235" s="5">
         <v>5.8000000000000003E-2</v>
@@ -10398,10 +10398,10 @@
         <v>311</v>
       </c>
       <c r="E235" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G235" s="2">
         <v>36</v>
@@ -10416,7 +10416,7 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B236" s="5">
         <v>0.06</v>
@@ -10428,10 +10428,10 @@
         <v>311</v>
       </c>
       <c r="E236" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G236" s="2">
         <v>80</v>
@@ -10446,7 +10446,7 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B237" s="5">
         <v>5.5E-2</v>
@@ -10458,10 +10458,10 @@
         <v>311</v>
       </c>
       <c r="E237" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G237" s="2">
         <v>26.8</v>
@@ -10476,7 +10476,7 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B238" s="5">
         <v>7.4999999999999997E-2</v>
@@ -10488,10 +10488,10 @@
         <v>311</v>
       </c>
       <c r="E238" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G238" s="2">
         <v>30</v>
@@ -10506,7 +10506,7 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B239" s="5">
         <v>4.5600000000000002E-2</v>
@@ -10518,10 +10518,10 @@
         <v>311</v>
       </c>
       <c r="E239" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G239" s="2">
         <v>11</v>
@@ -10536,7 +10536,7 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B240" s="5">
         <v>0.16</v>
@@ -10548,10 +10548,10 @@
         <v>311</v>
       </c>
       <c r="E240" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G240" s="2">
         <v>130</v>
@@ -10566,7 +10566,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B241" s="5">
         <v>8.7999999999999995E-2</v>
@@ -10578,10 +10578,10 @@
         <v>311</v>
       </c>
       <c r="E241" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="G241" s="2">
         <v>6.8</v>
@@ -10608,10 +10608,10 @@
         <v>311</v>
       </c>
       <c r="E242" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G242" s="2">
         <v>0</v>
@@ -10624,7 +10624,7 @@
         <v>0 - 5,69</v>
       </c>
       <c r="J242" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
@@ -10823,17 +10823,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -10843,37 +10843,37 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -10883,282 +10883,282 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
@@ -11173,12 +11173,12 @@
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
@@ -11188,27 +11188,27 @@
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
@@ -11223,47 +11223,47 @@
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
   </sheetData>

--- a/Base de Dados.xlsx
+++ b/Base de Dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Estudos\Desdobramento - Sigma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F688004-7524-4CD3-A7AB-AC87897FC74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2755A827-00FE-4D5A-8E10-2E4556B36960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{052EBD17-0308-4E6D-95A6-CA02714B48B2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{052EBD17-0308-4E6D-95A6-CA02714B48B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Base de Dados" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base de Dados'!$A$1:$I$219</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Equipamentos!$A$2:$A$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Equipamentos!$A$2:$A$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="915">
   <si>
     <t>Bias MÃ¡ximo</t>
   </si>
@@ -46,9 +46,6 @@
     <t>Material</t>
   </si>
   <si>
-    <t>Equipamento</t>
-  </si>
-  <si>
     <t>norm</t>
   </si>
   <si>
@@ -2326,9 +2323,6 @@
     <t>BIOQ_4_2_2</t>
   </si>
   <si>
-    <t>00294_Capillarys OCTA</t>
-  </si>
-  <si>
     <t>BN II _ 01</t>
   </si>
   <si>
@@ -2338,117 +2332,12 @@
     <t>Cappilarys _ 917</t>
   </si>
   <si>
-    <t>Cobas 3_2_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 1_1_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 1_2_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 1_3_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 1_4_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 2_1_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 2_2_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 2_3_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 3_1_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 3_2_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 3_3_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 3_3_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 4_1_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 4_2_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 6_1_1</t>
-  </si>
-  <si>
     <t>Immulite 2000 XPI _ 03</t>
   </si>
   <si>
     <t>Liaison XL _ 1 (203)</t>
   </si>
   <si>
-    <t>Cobas Imuno 1_1_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 1_2_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 1_3_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 1_4_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 2_1_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 2_2_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 2_3_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 3_1_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 3_2_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 4_1_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 4_2_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 4_3_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 4_3_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 4_4_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 4_4_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 6_1_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 6_2_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 6_2_2</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 6_3_1</t>
-  </si>
-  <si>
-    <t>Cobas Imuno 6_3_2</t>
-  </si>
-  <si>
     <t>Immulite 2000 XPI _ 04</t>
   </si>
   <si>
@@ -2515,15 +2404,6 @@
     <t>XN-10 - 4B - 55002</t>
   </si>
   <si>
-    <t>C-513 - 0022</t>
-  </si>
-  <si>
-    <t>C-513 - 0024</t>
-  </si>
-  <si>
-    <t>C-513 - 0030</t>
-  </si>
-  <si>
     <t>RBC</t>
   </si>
   <si>
@@ -2789,6 +2669,120 @@
   </si>
   <si>
     <t>HbA1c (D10)</t>
+  </si>
+  <si>
+    <t>Capillarys OCTA</t>
+  </si>
+  <si>
+    <t>Cobas C-513 - 0022</t>
+  </si>
+  <si>
+    <t>Cobas C-513 - 0024</t>
+  </si>
+  <si>
+    <t>Cobas C-513 - 0030</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 1_1_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 1_1_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 1_2_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 1_2_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 1_3_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 1_3_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 1_4_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 1_4_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 2_1_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 2_1_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 2_2_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 2_2_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 2_3_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 2_3_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 3_1_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 3_1_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 3_2_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 3_2_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 3_3_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 3_3_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 4_1_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 4_1_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 4_2_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 4_2_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 4_3_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 4_3_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 4_4_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 4_4_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 6_1_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 6_1_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 6_2_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 6_2_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 6_3_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 6_3_2</t>
   </si>
 </sst>
 </file>
@@ -3360,10 +3354,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}" name="Equipamentos" displayName="Equipamentos" ref="A1:A89" totalsRowShown="0">
-  <autoFilter ref="A1:A89" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A89">
-    <sortCondition ref="A1:A89"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}" name="Equipamentos" displayName="Equipamentos" ref="A1:A87" totalsRowShown="0">
+  <autoFilter ref="A1:A87" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A87">
+    <sortCondition ref="A1:A87"/>
   </sortState>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{1B9AEB56-1EBB-4F60-AF89-FB7F0CA8B355}" name="Equipamentos"/>
@@ -3704,10 +3698,10 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -3716,27 +3710,27 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="I1" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>874</v>
+        <v>834</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B2" s="1">
         <v>0.22</v>
@@ -3745,13 +3739,13 @@
         <v>0.11</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F2" t="s">
         <v>250</v>
-      </c>
-      <c r="F2" t="s">
-        <v>251</v>
       </c>
       <c r="G2" s="2">
         <v>3.89</v>
@@ -3760,12 +3754,12 @@
         <v>26.8</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B3" s="1">
         <v>0.3</v>
@@ -3774,13 +3768,13 @@
         <v>0.15</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
+        <v>380</v>
+      </c>
+      <c r="F3" t="s">
         <v>381</v>
-      </c>
-      <c r="F3" t="s">
-        <v>382</v>
       </c>
       <c r="G3" s="2">
         <v>1</v>
@@ -3789,12 +3783,12 @@
         <v>75</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B4" s="1">
         <v>0.15</v>
@@ -3803,13 +3797,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
         <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
       </c>
       <c r="G4" s="2">
         <v>3.4</v>
@@ -3818,12 +3812,12 @@
         <v>7</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1">
         <v>0.35</v>
@@ -3832,13 +3826,13 @@
         <v>0.05</v>
       </c>
       <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
       </c>
       <c r="G5" s="2">
         <v>5</v>
@@ -3847,12 +3841,12 @@
         <v>46</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
         <v>0.15</v>
@@ -3861,13 +3855,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>17</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -3876,12 +3870,12 @@
         <v>0.99</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B7" s="1">
         <v>0.2</v>
@@ -3890,13 +3884,13 @@
         <v>0.1</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" t="s">
         <v>119</v>
-      </c>
-      <c r="F7" t="s">
-        <v>120</v>
       </c>
       <c r="G7" s="2">
         <v>0.09</v>
@@ -3905,12 +3899,12 @@
         <v>0.3</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B8" s="1">
         <v>6.0999999999999999E-2</v>
@@ -3919,13 +3913,13 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
         <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>20</v>
       </c>
       <c r="G8" s="2">
         <v>3.5</v>
@@ -3934,12 +3928,12 @@
         <v>5.2</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B9" s="1">
         <v>0.27</v>
@@ -3948,13 +3942,13 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F9" t="s">
         <v>241</v>
-      </c>
-      <c r="F9" t="s">
-        <v>242</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -3963,12 +3957,12 @@
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1">
         <v>0.3</v>
@@ -3977,13 +3971,13 @@
         <v>0.126</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
         <v>25</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
       </c>
       <c r="G10" s="2">
         <v>2.52</v>
@@ -3992,12 +3986,12 @@
         <v>39.200000000000003</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B11" s="1">
         <v>0.18</v>
@@ -4006,13 +4000,13 @@
         <v>0.09</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
         <v>27</v>
-      </c>
-      <c r="F11" t="s">
-        <v>28</v>
       </c>
       <c r="G11" s="2">
         <v>90</v>
@@ -4021,12 +4015,12 @@
         <v>200</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B12" s="1">
         <v>0.2</v>
@@ -4035,18 +4029,18 @@
         <v>0.1</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1">
         <v>0.18</v>
@@ -4055,13 +4049,13 @@
         <v>0.09</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
         <v>31</v>
-      </c>
-      <c r="F13" t="s">
-        <v>32</v>
       </c>
       <c r="G13" s="2">
         <v>58</v>
@@ -4070,12 +4064,12 @@
         <v>155</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B14" s="1">
         <v>0.2</v>
@@ -4084,18 +4078,18 @@
         <v>0.06</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1">
         <v>0.2</v>
@@ -4104,13 +4098,13 @@
         <v>0.1</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" t="s">
         <v>35</v>
-      </c>
-      <c r="F15" t="s">
-        <v>36</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -4119,12 +4113,12 @@
         <v>5.8</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" s="1">
         <v>0.114</v>
@@ -4133,13 +4127,13 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" t="s">
         <v>38</v>
-      </c>
-      <c r="F16" t="s">
-        <v>39</v>
       </c>
       <c r="G16" s="2">
         <v>0.01</v>
@@ -4148,12 +4142,12 @@
         <v>2.71</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B17" s="1">
         <v>0.3</v>
@@ -4162,13 +4156,13 @@
         <v>0.15</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
+        <v>246</v>
+      </c>
+      <c r="F17" t="s">
         <v>247</v>
-      </c>
-      <c r="F17" t="s">
-        <v>248</v>
       </c>
       <c r="G17" s="2">
         <v>33</v>
@@ -4177,12 +4171,12 @@
         <v>193</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B18" s="1">
         <v>0.19400000000000001</v>
@@ -4191,13 +4185,13 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F18" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G18" s="2">
         <v>15</v>
@@ -4206,12 +4200,12 @@
         <v>99</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="1">
         <v>0.2</v>
@@ -4220,13 +4214,13 @@
         <v>0.1</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" t="s">
         <v>43</v>
-      </c>
-      <c r="F19" t="s">
-        <v>44</v>
       </c>
       <c r="G19" s="2">
         <v>19</v>
@@ -4235,12 +4229,12 @@
         <v>54</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B20" s="1">
         <v>0.3</v>
@@ -4249,13 +4243,13 @@
         <v>0.15</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
         <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>47</v>
       </c>
       <c r="G20" s="2">
         <v>0.19</v>
@@ -4264,12 +4258,12 @@
         <v>1.07</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B21" s="1">
         <v>0.3</v>
@@ -4278,13 +4272,13 @@
         <v>0.08</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" t="s">
         <v>40</v>
-      </c>
-      <c r="F21" t="s">
-        <v>41</v>
       </c>
       <c r="G21" s="2">
         <v>28</v>
@@ -4293,12 +4287,12 @@
         <v>100</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B22" s="1">
         <v>0.3</v>
@@ -4307,13 +4301,13 @@
         <v>0.15</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" t="s">
         <v>52</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
@@ -4322,12 +4316,12 @@
         <v>9.99</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="1">
         <v>0.24</v>
@@ -4336,13 +4330,13 @@
         <v>0.12</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" t="s">
         <v>55</v>
-      </c>
-      <c r="F23" t="s">
-        <v>56</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
@@ -4351,12 +4345,12 @@
         <v>0.99</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24" s="1">
         <v>0.12</v>
@@ -4365,13 +4359,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" t="s">
         <v>58</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
       </c>
       <c r="G24" s="2">
         <v>1.01</v>
@@ -4380,12 +4374,12 @@
         <v>60</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25" s="1">
         <v>0.18099999999999999</v>
@@ -4394,13 +4388,13 @@
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" t="s">
         <v>61</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
@@ -4409,15 +4403,15 @@
         <v>0.89</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>816</v>
+        <v>779</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>875</v>
+        <v>835</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="1">
         <v>0.18</v>
@@ -4426,13 +4420,13 @@
         <v>0.09</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" t="s">
         <v>64</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
       </c>
       <c r="G26" s="2">
         <v>1.01</v>
@@ -4441,12 +4435,12 @@
         <v>60</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1">
         <v>0.12</v>
@@ -4455,13 +4449,13 @@
         <v>0.06</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" t="s">
         <v>67</v>
-      </c>
-      <c r="F27" t="s">
-        <v>68</v>
       </c>
       <c r="G27" s="2">
         <v>1.01</v>
@@ -4470,12 +4464,12 @@
         <v>60</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B28" s="1">
         <v>0.153</v>
@@ -4484,13 +4478,13 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" t="s">
         <v>70</v>
-      </c>
-      <c r="F28" t="s">
-        <v>71</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
@@ -4499,12 +4493,12 @@
         <v>9.99</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B29" s="1">
         <v>0.24</v>
@@ -4513,13 +4507,13 @@
         <v>0.12</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" t="s">
         <v>73</v>
-      </c>
-      <c r="F29" t="s">
-        <v>74</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
@@ -4528,15 +4522,15 @@
         <v>0.89</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>816</v>
+        <v>779</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>876</v>
+        <v>836</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B30" s="1">
         <v>0.13500000000000001</v>
@@ -4545,13 +4539,13 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" t="s">
         <v>76</v>
-      </c>
-      <c r="F30" t="s">
-        <v>77</v>
       </c>
       <c r="G30" s="2">
         <v>3</v>
@@ -4560,12 +4554,12 @@
         <v>28</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B31" s="1">
         <v>0.14199999999999999</v>
@@ -4574,13 +4568,13 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="D31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" t="s">
         <v>79</v>
-      </c>
-      <c r="F31" t="s">
-        <v>80</v>
       </c>
       <c r="G31" s="2">
         <v>2.6</v>
@@ -4589,12 +4583,12 @@
         <v>24.9</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B32" s="1">
         <v>0.3</v>
@@ -4603,13 +4597,13 @@
         <v>0.15</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E32" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" t="s">
         <v>92</v>
-      </c>
-      <c r="F32" t="s">
-        <v>93</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
@@ -4618,12 +4612,12 @@
         <v>114</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>877</v>
+        <v>837</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B33" s="1">
         <v>0.22</v>
@@ -4632,13 +4626,13 @@
         <v>0.11</v>
       </c>
       <c r="D33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E33" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" t="s">
         <v>94</v>
-      </c>
-      <c r="F33" t="s">
-        <v>95</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
@@ -4647,12 +4641,12 @@
         <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>878</v>
+        <v>838</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B34" s="1">
         <v>0.3</v>
@@ -4661,13 +4655,13 @@
         <v>0.15</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" t="s">
         <v>82</v>
-      </c>
-      <c r="F34" t="s">
-        <v>83</v>
       </c>
       <c r="G34" s="2">
         <v>46</v>
@@ -4676,12 +4670,12 @@
         <v>304</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B35" s="1">
         <v>0.155</v>
@@ -4690,13 +4684,13 @@
         <v>0.08</v>
       </c>
       <c r="D35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E35" t="s">
+        <v>84</v>
+      </c>
+      <c r="F35" t="s">
         <v>85</v>
-      </c>
-      <c r="F35" t="s">
-        <v>86</v>
       </c>
       <c r="G35" s="2">
         <v>46</v>
@@ -4705,12 +4699,12 @@
         <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B36" s="1">
         <v>0.3</v>
@@ -4719,10 +4713,10 @@
         <v>0.15</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
@@ -4731,15 +4725,15 @@
         <v>6.99</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B37" s="1">
         <v>0.3</v>
@@ -4748,10 +4742,10 @@
         <v>0.15</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
@@ -4760,15 +4754,15 @@
         <v>6.99</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B38" s="1">
         <v>0.19500000000000001</v>
@@ -4777,21 +4771,21 @@
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
+        <v>98</v>
+      </c>
+      <c r="F38" t="s">
         <v>99</v>
       </c>
-      <c r="F38" t="s">
-        <v>100</v>
-      </c>
       <c r="I38" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B39" s="1">
         <v>0.22500000000000001</v>
@@ -4800,21 +4794,21 @@
         <v>0.113</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
         <v>102</v>
       </c>
-      <c r="F39" t="s">
-        <v>103</v>
-      </c>
       <c r="I39" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B40" s="1">
         <v>0.3</v>
@@ -4823,10 +4817,10 @@
         <v>0.15</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
@@ -4835,15 +4829,15 @@
         <v>6.99</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B41" s="1">
         <v>0.3</v>
@@ -4852,10 +4846,10 @@
         <v>0.15</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
@@ -4864,15 +4858,15 @@
         <v>6.99</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B42" s="1">
         <v>0.22</v>
@@ -4881,13 +4875,13 @@
         <v>0.11</v>
       </c>
       <c r="D42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" t="s">
         <v>109</v>
-      </c>
-      <c r="F42" t="s">
-        <v>110</v>
       </c>
       <c r="G42" s="2">
         <v>3.5</v>
@@ -4896,12 +4890,12 @@
         <v>77</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B43" s="1">
         <v>0.22800000000000001</v>
@@ -4910,13 +4904,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E43" t="s">
+        <v>111</v>
+      </c>
+      <c r="F43" t="s">
         <v>112</v>
-      </c>
-      <c r="F43" t="s">
-        <v>113</v>
       </c>
       <c r="G43" s="2">
         <v>0.12</v>
@@ -4925,12 +4919,12 @@
         <v>0.78</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B44" s="1">
         <v>0.15</v>
@@ -4939,18 +4933,18 @@
         <v>0.03</v>
       </c>
       <c r="D44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B45" s="1">
         <v>0.12</v>
@@ -4959,18 +4953,18 @@
         <v>0.06</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B46" s="1">
         <v>0.2</v>
@@ -4979,13 +4973,13 @@
         <v>0.1</v>
       </c>
       <c r="D46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E46" t="s">
+        <v>303</v>
+      </c>
+      <c r="F46" t="s">
         <v>304</v>
-      </c>
-      <c r="F46" t="s">
-        <v>305</v>
       </c>
       <c r="G46" s="2">
         <v>0</v>
@@ -4994,12 +4988,12 @@
         <v>5</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B47" s="1">
         <v>0.19400000000000001</v>
@@ -5008,13 +5002,13 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="D47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F47" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
@@ -5023,12 +5017,12 @@
         <v>650</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B48" s="1">
         <v>0.24</v>
@@ -5037,13 +5031,13 @@
         <v>0.12</v>
       </c>
       <c r="D48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E48" t="s">
+        <v>321</v>
+      </c>
+      <c r="F48" t="s">
         <v>322</v>
-      </c>
-      <c r="F48" t="s">
-        <v>323</v>
       </c>
       <c r="G48" s="2">
         <v>3</v>
@@ -5052,12 +5046,12 @@
         <v>15</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B49" s="1">
         <v>0.24</v>
@@ -5066,13 +5060,13 @@
         <v>0.12</v>
       </c>
       <c r="D49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E49" t="s">
+        <v>124</v>
+      </c>
+      <c r="F49" t="s">
         <v>125</v>
-      </c>
-      <c r="F49" t="s">
-        <v>126</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
@@ -5081,12 +5075,12 @@
         <v>10</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B50" s="1">
         <v>0.3</v>
@@ -5095,13 +5089,13 @@
         <v>0.15</v>
       </c>
       <c r="D50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E50" t="s">
+        <v>127</v>
+      </c>
+      <c r="F50" t="s">
         <v>128</v>
-      </c>
-      <c r="F50" t="s">
-        <v>129</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
@@ -5110,12 +5104,12 @@
         <v>0.9</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B51" s="1">
         <v>0.155</v>
@@ -5124,13 +5118,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D51" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E51" t="s">
+        <v>129</v>
+      </c>
+      <c r="F51" t="s">
         <v>130</v>
-      </c>
-      <c r="F51" t="s">
-        <v>131</v>
       </c>
       <c r="G51" s="2">
         <v>21</v>
@@ -5139,12 +5133,12 @@
         <v>39</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B52" s="1">
         <v>0.17</v>
@@ -5153,13 +5147,13 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E52" t="s">
+        <v>132</v>
+      </c>
+      <c r="F52" t="s">
         <v>133</v>
-      </c>
-      <c r="F52" t="s">
-        <v>134</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
@@ -5168,12 +5162,12 @@
         <v>35</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B53" s="1">
         <v>0.17</v>
@@ -5182,13 +5176,13 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E53" t="s">
+        <v>135</v>
+      </c>
+      <c r="F53" t="s">
         <v>136</v>
-      </c>
-      <c r="F53" t="s">
-        <v>137</v>
       </c>
       <c r="G53" s="2">
         <v>0</v>
@@ -5197,12 +5191,12 @@
         <v>28.5</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B54" s="1">
         <v>0.2</v>
@@ -5211,13 +5205,13 @@
         <v>0.1</v>
       </c>
       <c r="D54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E54" t="s">
+        <v>138</v>
+      </c>
+      <c r="F54" t="s">
         <v>139</v>
-      </c>
-      <c r="F54" t="s">
-        <v>140</v>
       </c>
       <c r="G54" s="2">
         <v>0</v>
@@ -5226,12 +5220,12 @@
         <v>34</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B55" s="1">
         <v>0.18</v>
@@ -5240,13 +5234,13 @@
         <v>0.09</v>
       </c>
       <c r="D55" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E55" t="s">
+        <v>141</v>
+      </c>
+      <c r="F55" t="s">
         <v>142</v>
-      </c>
-      <c r="F55" t="s">
-        <v>143</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
@@ -5255,12 +5249,12 @@
         <v>25</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B56" s="1">
         <v>0.24</v>
@@ -5269,13 +5263,13 @@
         <v>0.12</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E56" t="s">
+        <v>144</v>
+      </c>
+      <c r="F56" t="s">
         <v>145</v>
-      </c>
-      <c r="F56" t="s">
-        <v>146</v>
       </c>
       <c r="G56" s="2">
         <v>0</v>
@@ -5284,12 +5278,12 @@
         <v>6.9</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B57" s="1">
         <v>0.3</v>
@@ -5298,13 +5292,13 @@
         <v>0.15</v>
       </c>
       <c r="D57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E57" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F57" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G57" s="2">
         <v>135</v>
@@ -5313,12 +5307,12 @@
         <v>225</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B58" s="1">
         <v>0.15</v>
@@ -5327,13 +5321,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D58" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E58" t="s">
+        <v>146</v>
+      </c>
+      <c r="F58" t="s">
         <v>147</v>
-      </c>
-      <c r="F58" t="s">
-        <v>148</v>
       </c>
       <c r="G58" s="2">
         <v>8.1999999999999993</v>
@@ -5342,12 +5336,12 @@
         <v>9.6</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B59" s="1">
         <v>0.12</v>
@@ -5356,13 +5350,13 @@
         <v>0.06</v>
       </c>
       <c r="D59" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E59" t="s">
+        <v>150</v>
+      </c>
+      <c r="F59" t="s">
         <v>151</v>
-      </c>
-      <c r="F59" t="s">
-        <v>152</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -5371,12 +5365,12 @@
         <v>1.4</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B60" s="1">
         <v>0.3</v>
@@ -5385,13 +5379,13 @@
         <v>0.15</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E60" t="s">
+        <v>153</v>
+      </c>
+      <c r="F60" t="s">
         <v>154</v>
-      </c>
-      <c r="F60" t="s">
-        <v>155</v>
       </c>
       <c r="G60" s="2">
         <v>0</v>
@@ -5400,12 +5394,12 @@
         <v>14.3</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B61" s="1">
         <v>0.27</v>
@@ -5414,13 +5408,13 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="D61" t="s">
+        <v>156</v>
+      </c>
+      <c r="E61" t="s">
         <v>157</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>158</v>
-      </c>
-      <c r="F61" t="s">
-        <v>159</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
@@ -5429,12 +5423,12 @@
         <v>50</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B62" s="1">
         <v>0.3</v>
@@ -5443,13 +5437,13 @@
         <v>0.15</v>
       </c>
       <c r="D62" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E62" t="s">
+        <v>371</v>
+      </c>
+      <c r="F62" t="s">
         <v>372</v>
-      </c>
-      <c r="F62" t="s">
-        <v>373</v>
       </c>
       <c r="G62" s="2">
         <v>30</v>
@@ -5458,12 +5452,12 @@
         <v>130</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B63" s="1">
         <v>0.35</v>
@@ -5472,13 +5466,13 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E63" t="s">
+        <v>160</v>
+      </c>
+      <c r="F63" t="s">
         <v>161</v>
-      </c>
-      <c r="F63" t="s">
-        <v>162</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
@@ -5487,15 +5481,15 @@
         <v>13.99</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>881</v>
+        <v>841</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>882</v>
+        <v>842</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B64" s="1">
         <v>0.35</v>
@@ -5504,13 +5498,13 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E64" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G64" s="2">
         <v>0</v>
@@ -5519,15 +5513,15 @@
         <v>9.99</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>883</v>
+        <v>843</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B65" s="1">
         <v>0.3</v>
@@ -5536,13 +5530,13 @@
         <v>0.15</v>
       </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E65" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
@@ -5551,15 +5545,15 @@
         <v>9.99</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>883</v>
+        <v>843</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B66" s="1">
         <v>0.3</v>
@@ -5568,13 +5562,13 @@
         <v>0.15</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E66" t="s">
+        <v>167</v>
+      </c>
+      <c r="F66" t="s">
         <v>168</v>
-      </c>
-      <c r="F66" t="s">
-        <v>169</v>
       </c>
       <c r="G66" s="2">
         <v>0</v>
@@ -5583,15 +5577,15 @@
         <v>8.99</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>884</v>
+        <v>844</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>885</v>
+        <v>845</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B67" s="1">
         <v>0.33400000000000002</v>
@@ -5600,13 +5594,13 @@
         <v>0.15</v>
       </c>
       <c r="D67" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E67" t="s">
+        <v>170</v>
+      </c>
+      <c r="F67" t="s">
         <v>171</v>
-      </c>
-      <c r="F67" t="s">
-        <v>172</v>
       </c>
       <c r="G67" s="2">
         <v>0</v>
@@ -5615,15 +5609,15 @@
         <v>0.89</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>816</v>
+        <v>779</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>886</v>
+        <v>846</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B68" s="1">
         <v>0.3</v>
@@ -5632,13 +5626,13 @@
         <v>0.15</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E68" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F68" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G68" s="2">
         <v>0</v>
@@ -5647,15 +5641,15 @@
         <v>6.99</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B69" s="1">
         <v>0.17</v>
@@ -5664,13 +5658,13 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E69" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F69" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G69" s="2">
         <v>0.3</v>
@@ -5679,12 +5673,12 @@
         <v>3.8</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B70" s="1">
         <v>0.12</v>
@@ -5693,13 +5687,13 @@
         <v>0.06</v>
       </c>
       <c r="D70" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E70" t="s">
+        <v>177</v>
+      </c>
+      <c r="F70" t="s">
         <v>178</v>
-      </c>
-      <c r="F70" t="s">
-        <v>179</v>
       </c>
       <c r="G70" s="2">
         <v>20</v>
@@ -5708,12 +5702,12 @@
         <v>60</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B71" s="1">
         <v>0.24</v>
@@ -5722,13 +5716,13 @@
         <v>0.12</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E71" t="s">
+        <v>180</v>
+      </c>
+      <c r="F71" t="s">
         <v>181</v>
-      </c>
-      <c r="F71" t="s">
-        <v>182</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
@@ -5737,12 +5731,12 @@
         <v>0.99</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B72" s="1">
         <v>0.15</v>
@@ -5751,13 +5745,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E72" t="s">
+        <v>183</v>
+      </c>
+      <c r="F72" t="s">
         <v>184</v>
-      </c>
-      <c r="F72" t="s">
-        <v>185</v>
       </c>
       <c r="G72" s="2">
         <v>0.62</v>
@@ -5766,12 +5760,12 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B73" s="1">
         <v>0.25</v>
@@ -5780,13 +5774,13 @@
         <v>0.125</v>
       </c>
       <c r="D73" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E73" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F73" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G73" s="2">
         <v>100</v>
@@ -5795,12 +5789,12 @@
         <v>300</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B74" s="1">
         <v>0.13</v>
@@ -5809,13 +5803,13 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="D74" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E74" t="s">
+        <v>187</v>
+      </c>
+      <c r="F74" t="s">
         <v>188</v>
-      </c>
-      <c r="F74" t="s">
-        <v>189</v>
       </c>
       <c r="G74" s="2">
         <v>98</v>
@@ -5824,12 +5818,12 @@
         <v>107</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B75" s="1">
         <v>0.1</v>
@@ -5838,13 +5832,13 @@
         <v>0.05</v>
       </c>
       <c r="D75" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E75" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F75" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="G75" s="2">
         <v>110</v>
@@ -5853,12 +5847,12 @@
         <v>250</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B76" s="1">
         <v>0.23</v>
@@ -5867,13 +5861,13 @@
         <v>0.115</v>
       </c>
       <c r="D76" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E76" t="s">
+        <v>190</v>
+      </c>
+      <c r="F76" t="s">
         <v>191</v>
-      </c>
-      <c r="F76" t="s">
-        <v>192</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
@@ -5882,15 +5876,15 @@
         <v>0.49</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>887</v>
+        <v>847</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>888</v>
+        <v>848</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B77" s="1">
         <v>0.15</v>
@@ -5899,13 +5893,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E77" t="s">
+        <v>193</v>
+      </c>
+      <c r="F77" t="s">
         <v>194</v>
-      </c>
-      <c r="F77" t="s">
-        <v>195</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
@@ -5914,15 +5908,15 @@
         <v>0.69</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>889</v>
+        <v>849</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>890</v>
+        <v>850</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B78" s="1">
         <v>0.4</v>
@@ -5931,13 +5925,13 @@
         <v>0.2</v>
       </c>
       <c r="D78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E78" t="s">
+        <v>500</v>
+      </c>
+      <c r="F78" t="s">
         <v>501</v>
-      </c>
-      <c r="F78" t="s">
-        <v>502</v>
       </c>
       <c r="G78" s="2">
         <v>5</v>
@@ -5946,12 +5940,12 @@
         <v>41</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B79" s="1">
         <v>0.2</v>
@@ -5960,13 +5954,13 @@
         <v>0.1</v>
       </c>
       <c r="D79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E79" t="s">
+        <v>512</v>
+      </c>
+      <c r="F79" t="s">
         <v>513</v>
-      </c>
-      <c r="F79" t="s">
-        <v>514</v>
       </c>
       <c r="G79" s="2">
         <v>200</v>
@@ -5975,12 +5969,12 @@
         <v>360</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B80" s="1">
         <v>0.16</v>
@@ -5989,13 +5983,13 @@
         <v>0.08</v>
       </c>
       <c r="D80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E80" t="s">
+        <v>515</v>
+      </c>
+      <c r="F80" t="s">
         <v>516</v>
-      </c>
-      <c r="F80" t="s">
-        <v>517</v>
       </c>
       <c r="G80" s="2">
         <v>50</v>
@@ -6004,12 +5998,12 @@
         <v>150</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B81" s="1">
         <v>0.18</v>
@@ -6018,13 +6012,13 @@
         <v>0.09</v>
       </c>
       <c r="D81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E81" t="s">
+        <v>202</v>
+      </c>
+      <c r="F81" t="s">
         <v>203</v>
-      </c>
-      <c r="F81" t="s">
-        <v>204</v>
       </c>
       <c r="G81" s="2">
         <v>90</v>
@@ -6033,12 +6027,12 @@
         <v>170</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B82" s="1">
         <v>0.17</v>
@@ -6047,13 +6041,13 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="D82" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E82" t="s">
+        <v>205</v>
+      </c>
+      <c r="F82" t="s">
         <v>206</v>
-      </c>
-      <c r="F82" t="s">
-        <v>207</v>
       </c>
       <c r="G82" s="2">
         <v>12</v>
@@ -6062,12 +6056,12 @@
         <v>36</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B83" s="1">
         <v>0.2</v>
@@ -6076,13 +6070,13 @@
         <v>0.1</v>
       </c>
       <c r="D83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E83" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F83" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G83" s="2">
         <v>5.27</v>
@@ -6091,12 +6085,12 @@
         <v>22.45</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B84" s="1">
         <v>0.24</v>
@@ -6105,13 +6099,13 @@
         <v>0.12</v>
       </c>
       <c r="D84" t="s">
+        <v>211</v>
+      </c>
+      <c r="E84" t="s">
         <v>212</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>213</v>
-      </c>
-      <c r="F84" t="s">
-        <v>214</v>
       </c>
       <c r="G84" s="2">
         <v>1.5</v>
@@ -6120,12 +6114,12 @@
         <v>20.29</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B85" s="1">
         <v>0.2</v>
@@ -6134,13 +6128,13 @@
         <v>0.1</v>
       </c>
       <c r="D85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E85" t="s">
+        <v>216</v>
+      </c>
+      <c r="F85" t="s">
         <v>217</v>
-      </c>
-      <c r="F85" t="s">
-        <v>218</v>
       </c>
       <c r="G85" s="2">
         <v>0.67</v>
@@ -6149,12 +6143,12 @@
         <v>1.17</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B86" s="1">
         <v>0.25</v>
@@ -6163,13 +6157,13 @@
         <v>0.125</v>
       </c>
       <c r="D86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E86" t="s">
+        <v>541</v>
+      </c>
+      <c r="F86" t="s">
         <v>542</v>
-      </c>
-      <c r="F86" t="s">
-        <v>543</v>
       </c>
       <c r="G86" s="2">
         <v>80</v>
@@ -6178,12 +6172,12 @@
         <v>120</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B87" s="1">
         <v>0.3</v>
@@ -6192,13 +6186,13 @@
         <v>0.15</v>
       </c>
       <c r="D87" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E87" t="s">
+        <v>722</v>
+      </c>
+      <c r="F87" t="s">
         <v>723</v>
-      </c>
-      <c r="F87" t="s">
-        <v>724</v>
       </c>
       <c r="G87" s="2">
         <v>39</v>
@@ -6207,12 +6201,12 @@
         <v>259</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>813</v>
+        <v>776</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B88" s="1">
         <v>0.33</v>
@@ -6221,13 +6215,13 @@
         <v>0.16500000000000001</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E88" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F88" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G88" s="2">
         <v>0</v>
@@ -6236,15 +6230,15 @@
         <v>9.99</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J88" s="8" t="s">
-        <v>891</v>
+        <v>851</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B89" s="1">
         <v>0.18</v>
@@ -6253,13 +6247,13 @@
         <v>0.09</v>
       </c>
       <c r="D89" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E89" t="s">
+        <v>223</v>
+      </c>
+      <c r="F89" t="s">
         <v>224</v>
-      </c>
-      <c r="F89" t="s">
-        <v>225</v>
       </c>
       <c r="G89" s="2">
         <v>0</v>
@@ -6268,12 +6262,12 @@
         <v>200</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B90" s="1">
         <v>0.24</v>
@@ -6282,13 +6276,13 @@
         <v>0.12</v>
       </c>
       <c r="D90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E90" t="s">
+        <v>226</v>
+      </c>
+      <c r="F90" t="s">
         <v>227</v>
-      </c>
-      <c r="F90" t="s">
-        <v>228</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
@@ -6297,15 +6291,15 @@
         <v>0.69</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>889</v>
+        <v>849</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>890</v>
+        <v>850</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B91" s="1">
         <v>0.15</v>
@@ -6314,13 +6308,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D91" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E91" t="s">
+        <v>229</v>
+      </c>
+      <c r="F91" t="s">
         <v>230</v>
-      </c>
-      <c r="F91" t="s">
-        <v>231</v>
       </c>
       <c r="G91" s="2">
         <v>0</v>
@@ -6329,15 +6323,15 @@
         <v>0.59</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>892</v>
+        <v>852</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>893</v>
+        <v>853</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B92" s="1">
         <v>0.15</v>
@@ -6346,13 +6340,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D92" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E92" t="s">
+        <v>232</v>
+      </c>
+      <c r="F92" t="s">
         <v>233</v>
-      </c>
-      <c r="F92" t="s">
-        <v>234</v>
       </c>
       <c r="G92" s="2">
         <v>5</v>
@@ -6361,12 +6355,12 @@
         <v>138</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B93" s="1">
         <v>0.23</v>
@@ -6375,13 +6369,13 @@
         <v>0.115</v>
       </c>
       <c r="D93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E93" t="s">
+        <v>235</v>
+      </c>
+      <c r="F93" t="s">
         <v>236</v>
-      </c>
-      <c r="F93" t="s">
-        <v>237</v>
       </c>
       <c r="G93" s="2">
         <v>4.0999999999999996</v>
@@ -6390,12 +6384,12 @@
         <v>12</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B94" s="1">
         <v>0.3</v>
@@ -6404,13 +6398,13 @@
         <v>0.15</v>
       </c>
       <c r="D94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E94" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F94" t="s">
-        <v>894</v>
+        <v>854</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
@@ -6419,15 +6413,15 @@
         <v>6.99</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>895</v>
+        <v>855</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B95" s="1">
         <v>0.2</v>
@@ -6436,13 +6430,13 @@
         <v>0.1</v>
       </c>
       <c r="D95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E95" t="s">
+        <v>254</v>
+      </c>
+      <c r="F95" t="s">
         <v>255</v>
-      </c>
-      <c r="F95" t="s">
-        <v>256</v>
       </c>
       <c r="G95" s="2">
         <v>2.5</v>
@@ -6451,12 +6445,12 @@
         <v>4.5</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B96" s="1">
         <v>0.25</v>
@@ -6465,13 +6459,13 @@
         <v>0.125</v>
       </c>
       <c r="D96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E96" t="s">
+        <v>243</v>
+      </c>
+      <c r="F96" t="s">
         <v>244</v>
-      </c>
-      <c r="F96" t="s">
-        <v>245</v>
       </c>
       <c r="G96" s="2">
         <v>34</v>
@@ -6480,12 +6474,12 @@
         <v>500</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B97" s="1">
         <v>0.36</v>
@@ -6494,13 +6488,13 @@
         <v>0.18</v>
       </c>
       <c r="D97" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E97" t="s">
+        <v>121</v>
+      </c>
+      <c r="F97" t="s">
         <v>122</v>
-      </c>
-      <c r="F97" t="s">
-        <v>123</v>
       </c>
       <c r="G97" s="2">
         <v>0.3</v>
@@ -6509,12 +6503,12 @@
         <v>1.2</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B98" s="1">
         <v>0.3</v>
@@ -6523,13 +6517,13 @@
         <v>0.15</v>
       </c>
       <c r="D98" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E98" t="s">
+        <v>218</v>
+      </c>
+      <c r="F98" t="s">
         <v>219</v>
-      </c>
-      <c r="F98" t="s">
-        <v>220</v>
       </c>
       <c r="G98" s="2">
         <v>125</v>
@@ -6538,12 +6532,12 @@
         <v>345</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B99" s="1">
         <v>0.13</v>
@@ -6552,13 +6546,13 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="D99" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E99" t="s">
+        <v>199</v>
+      </c>
+      <c r="F99" t="s">
         <v>200</v>
-      </c>
-      <c r="F99" t="s">
-        <v>201</v>
       </c>
       <c r="G99" s="2">
         <v>100</v>
@@ -6567,12 +6561,12 @@
         <v>199</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B100" s="1">
         <v>0.3</v>
@@ -6581,13 +6575,13 @@
         <v>0.15</v>
       </c>
       <c r="D100" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E100" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F100" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G100" s="2">
         <v>40</v>
@@ -6596,12 +6590,12 @@
         <v>150</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B101" s="1">
         <v>0.13</v>
@@ -6610,13 +6604,13 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="D101" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E101" t="s">
+        <v>275</v>
+      </c>
+      <c r="F101" t="s">
         <v>276</v>
-      </c>
-      <c r="F101" t="s">
-        <v>277</v>
       </c>
       <c r="G101" s="2">
         <v>70</v>
@@ -6625,12 +6619,12 @@
         <v>99</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B102" s="1">
         <v>0.15</v>
@@ -6639,13 +6633,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D102" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E102" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F102" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G102" s="2">
         <v>25.8</v>
@@ -6654,12 +6648,12 @@
         <v>134.80000000000001</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B103" s="1">
         <v>0.12</v>
@@ -6668,18 +6662,18 @@
         <v>0.06</v>
       </c>
       <c r="D103" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E103" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B104" s="1">
         <v>0.15</v>
@@ -6688,13 +6682,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D104" t="s">
+        <v>264</v>
+      </c>
+      <c r="E104" t="s">
         <v>265</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>266</v>
-      </c>
-      <c r="F104" t="s">
-        <v>267</v>
       </c>
       <c r="G104" s="2">
         <v>13</v>
@@ -6703,12 +6697,12 @@
         <v>115</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B105" s="1">
         <v>0.35</v>
@@ -6717,13 +6711,13 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="D105" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E105" t="s">
+        <v>252</v>
+      </c>
+      <c r="F105" t="s">
         <v>253</v>
-      </c>
-      <c r="F105" t="s">
-        <v>254</v>
       </c>
       <c r="G105" s="2">
         <v>40</v>
@@ -6732,12 +6726,12 @@
         <v>129</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B106" s="1">
         <v>0.16</v>
@@ -6746,13 +6740,13 @@
         <v>0.08</v>
       </c>
       <c r="D106" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E106" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F106" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G106" s="2">
         <v>0</v>
@@ -6761,12 +6755,12 @@
         <v>3</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B107" s="1">
         <v>0.3</v>
@@ -6775,10 +6769,10 @@
         <v>0.15</v>
       </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E107" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G107" s="2">
         <v>0</v>
@@ -6787,15 +6781,15 @@
         <v>6.99</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B108" s="1">
         <v>0.3</v>
@@ -6804,10 +6798,10 @@
         <v>0.15</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E108" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G108" s="2">
         <v>0</v>
@@ -6816,15 +6810,15 @@
         <v>6.99</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B109" s="1">
         <v>0.12</v>
@@ -6833,13 +6827,13 @@
         <v>0.06</v>
       </c>
       <c r="D109" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E109" t="s">
+        <v>275</v>
+      </c>
+      <c r="F109" t="s">
         <v>276</v>
-      </c>
-      <c r="F109" t="s">
-        <v>277</v>
       </c>
       <c r="G109" s="2">
         <v>70</v>
@@ -6848,12 +6842,12 @@
         <v>99</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B110" s="1">
         <v>0.3</v>
@@ -6862,13 +6856,13 @@
         <v>0.15</v>
       </c>
       <c r="D110" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F110" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G110" s="2">
         <v>0</v>
@@ -6877,12 +6871,12 @@
         <v>60</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B111" s="1">
         <v>0.15</v>
@@ -6891,13 +6885,13 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="D111" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E111" t="s">
+        <v>275</v>
+      </c>
+      <c r="F111" t="s">
         <v>276</v>
-      </c>
-      <c r="F111" t="s">
-        <v>277</v>
       </c>
       <c r="G111" s="2">
         <v>0</v>
@@ -6906,12 +6900,12 @@
         <v>500</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B112" s="1">
         <v>0.21</v>
@@ -6920,13 +6914,13 @@
         <v>0.105</v>
       </c>
       <c r="D112" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E112" t="s">
+        <v>278</v>
+      </c>
+      <c r="F112" t="s">
         <v>279</v>
-      </c>
-      <c r="F112" t="s">
-        <v>280</v>
       </c>
       <c r="G112" s="2">
         <v>0.01</v>
@@ -6935,12 +6929,12 @@
         <v>0.89</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B113" s="1">
         <v>0.16</v>
@@ -6949,13 +6943,13 @@
         <v>0.04</v>
       </c>
       <c r="D113" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E113" t="s">
+        <v>281</v>
+      </c>
+      <c r="F113" t="s">
         <v>282</v>
-      </c>
-      <c r="F113" t="s">
-        <v>283</v>
       </c>
       <c r="G113" s="2">
         <v>30</v>
@@ -6964,26 +6958,26 @@
         <v>200</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D114" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E114" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B115" s="1">
         <v>0.125</v>
@@ -6992,18 +6986,18 @@
         <v>6.3E-2</v>
       </c>
       <c r="D115" t="s">
+        <v>287</v>
+      </c>
+      <c r="E115" t="s">
         <v>288</v>
       </c>
-      <c r="E115" t="s">
-        <v>289</v>
-      </c>
       <c r="I115" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B116" s="1">
         <v>0.12</v>
@@ -7012,18 +7006,18 @@
         <v>0.06</v>
       </c>
       <c r="D116" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E116" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B117" s="1">
         <v>7.0000000000000001E-3</v>
@@ -7032,18 +7026,18 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D117" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E117" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B118" s="1">
         <v>0.22</v>
@@ -7052,18 +7046,18 @@
         <v>0.05</v>
       </c>
       <c r="D118" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E118" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B119" s="1">
         <v>0.15</v>
@@ -7072,18 +7066,18 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="D119" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E119" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>916</v>
+        <v>876</v>
       </c>
       <c r="B120" s="1">
         <v>0.05</v>
@@ -7092,13 +7086,13 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="D120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E120" t="s">
+        <v>298</v>
+      </c>
+      <c r="F120" t="s">
         <v>299</v>
-      </c>
-      <c r="F120" t="s">
-        <v>300</v>
       </c>
       <c r="G120" s="2">
         <v>4.2</v>
@@ -7107,12 +7101,12 @@
         <v>5.6</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B121" s="1">
         <v>0.24</v>
@@ -7121,13 +7115,13 @@
         <v>0.12</v>
       </c>
       <c r="D121" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E121" t="s">
+        <v>296</v>
+      </c>
+      <c r="F121" t="s">
         <v>297</v>
-      </c>
-      <c r="F121" t="s">
-        <v>298</v>
       </c>
       <c r="G121" s="2">
         <v>0</v>
@@ -7136,12 +7130,12 @@
         <v>0.99</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B122" s="1">
         <v>0.186</v>
@@ -7150,13 +7144,13 @@
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="D122" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E122" t="s">
+        <v>300</v>
+      </c>
+      <c r="F122" t="s">
         <v>301</v>
-      </c>
-      <c r="F122" t="s">
-        <v>302</v>
       </c>
       <c r="G122" s="2">
         <v>0</v>
@@ -7165,12 +7159,12 @@
         <v>0.9</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B123" s="1">
         <v>0.3</v>
@@ -7179,13 +7173,13 @@
         <v>0.15</v>
       </c>
       <c r="D123" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F123" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G123" s="2">
         <v>40</v>
@@ -7194,12 +7188,12 @@
         <v>60</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B124" s="1">
         <v>0.22</v>
@@ -7208,18 +7202,18 @@
         <v>0.05</v>
       </c>
       <c r="D124" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E124" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B125" s="1">
         <v>0.11</v>
@@ -7228,18 +7222,18 @@
         <v>2.7E-2</v>
       </c>
       <c r="D125" t="s">
+        <v>310</v>
+      </c>
+      <c r="E125" t="s">
         <v>311</v>
       </c>
-      <c r="E125" t="s">
-        <v>312</v>
-      </c>
       <c r="I125" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B126" s="1">
         <v>0.24</v>
@@ -7248,13 +7242,13 @@
         <v>0.12</v>
       </c>
       <c r="D126" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E126" t="s">
+        <v>313</v>
+      </c>
+      <c r="F126" t="s">
         <v>314</v>
-      </c>
-      <c r="F126" t="s">
-        <v>315</v>
       </c>
       <c r="G126" s="2">
         <v>0</v>
@@ -7263,12 +7257,12 @@
         <v>0.9</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B127" s="1">
         <v>0.42</v>
@@ -7277,13 +7271,13 @@
         <v>0.21</v>
       </c>
       <c r="D127" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E127" t="s">
+        <v>316</v>
+      </c>
+      <c r="F127" t="s">
         <v>317</v>
-      </c>
-      <c r="F127" t="s">
-        <v>318</v>
       </c>
       <c r="G127" s="2">
         <v>0</v>
@@ -7292,12 +7286,12 @@
         <v>0.9</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B128" s="1">
         <v>0.18</v>
@@ -7306,13 +7300,13 @@
         <v>0.09</v>
       </c>
       <c r="D128" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F128" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G128" s="2">
         <v>0</v>
@@ -7321,12 +7315,12 @@
         <v>0.99</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B129" s="1">
         <v>0.16</v>
@@ -7335,13 +7329,13 @@
         <v>0.08</v>
       </c>
       <c r="D129" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E129" t="s">
+        <v>411</v>
+      </c>
+      <c r="F129" t="s">
         <v>412</v>
-      </c>
-      <c r="F129" t="s">
-        <v>413</v>
       </c>
       <c r="G129" s="2">
         <v>0.15</v>
@@ -7350,12 +7344,12 @@
         <v>5</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B130" s="1">
         <v>0.15</v>
@@ -7364,21 +7358,21 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D130" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E130" t="s">
+        <v>324</v>
+      </c>
+      <c r="F130" t="s">
         <v>325</v>
       </c>
-      <c r="F130" t="s">
-        <v>326</v>
-      </c>
       <c r="I130" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B131" s="1">
         <v>0.17</v>
@@ -7387,13 +7381,13 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="D131" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E131" t="s">
+        <v>348</v>
+      </c>
+      <c r="F131" t="s">
         <v>349</v>
-      </c>
-      <c r="F131" t="s">
-        <v>350</v>
       </c>
       <c r="G131" s="2">
         <v>40</v>
@@ -7402,12 +7396,12 @@
         <v>350</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B132" s="1">
         <v>0.35</v>
@@ -7416,18 +7410,18 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="D132" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E132" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B133" s="1">
         <v>0.35</v>
@@ -7436,18 +7430,18 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="D133" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E133" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B134" s="1">
         <v>0.22</v>
@@ -7456,18 +7450,18 @@
         <v>0.11</v>
       </c>
       <c r="D134" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E134" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B135" s="1">
         <v>0.2</v>
@@ -7476,13 +7470,13 @@
         <v>0.1</v>
       </c>
       <c r="D135" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E135" t="s">
+        <v>337</v>
+      </c>
+      <c r="F135" t="s">
         <v>338</v>
-      </c>
-      <c r="F135" t="s">
-        <v>339</v>
       </c>
       <c r="G135" s="2">
         <v>3.4</v>
@@ -7491,12 +7485,12 @@
         <v>6.8</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B136" s="1">
         <v>0.17</v>
@@ -7505,13 +7499,13 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="D136" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E136" t="s">
+        <v>351</v>
+      </c>
+      <c r="F136" t="s">
         <v>352</v>
-      </c>
-      <c r="F136" t="s">
-        <v>353</v>
       </c>
       <c r="G136" s="2">
         <v>650</v>
@@ -7520,12 +7514,12 @@
         <v>1600</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B137" s="1">
         <v>0.12</v>
@@ -7534,10 +7528,10 @@
         <v>0.06</v>
       </c>
       <c r="D137" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G137" s="2">
         <v>405</v>
@@ -7546,12 +7540,12 @@
         <v>1011</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B138" s="1">
         <v>0.15</v>
@@ -7560,10 +7554,10 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D138" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E138" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G138" s="2">
         <v>169</v>
@@ -7572,12 +7566,12 @@
         <v>786</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B139" s="1">
         <v>0.15</v>
@@ -7586,10 +7580,10 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D139" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E139" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G139" s="2">
         <v>11</v>
@@ -7598,12 +7592,12 @@
         <v>85</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B140" s="1">
         <v>0.12</v>
@@ -7612,10 +7606,10 @@
         <v>0.06</v>
       </c>
       <c r="D140" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G140" s="2">
         <v>3</v>
@@ -7624,12 +7618,12 @@
         <v>201</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B141" s="1">
         <v>0.17</v>
@@ -7638,13 +7632,13 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="D141" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E141" t="s">
+        <v>354</v>
+      </c>
+      <c r="F141" t="s">
         <v>355</v>
-      </c>
-      <c r="F141" t="s">
-        <v>356</v>
       </c>
       <c r="G141" s="2">
         <v>50</v>
@@ -7653,12 +7647,12 @@
         <v>300</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B142" s="1">
         <v>0.157</v>
@@ -7667,13 +7661,13 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="D142" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F142" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G142" s="2">
         <v>2.6</v>
@@ -7682,12 +7676,12 @@
         <v>24.9</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B143" s="1">
         <v>0.3</v>
@@ -7696,10 +7690,10 @@
         <v>0.15</v>
       </c>
       <c r="D143" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E143" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G143" s="2">
         <v>0</v>
@@ -7708,15 +7702,15 @@
         <v>6.99</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B144" s="1">
         <v>0.11</v>
@@ -7725,13 +7719,13 @@
         <v>5.5E-2</v>
       </c>
       <c r="D144" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E144" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F144" t="s">
-        <v>898</v>
+        <v>858</v>
       </c>
       <c r="G144" s="2">
         <v>170</v>
@@ -7740,12 +7734,12 @@
         <v>370</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>896</v>
+        <v>856</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B145" s="1">
         <v>0.2</v>
@@ -7754,13 +7748,13 @@
         <v>0.1</v>
       </c>
       <c r="D145" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E145" t="s">
+        <v>361</v>
+      </c>
+      <c r="F145" t="s">
         <v>362</v>
-      </c>
-      <c r="F145" t="s">
-        <v>363</v>
       </c>
       <c r="G145" s="2">
         <v>6.7</v>
@@ -7769,12 +7763,12 @@
         <v>22.4</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B146" s="1">
         <v>0.3</v>
@@ -7783,10 +7777,10 @@
         <v>0.15</v>
       </c>
       <c r="D146" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E146" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G146" s="2">
         <v>0</v>
@@ -7795,15 +7789,15 @@
         <v>6.99</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J146" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B147" s="1">
         <v>0.12</v>
@@ -7812,13 +7806,13 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="D147" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E147" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F147" t="s">
-        <v>899</v>
+        <v>859</v>
       </c>
       <c r="G147" s="2">
         <v>90</v>
@@ -7827,12 +7821,12 @@
         <v>210</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>897</v>
+        <v>857</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B148" s="1">
         <v>0.2</v>
@@ -7841,13 +7835,13 @@
         <v>0.1</v>
       </c>
       <c r="D148" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E148" t="s">
+        <v>366</v>
+      </c>
+      <c r="F148" t="s">
         <v>367</v>
-      </c>
-      <c r="F148" t="s">
-        <v>368</v>
       </c>
       <c r="G148" s="2">
         <v>8.3000000000000007</v>
@@ -7856,12 +7850,12 @@
         <v>27</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B149" s="1">
         <v>0.25</v>
@@ -7870,13 +7864,13 @@
         <v>0.125</v>
       </c>
       <c r="D149" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E149" t="s">
+        <v>385</v>
+      </c>
+      <c r="F149" t="s">
         <v>386</v>
-      </c>
-      <c r="F149" t="s">
-        <v>387</v>
       </c>
       <c r="G149" s="2">
         <v>1.7</v>
@@ -7885,12 +7879,12 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B150" s="1">
         <v>0.3</v>
@@ -7899,13 +7893,13 @@
         <v>0.15</v>
       </c>
       <c r="D150" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E150" t="s">
+        <v>497</v>
+      </c>
+      <c r="F150" t="s">
         <v>498</v>
-      </c>
-      <c r="F150" t="s">
-        <v>499</v>
       </c>
       <c r="G150" s="2">
         <v>5</v>
@@ -7914,12 +7908,12 @@
         <v>40</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B151" s="1">
         <v>0.14000000000000001</v>
@@ -7928,13 +7922,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D151" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E151" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F151" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G151" s="2">
         <v>1.7</v>
@@ -7943,12 +7937,12 @@
         <v>8.6</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B152" s="1">
         <v>0.2</v>
@@ -7957,13 +7951,13 @@
         <v>0.1</v>
       </c>
       <c r="D152" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E152" t="s">
+        <v>196</v>
+      </c>
+      <c r="F152" t="s">
         <v>197</v>
-      </c>
-      <c r="F152" t="s">
-        <v>198</v>
       </c>
       <c r="G152" s="2">
         <v>76</v>
@@ -7972,12 +7966,12 @@
         <v>152</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B153" s="1">
         <v>0.3</v>
@@ -7986,13 +7980,13 @@
         <v>0.15</v>
       </c>
       <c r="D153" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E153" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F153" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G153" s="2">
         <v>4.0999999999999996</v>
@@ -8001,12 +7995,12 @@
         <v>13.8</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B154" s="1">
         <v>0.25</v>
@@ -8015,13 +8009,13 @@
         <v>0.125</v>
       </c>
       <c r="D154" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E154" t="s">
+        <v>383</v>
+      </c>
+      <c r="F154" t="s">
         <v>384</v>
-      </c>
-      <c r="F154" t="s">
-        <v>385</v>
       </c>
       <c r="G154" s="2">
         <v>0.5</v>
@@ -8030,12 +8024,12 @@
         <v>1.2</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B155" s="1">
         <v>0.1</v>
@@ -8044,13 +8038,13 @@
         <v>0.05</v>
       </c>
       <c r="D155" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E155" t="s">
+        <v>416</v>
+      </c>
+      <c r="F155" t="s">
         <v>417</v>
-      </c>
-      <c r="F155" t="s">
-        <v>418</v>
       </c>
       <c r="G155" s="2">
         <v>3.5</v>
@@ -8059,12 +8053,12 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B156" s="1">
         <v>0.1</v>
@@ -8073,13 +8067,13 @@
         <v>0.05</v>
       </c>
       <c r="D156" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E156" t="s">
+        <v>731</v>
+      </c>
+      <c r="F156" t="s">
         <v>732</v>
-      </c>
-      <c r="F156" t="s">
-        <v>733</v>
       </c>
       <c r="G156" s="2">
         <v>17</v>
@@ -8088,12 +8082,12 @@
         <v>164</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B157" s="1">
         <v>0.2</v>
@@ -8102,13 +8096,13 @@
         <v>0.1</v>
       </c>
       <c r="D157" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E157" t="s">
+        <v>388</v>
+      </c>
+      <c r="F157" t="s">
         <v>389</v>
-      </c>
-      <c r="F157" t="s">
-        <v>390</v>
       </c>
       <c r="G157" s="2">
         <v>0.5</v>
@@ -8117,12 +8111,12 @@
         <v>2.5</v>
       </c>
       <c r="I157" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B158" s="1">
         <v>0.3</v>
@@ -8131,10 +8125,10 @@
         <v>0.15</v>
       </c>
       <c r="D158" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E158" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G158" s="2">
         <v>0</v>
@@ -8143,15 +8137,15 @@
         <v>3.49</v>
       </c>
       <c r="I158" s="3" t="s">
-        <v>900</v>
+        <v>860</v>
       </c>
       <c r="J158" s="6" t="s">
-        <v>901</v>
+        <v>861</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B159" s="1">
         <v>0.36</v>
@@ -8160,13 +8154,13 @@
         <v>0.18</v>
       </c>
       <c r="D159" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E159" t="s">
+        <v>393</v>
+      </c>
+      <c r="F159" t="s">
         <v>394</v>
-      </c>
-      <c r="F159" t="s">
-        <v>395</v>
       </c>
       <c r="G159" s="2">
         <v>0</v>
@@ -8175,12 +8169,12 @@
         <v>9.99</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B160" s="1">
         <v>0.3</v>
@@ -8189,13 +8183,13 @@
         <v>0.15</v>
       </c>
       <c r="D160" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E160" t="s">
+        <v>396</v>
+      </c>
+      <c r="F160" t="s">
         <v>397</v>
-      </c>
-      <c r="F160" t="s">
-        <v>398</v>
       </c>
       <c r="G160" s="2">
         <v>0</v>
@@ -8204,12 +8198,12 @@
         <v>9.99</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B161" s="1">
         <v>0.155</v>
@@ -8218,13 +8212,13 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="D161" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E161" t="s">
+        <v>399</v>
+      </c>
+      <c r="F161" t="s">
         <v>400</v>
-      </c>
-      <c r="F161" t="s">
-        <v>401</v>
       </c>
       <c r="G161" s="2">
         <v>14</v>
@@ -8233,12 +8227,12 @@
         <v>46</v>
       </c>
       <c r="I161" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B162" s="1">
         <v>0.18</v>
@@ -8247,13 +8241,13 @@
         <v>0.09</v>
       </c>
       <c r="D162" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E162" t="s">
+        <v>402</v>
+      </c>
+      <c r="F162" t="s">
         <v>403</v>
-      </c>
-      <c r="F162" t="s">
-        <v>404</v>
       </c>
       <c r="G162" s="2">
         <v>17.3</v>
@@ -8262,12 +8256,12 @@
         <v>74.099999999999994</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>902</v>
+        <v>862</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B163" s="1">
         <v>0.33</v>
@@ -8276,13 +8270,13 @@
         <v>0.16500000000000001</v>
       </c>
       <c r="D163" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E163" t="s">
+        <v>405</v>
+      </c>
+      <c r="F163" t="s">
         <v>406</v>
-      </c>
-      <c r="F163" t="s">
-        <v>407</v>
       </c>
       <c r="G163" s="2">
         <v>0.1</v>
@@ -8291,15 +8285,15 @@
         <v>1.99</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="J163" s="6" t="s">
-        <v>903</v>
+        <v>863</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B164" s="1">
         <v>0.4</v>
@@ -8308,13 +8302,13 @@
         <v>0.2</v>
       </c>
       <c r="D164" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E164" t="s">
+        <v>408</v>
+      </c>
+      <c r="F164" t="s">
         <v>409</v>
-      </c>
-      <c r="F164" t="s">
-        <v>410</v>
       </c>
       <c r="G164" s="2">
         <v>0</v>
@@ -8323,15 +8317,15 @@
         <v>0.89</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>816</v>
+        <v>779</v>
       </c>
       <c r="J164" s="6" t="s">
-        <v>886</v>
+        <v>846</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B165" s="1">
         <v>0.32</v>
@@ -8340,13 +8334,13 @@
         <v>0.16</v>
       </c>
       <c r="D165" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F165" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G165" s="2">
         <v>1</v>
@@ -8355,12 +8349,12 @@
         <v>25</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B166" s="1">
         <v>0.13</v>
@@ -8369,13 +8363,13 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="D166" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E166" t="s">
+        <v>414</v>
+      </c>
+      <c r="F166" t="s">
         <v>415</v>
-      </c>
-      <c r="F166" t="s">
-        <v>416</v>
       </c>
       <c r="G166" s="2">
         <v>1.1000000000000001</v>
@@ -8384,12 +8378,12 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>904</v>
+        <v>864</v>
       </c>
       <c r="B167" s="1">
         <v>0.25</v>
@@ -8398,13 +8392,13 @@
         <v>0.125</v>
       </c>
       <c r="D167" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E167" t="s">
+        <v>429</v>
+      </c>
+      <c r="F167" t="s">
         <v>430</v>
-      </c>
-      <c r="F167" t="s">
-        <v>431</v>
       </c>
       <c r="G167" s="2">
         <v>15</v>
@@ -8413,12 +8407,12 @@
         <v>45</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>905</v>
+        <v>865</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B168" s="1">
         <v>0.12</v>
@@ -8427,13 +8421,13 @@
         <v>0.06</v>
       </c>
       <c r="D168" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E168" t="s">
+        <v>431</v>
+      </c>
+      <c r="F168" t="s">
         <v>432</v>
-      </c>
-      <c r="F168" t="s">
-        <v>433</v>
       </c>
       <c r="G168" s="2">
         <v>6.4</v>
@@ -8442,12 +8436,12 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B169" s="1">
         <v>0.3</v>
@@ -8456,10 +8450,10 @@
         <v>0.15</v>
       </c>
       <c r="D169" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E169" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G169" s="2">
         <v>0</v>
@@ -8468,15 +8462,15 @@
         <v>1.99</v>
       </c>
       <c r="I169" s="3" t="s">
-        <v>906</v>
+        <v>866</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>907</v>
+        <v>867</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B170" s="1">
         <v>0.2</v>
@@ -8485,13 +8479,13 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="D170" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E170" t="s">
+        <v>421</v>
+      </c>
+      <c r="F170" t="s">
         <v>422</v>
-      </c>
-      <c r="F170" t="s">
-        <v>423</v>
       </c>
       <c r="G170" s="2">
         <v>20</v>
@@ -8500,12 +8494,12 @@
         <v>40</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B171" s="1">
         <v>0.14000000000000001</v>
@@ -8514,13 +8508,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D171" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E171" t="s">
+        <v>424</v>
+      </c>
+      <c r="F171" t="s">
         <v>425</v>
-      </c>
-      <c r="F171" t="s">
-        <v>426</v>
       </c>
       <c r="G171" s="2">
         <v>0.05</v>
@@ -8529,12 +8523,12 @@
         <v>15</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B172" s="1">
         <v>0.13</v>
@@ -8543,13 +8537,13 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="D172" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E172" t="s">
+        <v>427</v>
+      </c>
+      <c r="F172" t="s">
         <v>428</v>
-      </c>
-      <c r="F172" t="s">
-        <v>429</v>
       </c>
       <c r="G172" s="2">
         <v>2.1</v>
@@ -8558,12 +8552,12 @@
         <v>17.7</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B173" s="1">
         <v>0.4</v>
@@ -8572,13 +8566,13 @@
         <v>0.2</v>
       </c>
       <c r="D173" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E173" t="s">
+        <v>734</v>
+      </c>
+      <c r="F173" t="s">
         <v>735</v>
-      </c>
-      <c r="F173" t="s">
-        <v>736</v>
       </c>
       <c r="G173" s="2">
         <v>1</v>
@@ -8587,12 +8581,12 @@
         <v>15</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>814</v>
+        <v>777</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B174" s="1">
         <v>0.25</v>
@@ -8601,13 +8595,13 @@
         <v>0.125</v>
       </c>
       <c r="D174" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E174" t="s">
+        <v>199</v>
+      </c>
+      <c r="F174" t="s">
         <v>200</v>
-      </c>
-      <c r="F174" t="s">
-        <v>201</v>
       </c>
       <c r="G174" s="2">
         <v>100</v>
@@ -8616,12 +8610,12 @@
         <v>199</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B175" s="1">
         <v>0.05</v>
@@ -8630,13 +8624,13 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="D175" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E175" t="s">
+        <v>468</v>
+      </c>
+      <c r="F175" t="s">
         <v>469</v>
-      </c>
-      <c r="F175" t="s">
-        <v>470</v>
       </c>
       <c r="G175" s="2">
         <v>136</v>
@@ -8645,12 +8639,12 @@
         <v>145</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B176" s="1">
         <v>0.2</v>
@@ -8659,13 +8653,13 @@
         <v>0.1</v>
       </c>
       <c r="D176" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E176" t="s">
+        <v>434</v>
+      </c>
+      <c r="F176" t="s">
         <v>435</v>
-      </c>
-      <c r="F176" t="s">
-        <v>436</v>
       </c>
       <c r="G176" s="2">
         <v>0.01</v>
@@ -8674,12 +8668,12 @@
         <v>0.72</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B177" s="1">
         <v>0.17</v>
@@ -8688,13 +8682,13 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="D177" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E177" t="s">
+        <v>437</v>
+      </c>
+      <c r="F177" t="s">
         <v>438</v>
-      </c>
-      <c r="F177" t="s">
-        <v>439</v>
       </c>
       <c r="G177" s="2">
         <v>0</v>
@@ -8703,12 +8697,12 @@
         <v>0.06</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B178" s="1">
         <v>0.42</v>
@@ -8717,21 +8711,21 @@
         <v>0.21</v>
       </c>
       <c r="D178" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E178" t="s">
+        <v>440</v>
+      </c>
+      <c r="F178" t="s">
         <v>441</v>
       </c>
-      <c r="F178" t="s">
-        <v>442</v>
-      </c>
       <c r="I178" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B179" s="1">
         <v>0.3</v>
@@ -8740,10 +8734,10 @@
         <v>0.15</v>
       </c>
       <c r="D179" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E179" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G179" s="2">
         <v>0</v>
@@ -8752,15 +8746,15 @@
         <v>6.99</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J179" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B180" s="1">
         <v>0.3</v>
@@ -8769,10 +8763,10 @@
         <v>0.15</v>
       </c>
       <c r="D180" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E180" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G180" s="2">
         <v>0</v>
@@ -8781,15 +8775,15 @@
         <v>6.99</v>
       </c>
       <c r="I180" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J180" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B181" s="1">
         <v>0.23</v>
@@ -8798,13 +8792,13 @@
         <v>0.115</v>
       </c>
       <c r="D181" t="s">
+        <v>447</v>
+      </c>
+      <c r="E181" t="s">
         <v>448</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>449</v>
-      </c>
-      <c r="F181" t="s">
-        <v>450</v>
       </c>
       <c r="G181" s="2">
         <v>0</v>
@@ -8813,12 +8807,12 @@
         <v>9.99</v>
       </c>
       <c r="I181" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B182" s="1">
         <v>0.222</v>
@@ -8827,13 +8821,13 @@
         <v>0.111</v>
       </c>
       <c r="D182" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E182" t="s">
+        <v>451</v>
+      </c>
+      <c r="F182" t="s">
         <v>452</v>
-      </c>
-      <c r="F182" t="s">
-        <v>453</v>
       </c>
       <c r="G182" s="2">
         <v>0</v>
@@ -8842,15 +8836,15 @@
         <v>0.79</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J182" s="6" t="s">
-        <v>908</v>
+        <v>868</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B183" s="1">
         <v>0.3</v>
@@ -8859,13 +8853,13 @@
         <v>0.15</v>
       </c>
       <c r="D183" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E183" t="s">
+        <v>454</v>
+      </c>
+      <c r="F183" t="s">
         <v>455</v>
-      </c>
-      <c r="F183" t="s">
-        <v>456</v>
       </c>
       <c r="G183" s="2">
         <v>0</v>
@@ -8874,15 +8868,15 @@
         <v>13.49</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J183" s="6" t="s">
-        <v>909</v>
+        <v>869</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B184" s="1">
         <v>0.3</v>
@@ -8891,13 +8885,13 @@
         <v>0.15</v>
       </c>
       <c r="D184" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E184" t="s">
+        <v>457</v>
+      </c>
+      <c r="F184" t="s">
         <v>458</v>
-      </c>
-      <c r="F184" t="s">
-        <v>459</v>
       </c>
       <c r="G184" s="2">
         <v>0</v>
@@ -8906,15 +8900,15 @@
         <v>0.89</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>816</v>
+        <v>779</v>
       </c>
       <c r="J184" s="6" t="s">
-        <v>910</v>
+        <v>870</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B185" s="1">
         <v>0.3</v>
@@ -8923,10 +8917,10 @@
         <v>0.15</v>
       </c>
       <c r="D185" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E185" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G185" s="2">
         <v>0</v>
@@ -8935,15 +8929,15 @@
         <v>6.99</v>
       </c>
       <c r="I185" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J185" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B186" s="1">
         <v>0.16</v>
@@ -8952,13 +8946,13 @@
         <v>0.08</v>
       </c>
       <c r="D186" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E186" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F186" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G186" s="2">
         <v>34.5</v>
@@ -8967,12 +8961,12 @@
         <v>568.9</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B187" s="1">
         <v>0.16</v>
@@ -8981,13 +8975,13 @@
         <v>0.08</v>
       </c>
       <c r="D187" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E187" t="s">
+        <v>464</v>
+      </c>
+      <c r="F187" t="s">
         <v>465</v>
-      </c>
-      <c r="F187" t="s">
-        <v>466</v>
       </c>
       <c r="G187" s="2">
         <v>20.6</v>
@@ -8996,12 +8990,12 @@
         <v>76.7</v>
       </c>
       <c r="I187" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B188" s="1">
         <v>0.3</v>
@@ -9010,10 +9004,10 @@
         <v>0.15</v>
       </c>
       <c r="D188" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E188" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G188" s="2">
         <v>0</v>
@@ -9022,15 +9016,15 @@
         <v>6.99</v>
       </c>
       <c r="I188" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J188" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B189" s="1">
         <v>0.1</v>
@@ -9039,13 +9033,13 @@
         <v>0.05</v>
       </c>
       <c r="D189" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E189" t="s">
+        <v>736</v>
+      </c>
+      <c r="F189" t="s">
         <v>737</v>
-      </c>
-      <c r="F189" t="s">
-        <v>738</v>
       </c>
       <c r="G189" s="2">
         <v>18</v>
@@ -9054,12 +9048,12 @@
         <v>301</v>
       </c>
       <c r="I189" s="3" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B190" s="1">
         <v>0.18</v>
@@ -9068,13 +9062,13 @@
         <v>0.09</v>
       </c>
       <c r="D190" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E190" t="s">
+        <v>523</v>
+      </c>
+      <c r="F190" t="s">
         <v>524</v>
-      </c>
-      <c r="F190" t="s">
-        <v>525</v>
       </c>
       <c r="G190" s="2">
         <v>16.600000000000001</v>
@@ -9083,12 +9077,12 @@
         <v>48.5</v>
       </c>
       <c r="I190" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B191" s="1">
         <v>0.16</v>
@@ -9097,13 +9091,13 @@
         <v>0.08</v>
       </c>
       <c r="D191" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E191" t="s">
+        <v>471</v>
+      </c>
+      <c r="F191" t="s">
         <v>472</v>
-      </c>
-      <c r="F191" t="s">
-        <v>473</v>
       </c>
       <c r="G191" s="2">
         <v>40.200000000000003</v>
@@ -9112,12 +9106,12 @@
         <v>225</v>
       </c>
       <c r="I191" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B192" s="1">
         <v>0.186</v>
@@ -9126,13 +9120,13 @@
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="D192" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E192" t="s">
+        <v>474</v>
+      </c>
+      <c r="F192" t="s">
         <v>475</v>
-      </c>
-      <c r="F192" t="s">
-        <v>476</v>
       </c>
       <c r="G192" s="2">
         <v>0</v>
@@ -9141,12 +9135,12 @@
         <v>0.99</v>
       </c>
       <c r="I192" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B193" s="1">
         <v>0.15</v>
@@ -9155,13 +9149,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D193" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E193" t="s">
+        <v>477</v>
+      </c>
+      <c r="F193" t="s">
         <v>478</v>
-      </c>
-      <c r="F193" t="s">
-        <v>479</v>
       </c>
       <c r="G193" s="2">
         <v>2.04</v>
@@ -9170,12 +9164,12 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B194" s="1">
         <v>0.24</v>
@@ -9184,13 +9178,13 @@
         <v>0.12</v>
       </c>
       <c r="D194" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E194" t="s">
+        <v>480</v>
+      </c>
+      <c r="F194" t="s">
         <v>481</v>
-      </c>
-      <c r="F194" t="s">
-        <v>482</v>
       </c>
       <c r="G194" s="2">
         <v>0.31</v>
@@ -9199,12 +9193,12 @@
         <v>0.95</v>
       </c>
       <c r="I194" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B195" s="1">
         <v>0.15</v>
@@ -9213,13 +9207,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D195" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E195" t="s">
+        <v>483</v>
+      </c>
+      <c r="F195" t="s">
         <v>484</v>
-      </c>
-      <c r="F195" t="s">
-        <v>485</v>
       </c>
       <c r="G195" s="2">
         <v>80</v>
@@ -9228,12 +9222,12 @@
         <v>200</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B196" s="1">
         <v>0.12</v>
@@ -9242,13 +9236,13 @@
         <v>0.06</v>
       </c>
       <c r="D196" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E196" t="s">
+        <v>486</v>
+      </c>
+      <c r="F196" t="s">
         <v>487</v>
-      </c>
-      <c r="F196" t="s">
-        <v>488</v>
       </c>
       <c r="G196" s="2">
         <v>0.77</v>
@@ -9257,12 +9251,12 @@
         <v>1.68</v>
       </c>
       <c r="I196" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B197" s="1">
         <v>0.15</v>
@@ -9271,13 +9265,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D197" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E197" t="s">
+        <v>489</v>
+      </c>
+      <c r="F197" t="s">
         <v>490</v>
-      </c>
-      <c r="F197" t="s">
-        <v>491</v>
       </c>
       <c r="G197" s="2">
         <v>4.5</v>
@@ -9286,12 +9280,12 @@
         <v>12.1</v>
       </c>
       <c r="I197" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B198" s="1">
         <v>0.192</v>
@@ -9300,13 +9294,13 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="D198" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E198" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F198" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G198" s="2">
         <v>13</v>
@@ -9315,12 +9309,12 @@
         <v>39</v>
       </c>
       <c r="I198" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B199" s="1">
         <v>0.35</v>
@@ -9329,13 +9323,13 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="D199" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E199" t="s">
+        <v>494</v>
+      </c>
+      <c r="F199" t="s">
         <v>495</v>
-      </c>
-      <c r="F199" t="s">
-        <v>496</v>
       </c>
       <c r="G199" s="2">
         <v>193</v>
@@ -9344,12 +9338,12 @@
         <v>740</v>
       </c>
       <c r="I199" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B200" s="1">
         <v>0.2</v>
@@ -9358,13 +9352,13 @@
         <v>0.1</v>
       </c>
       <c r="D200" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E200" t="s">
+        <v>494</v>
+      </c>
+      <c r="F200" t="s">
         <v>495</v>
-      </c>
-      <c r="F200" t="s">
-        <v>496</v>
       </c>
       <c r="G200" s="2">
         <v>193</v>
@@ -9373,12 +9367,12 @@
         <v>740</v>
       </c>
       <c r="I200" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B201" s="1">
         <v>0.2</v>
@@ -9387,13 +9381,13 @@
         <v>0.1</v>
       </c>
       <c r="D201" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E201" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F201" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G201" s="2">
         <v>39</v>
@@ -9402,12 +9396,12 @@
         <v>308</v>
       </c>
       <c r="I201" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B202" s="1">
         <v>0.12</v>
@@ -9416,13 +9410,13 @@
         <v>0.06</v>
       </c>
       <c r="D202" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E202" t="s">
+        <v>18</v>
+      </c>
+      <c r="F202" t="s">
         <v>19</v>
-      </c>
-      <c r="F202" t="s">
-        <v>20</v>
       </c>
       <c r="G202" s="2">
         <v>3.5</v>
@@ -9431,12 +9425,12 @@
         <v>5.2</v>
       </c>
       <c r="I202" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B203" s="1">
         <v>0.2</v>
@@ -9445,13 +9439,13 @@
         <v>0.1</v>
       </c>
       <c r="D203" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E203" t="s">
+        <v>503</v>
+      </c>
+      <c r="F203" t="s">
         <v>504</v>
-      </c>
-      <c r="F203" t="s">
-        <v>505</v>
       </c>
       <c r="G203" s="2">
         <v>3.5</v>
@@ -9460,12 +9454,12 @@
         <v>77</v>
       </c>
       <c r="I203" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B204" s="1">
         <v>0.23</v>
@@ -9474,13 +9468,13 @@
         <v>0.115</v>
       </c>
       <c r="D204" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E204" t="s">
+        <v>506</v>
+      </c>
+      <c r="F204" t="s">
         <v>507</v>
-      </c>
-      <c r="F204" t="s">
-        <v>508</v>
       </c>
       <c r="G204" s="2">
         <v>0</v>
@@ -9489,15 +9483,15 @@
         <v>0.99</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="J204" s="6" t="s">
-        <v>911</v>
+        <v>871</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B205" s="1">
         <v>0.153</v>
@@ -9506,13 +9500,13 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="D205" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E205" t="s">
+        <v>509</v>
+      </c>
+      <c r="F205" t="s">
         <v>510</v>
-      </c>
-      <c r="F205" t="s">
-        <v>511</v>
       </c>
       <c r="G205" s="2">
         <v>0</v>
@@ -9521,15 +9515,15 @@
         <v>0.79</v>
       </c>
       <c r="I205" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J205" s="6" t="s">
-        <v>912</v>
+        <v>872</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B206" s="1">
         <v>0.2</v>
@@ -9538,13 +9532,13 @@
         <v>0.1</v>
       </c>
       <c r="D206" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E206" t="s">
+        <v>95</v>
+      </c>
+      <c r="F206" t="s">
         <v>96</v>
-      </c>
-      <c r="F206" t="s">
-        <v>97</v>
       </c>
       <c r="G206" s="2">
         <v>0</v>
@@ -9553,12 +9547,12 @@
         <v>1.75</v>
       </c>
       <c r="I206" s="3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B207" s="1">
         <v>0.25</v>
@@ -9567,13 +9561,13 @@
         <v>0.125</v>
       </c>
       <c r="D207" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E207" t="s">
+        <v>376</v>
+      </c>
+      <c r="F207" t="s">
         <v>377</v>
-      </c>
-      <c r="F207" t="s">
-        <v>378</v>
       </c>
       <c r="G207" s="2">
         <v>13</v>
@@ -9582,12 +9576,12 @@
         <v>60</v>
       </c>
       <c r="I207" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B208" s="1">
         <v>0.35</v>
@@ -9596,13 +9590,13 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="D208" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E208" t="s">
+        <v>21</v>
+      </c>
+      <c r="F208" t="s">
         <v>22</v>
-      </c>
-      <c r="F208" t="s">
-        <v>23</v>
       </c>
       <c r="G208" s="2">
         <v>0</v>
@@ -9611,12 +9605,12 @@
         <v>7.6</v>
       </c>
       <c r="I208" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B209" s="1">
         <v>0.11</v>
@@ -9625,13 +9619,13 @@
         <v>5.5E-2</v>
       </c>
       <c r="D209" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E209" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F209" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G209" s="2">
         <v>0.27</v>
@@ -9640,12 +9634,12 @@
         <v>4.2</v>
       </c>
       <c r="I209" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B210" s="1">
         <v>0.3</v>
@@ -9654,13 +9648,13 @@
         <v>0.15</v>
       </c>
       <c r="D210" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E210" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F210" t="s">
-        <v>913</v>
+        <v>873</v>
       </c>
       <c r="G210" s="2">
         <v>0</v>
@@ -9669,15 +9663,15 @@
         <v>6.99</v>
       </c>
       <c r="I210" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J210" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B211" s="1">
         <v>0.3</v>
@@ -9686,13 +9680,13 @@
         <v>0.15</v>
       </c>
       <c r="D211" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E211" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F211" t="s">
-        <v>914</v>
+        <v>874</v>
       </c>
       <c r="G211" s="2">
         <v>0</v>
@@ -9701,15 +9695,15 @@
         <v>6.99</v>
       </c>
       <c r="I211" s="3" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="J211" s="7" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B212" s="1">
         <v>0.2</v>
@@ -9718,13 +9712,13 @@
         <v>0.1</v>
       </c>
       <c r="D212" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E212" t="s">
+        <v>48</v>
+      </c>
+      <c r="F212" t="s">
         <v>49</v>
-      </c>
-      <c r="F212" t="s">
-        <v>50</v>
       </c>
       <c r="G212" s="2">
         <v>20</v>
@@ -9733,12 +9727,12 @@
         <v>200</v>
       </c>
       <c r="I212" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B213" s="1">
         <v>0.221</v>
@@ -9747,13 +9741,13 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="D213" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E213" t="s">
+        <v>739</v>
+      </c>
+      <c r="F213" t="s">
         <v>740</v>
-      </c>
-      <c r="F213" t="s">
-        <v>741</v>
       </c>
       <c r="G213" s="2">
         <v>12</v>
@@ -9762,12 +9756,12 @@
         <v>20</v>
       </c>
       <c r="I213" s="3" t="s">
-        <v>815</v>
+        <v>778</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B214" s="1">
         <v>0.3</v>
@@ -9776,13 +9770,13 @@
         <v>0.15</v>
       </c>
       <c r="D214" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E214" t="s">
+        <v>526</v>
+      </c>
+      <c r="F214" t="s">
         <v>527</v>
-      </c>
-      <c r="F214" t="s">
-        <v>528</v>
       </c>
       <c r="G214" s="2">
         <v>0</v>
@@ -9791,12 +9785,12 @@
         <v>150</v>
       </c>
       <c r="I214" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B215" s="1">
         <v>0.3</v>
@@ -9805,13 +9799,13 @@
         <v>0.15</v>
       </c>
       <c r="D215" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E215" t="s">
+        <v>529</v>
+      </c>
+      <c r="F215" t="s">
         <v>530</v>
-      </c>
-      <c r="F215" t="s">
-        <v>531</v>
       </c>
       <c r="G215" s="2">
         <v>0</v>
@@ -9820,15 +9814,15 @@
         <v>0.89</v>
       </c>
       <c r="I215" s="3" t="s">
-        <v>816</v>
+        <v>779</v>
       </c>
       <c r="J215" s="6" t="s">
-        <v>886</v>
+        <v>846</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B216" s="1">
         <v>0.2</v>
@@ -9837,13 +9831,13 @@
         <v>0.1</v>
       </c>
       <c r="D216" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E216" t="s">
+        <v>532</v>
+      </c>
+      <c r="F216" t="s">
         <v>533</v>
-      </c>
-      <c r="F216" t="s">
-        <v>534</v>
       </c>
       <c r="G216" s="2">
         <v>197</v>
@@ -9852,12 +9846,12 @@
         <v>771</v>
       </c>
       <c r="I216" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B217" s="1">
         <v>0.25</v>
@@ -9866,13 +9860,13 @@
         <v>0.125</v>
       </c>
       <c r="D217" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E217" t="s">
+        <v>535</v>
+      </c>
+      <c r="F217" t="s">
         <v>536</v>
-      </c>
-      <c r="F217" t="s">
-        <v>537</v>
       </c>
       <c r="G217" s="2">
         <v>20</v>
@@ -9881,12 +9875,12 @@
         <v>100</v>
       </c>
       <c r="I217" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B218" s="1">
         <v>0.3</v>
@@ -9895,13 +9889,13 @@
         <v>0.15</v>
       </c>
       <c r="D218" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E218" t="s">
+        <v>538</v>
+      </c>
+      <c r="F218" t="s">
         <v>539</v>
-      </c>
-      <c r="F218" t="s">
-        <v>540</v>
       </c>
       <c r="G218" s="2">
         <v>19.899999999999999</v>
@@ -9910,12 +9904,12 @@
         <v>79.3</v>
       </c>
       <c r="I218" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B219" s="1">
         <v>0.25</v>
@@ -9924,13 +9918,13 @@
         <v>0.125</v>
       </c>
       <c r="D219" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E219" t="s">
+        <v>257</v>
+      </c>
+      <c r="F219" t="s">
         <v>258</v>
-      </c>
-      <c r="F219" t="s">
-        <v>259</v>
       </c>
       <c r="G219" s="2">
         <v>205</v>
@@ -9939,12 +9933,12 @@
         <v>285</v>
       </c>
       <c r="I219" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>828</v>
+        <v>788</v>
       </c>
       <c r="B220" s="5">
         <v>5.5E-2</v>
@@ -9953,13 +9947,13 @@
         <v>0.01</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E220" t="s">
-        <v>851</v>
+        <v>811</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>828</v>
+        <v>788</v>
       </c>
       <c r="G220" s="2">
         <v>4</v>
@@ -9974,7 +9968,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>829</v>
+        <v>789</v>
       </c>
       <c r="B221" s="5">
         <v>0.12</v>
@@ -9983,13 +9977,13 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E221" t="s">
-        <v>852</v>
+        <v>812</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>829</v>
+        <v>789</v>
       </c>
       <c r="G221" s="2">
         <v>4</v>
@@ -10004,7 +9998,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>830</v>
+        <v>790</v>
       </c>
       <c r="B222" s="5">
         <v>0.17499999999999999</v>
@@ -10013,13 +10007,13 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E222" t="s">
-        <v>853</v>
+        <v>813</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>830</v>
+        <v>790</v>
       </c>
       <c r="G222" s="2">
         <v>1.48</v>
@@ -10034,7 +10028,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>831</v>
+        <v>791</v>
       </c>
       <c r="B223" s="5">
         <v>0.17599999999999999</v>
@@ -10043,13 +10037,13 @@
         <v>6.3E-2</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E223" t="s">
-        <v>854</v>
+        <v>814</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>831</v>
+        <v>791</v>
       </c>
       <c r="G223" s="2">
         <v>0.74</v>
@@ -10064,7 +10058,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>832</v>
+        <v>792</v>
       </c>
       <c r="B224" s="5">
         <v>0.27900000000000003</v>
@@ -10073,13 +10067,13 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E224" t="s">
-        <v>855</v>
+        <v>815</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>832</v>
+        <v>792</v>
       </c>
       <c r="G224" s="2">
         <v>0.37</v>
@@ -10094,7 +10088,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>833</v>
+        <v>793</v>
       </c>
       <c r="B225" s="5">
         <v>0.29699999999999999</v>
@@ -10103,13 +10097,13 @@
         <v>0.17299999999999999</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E225" t="s">
-        <v>856</v>
+        <v>816</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>833</v>
+        <v>793</v>
       </c>
       <c r="G225" s="2">
         <v>0</v>
@@ -10124,7 +10118,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>834</v>
+        <v>794</v>
       </c>
       <c r="B226" s="5">
         <v>0.27300000000000002</v>
@@ -10133,13 +10127,13 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E226" t="s">
-        <v>857</v>
+        <v>817</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>834</v>
+        <v>794</v>
       </c>
       <c r="G226" s="2">
         <v>0</v>
@@ -10154,7 +10148,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>835</v>
+        <v>795</v>
       </c>
       <c r="B227" s="5">
         <v>0.13439999999999999</v>
@@ -10163,13 +10157,13 @@
         <v>6.7199999999999996E-2</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E227" t="s">
-        <v>871</v>
+        <v>831</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>835</v>
+        <v>795</v>
       </c>
       <c r="G227" s="2">
         <v>130</v>
@@ -10184,7 +10178,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>836</v>
+        <v>796</v>
       </c>
       <c r="B228" s="5">
         <v>0.14979999999999999</v>
@@ -10193,13 +10187,13 @@
         <v>7.4899999999999994E-2</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E228" t="s">
-        <v>858</v>
+        <v>818</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>836</v>
+        <v>796</v>
       </c>
       <c r="G228" s="2">
         <v>0.9</v>
@@ -10214,7 +10208,7 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>837</v>
+        <v>797</v>
       </c>
       <c r="B229" s="5">
         <v>0.22800000000000001</v>
@@ -10223,13 +10217,13 @@
         <v>0.108</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E229" t="s">
-        <v>859</v>
+        <v>819</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>837</v>
+        <v>797</v>
       </c>
       <c r="G229" s="2">
         <v>0.59</v>
@@ -10244,7 +10238,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>838</v>
+        <v>798</v>
       </c>
       <c r="B230" s="5">
         <v>0.627</v>
@@ -10253,13 +10247,13 @@
         <v>0.20069999999999999</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E230" t="s">
-        <v>860</v>
+        <v>820</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>838</v>
+        <v>798</v>
       </c>
       <c r="G230" s="2">
         <v>1.57</v>
@@ -10274,7 +10268,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>839</v>
+        <v>799</v>
       </c>
       <c r="B231" s="5">
         <v>5.8000000000000003E-2</v>
@@ -10283,13 +10277,13 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E231" t="s">
-        <v>861</v>
+        <v>821</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>839</v>
+        <v>799</v>
       </c>
       <c r="G231" s="2">
         <v>13</v>
@@ -10304,7 +10298,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>840</v>
+        <v>800</v>
       </c>
       <c r="B232" s="5">
         <v>7.5200000000000003E-2</v>
@@ -10313,13 +10307,13 @@
         <v>3.7600000000000001E-2</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E232" t="s">
-        <v>862</v>
+        <v>822</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>840</v>
+        <v>800</v>
       </c>
       <c r="G232" s="2">
         <v>30.6</v>
@@ -10334,7 +10328,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>841</v>
+        <v>801</v>
       </c>
       <c r="B233" s="5">
         <v>0.15</v>
@@ -10343,13 +10337,13 @@
         <v>5.74E-2</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E233" t="s">
-        <v>863</v>
+        <v>823</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>841</v>
+        <v>801</v>
       </c>
       <c r="G233" s="2">
         <v>0</v>
@@ -10364,7 +10358,7 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>842</v>
+        <v>802</v>
       </c>
       <c r="B234" s="5">
         <v>0.2979</v>
@@ -10373,20 +10367,20 @@
         <v>0.1</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E234" t="s">
-        <v>864</v>
+        <v>824</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>842</v>
+        <v>802</v>
       </c>
       <c r="G234"/>
       <c r="H234"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>843</v>
+        <v>803</v>
       </c>
       <c r="B235" s="5">
         <v>5.8000000000000003E-2</v>
@@ -10395,13 +10389,13 @@
         <v>2.3E-2</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E235" t="s">
-        <v>865</v>
+        <v>825</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>843</v>
+        <v>803</v>
       </c>
       <c r="G235" s="2">
         <v>36</v>
@@ -10416,7 +10410,7 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>844</v>
+        <v>804</v>
       </c>
       <c r="B236" s="5">
         <v>0.06</v>
@@ -10425,13 +10419,13 @@
         <v>1.6E-2</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E236" t="s">
-        <v>866</v>
+        <v>826</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>844</v>
+        <v>804</v>
       </c>
       <c r="G236" s="2">
         <v>80</v>
@@ -10446,7 +10440,7 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>845</v>
+        <v>805</v>
       </c>
       <c r="B237" s="5">
         <v>5.5E-2</v>
@@ -10455,13 +10449,13 @@
         <v>0.02</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E237" t="s">
-        <v>867</v>
+        <v>827</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>845</v>
+        <v>805</v>
       </c>
       <c r="G237" s="2">
         <v>26.8</v>
@@ -10476,7 +10470,7 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>846</v>
+        <v>806</v>
       </c>
       <c r="B238" s="5">
         <v>7.4999999999999997E-2</v>
@@ -10485,13 +10479,13 @@
         <v>1.6E-2</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E238" t="s">
-        <v>868</v>
+        <v>828</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>846</v>
+        <v>806</v>
       </c>
       <c r="G238" s="2">
         <v>30</v>
@@ -10506,7 +10500,7 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>847</v>
+        <v>807</v>
       </c>
       <c r="B239" s="5">
         <v>4.5600000000000002E-2</v>
@@ -10515,13 +10509,13 @@
         <v>1.17E-2</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E239" t="s">
-        <v>869</v>
+        <v>829</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>847</v>
+        <v>807</v>
       </c>
       <c r="G239" s="2">
         <v>11</v>
@@ -10536,7 +10530,7 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="B240" s="5">
         <v>0.16</v>
@@ -10545,13 +10539,13 @@
         <v>0.05</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E240" t="s">
-        <v>870</v>
+        <v>830</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="G240" s="2">
         <v>130</v>
@@ -10566,7 +10560,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="B241" s="5">
         <v>8.7999999999999995E-2</v>
@@ -10575,13 +10569,13 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E241" t="s">
-        <v>872</v>
+        <v>832</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="G241" s="2">
         <v>6.8</v>
@@ -10596,7 +10590,7 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B242" s="5">
         <v>0.05</v>
@@ -10605,13 +10599,13 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E242" t="s">
-        <v>873</v>
+        <v>833</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>849</v>
+        <v>809</v>
       </c>
       <c r="G242" s="2">
         <v>0</v>
@@ -10624,7 +10618,7 @@
         <v>0 - 5,69</v>
       </c>
       <c r="J242" s="6" t="s">
-        <v>915</v>
+        <v>875</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
@@ -10815,7 +10809,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4341AA7A-BE9E-402B-8B8E-1C6E7BF75419}">
-  <dimension ref="A1:A89"/>
+  <dimension ref="A1:A87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -10823,447 +10817,437 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>812</v>
+        <v>775</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>762</v>
+        <v>877</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>807</v>
+        <v>770</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>808</v>
+        <v>771</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>811</v>
+        <v>774</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>825</v>
+        <v>878</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>826</v>
+        <v>879</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>827</v>
+        <v>880</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>766</v>
+        <v>881</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>767</v>
+        <v>882</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>783</v>
+        <v>883</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>768</v>
+        <v>884</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>784</v>
+        <v>885</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>769</v>
+        <v>886</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>785</v>
+        <v>887</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>770</v>
+        <v>888</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>786</v>
+        <v>889</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>771</v>
+        <v>890</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>787</v>
+        <v>891</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>772</v>
+        <v>892</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>788</v>
+        <v>893</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>773</v>
+        <v>894</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>789</v>
+        <v>895</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>774</v>
+        <v>896</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>790</v>
+        <v>897</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>775</v>
+        <v>898</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>791</v>
+        <v>899</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>776</v>
+        <v>900</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>777</v>
+        <v>901</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>778</v>
+        <v>902</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>792</v>
+        <v>903</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>779</v>
+        <v>904</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>793</v>
+        <v>905</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>794</v>
+        <v>906</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>795</v>
+        <v>907</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>796</v>
+        <v>908</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>797</v>
+        <v>909</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>780</v>
+        <v>910</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>798</v>
+        <v>911</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>799</v>
+        <v>912</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>800</v>
+        <v>913</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>801</v>
+        <v>914</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>802</v>
+        <v>284</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>285</v>
+        <v>149</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>150</v>
+        <v>772</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>809</v>
+        <v>773</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>810</v>
+        <v>764</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>2</v>
+        <v>766</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>803</v>
+        <v>767</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>782</v>
+        <v>768</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>804</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>805</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>51</v>
+        <v>769</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>88</v>
+      <c r="A80" s="4" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>806</v>
+      <c r="A81" s="4" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>817</v>
+        <v>782</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>818</v>
+        <v>783</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>819</v>
+        <v>784</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>820</v>
+        <v>785</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>821</v>
+        <v>786</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>824</v>
+        <v>787</v>
       </c>
     </row>
   </sheetData>

--- a/Base de Dados.xlsx
+++ b/Base de Dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcello.coutinho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D7F4802-8EA1-474D-BB64-84FE0A21A0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E72D585-A627-413B-B45B-1DB49FF0F846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{052EBD17-0308-4E6D-95A6-CA02714B48B2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="952">
   <si>
     <t>Bias MÃ¡ximo</t>
   </si>
@@ -2876,6 +2876,24 @@
   </si>
   <si>
     <t>ACL TOP 3</t>
+  </si>
+  <si>
+    <t>3,52 - 4,81</t>
+  </si>
+  <si>
+    <t>0,18 - 0,32</t>
+  </si>
+  <si>
+    <t>0,46 - 0,80</t>
+  </si>
+  <si>
+    <t>0,30 - 0,52</t>
+  </si>
+  <si>
+    <t>0,23 - 0,46</t>
+  </si>
+  <si>
+    <t>0,63 - 1,51</t>
   </si>
 </sst>
 </file>
@@ -4019,13 +4037,13 @@
         <v>19</v>
       </c>
       <c r="G8" s="1">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="H8" s="1">
-        <v>5.2</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>537</v>
+        <v>946</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -4131,8 +4149,14 @@
       <c r="E12" t="s">
         <v>28</v>
       </c>
+      <c r="G12" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.32</v>
+      </c>
       <c r="I12" s="2" t="s">
-        <v>541</v>
+        <v>947</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -4180,8 +4204,14 @@
       <c r="E14" t="s">
         <v>32</v>
       </c>
+      <c r="G14" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.8</v>
+      </c>
       <c r="I14" s="2" t="s">
-        <v>541</v>
+        <v>948</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -5035,8 +5065,14 @@
       <c r="E44" t="s">
         <v>112</v>
       </c>
+      <c r="G44" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0.52</v>
+      </c>
       <c r="I44" s="2" t="s">
-        <v>541</v>
+        <v>949</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -5055,8 +5091,14 @@
       <c r="E45" t="s">
         <v>113</v>
       </c>
+      <c r="G45" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0.46</v>
+      </c>
       <c r="I45" s="2" t="s">
-        <v>541</v>
+        <v>950</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -6764,8 +6806,14 @@
       <c r="E103" t="s">
         <v>258</v>
       </c>
+      <c r="G103" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="H103" s="1">
+        <v>1.51</v>
+      </c>
       <c r="I103" s="2" t="s">
-        <v>541</v>
+        <v>951</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">

--- a/Base de Dados.xlsx
+++ b/Base de Dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcello.coutinho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E72D585-A627-413B-B45B-1DB49FF0F846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD815F1F-00F4-4930-9C84-2B2E8AC81C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{052EBD17-0308-4E6D-95A6-CA02714B48B2}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Equipamentos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base de Dados'!$A$1:$I$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base de Dados'!$A$1:$J$278</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Equipamentos!$A$5:$A$81</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="1065">
   <si>
     <t>Bias MÃ¡ximo</t>
   </si>
@@ -982,9 +982,6 @@
     <t>htlviii</t>
   </si>
   <si>
-    <t>HTLV</t>
-  </si>
-  <si>
     <t>Kappa</t>
   </si>
   <si>
@@ -2149,9 +2146,6 @@
     <t>AURUIS</t>
   </si>
   <si>
-    <t>CAUIS</t>
-  </si>
-  <si>
     <t>100 - 300</t>
   </si>
   <si>
@@ -2894,6 +2888,351 @@
   </si>
   <si>
     <t>0,63 - 1,51</t>
+  </si>
+  <si>
+    <t>AINSUL</t>
+  </si>
+  <si>
+    <t>Descricao</t>
+  </si>
+  <si>
+    <t>LIPOPROTEINA A</t>
+  </si>
+  <si>
+    <t>ACIDO URICO</t>
+  </si>
+  <si>
+    <t>ALBUMINA</t>
+  </si>
+  <si>
+    <t>FATOR REUMATOIDE</t>
+  </si>
+  <si>
+    <t>FERRO</t>
+  </si>
+  <si>
+    <t>AMILASE</t>
+  </si>
+  <si>
+    <t>HOMOCISTEINA</t>
+  </si>
+  <si>
+    <t>CALCIO</t>
+  </si>
+  <si>
+    <t>LDL DOSADO</t>
+  </si>
+  <si>
+    <t>CLORO</t>
+  </si>
+  <si>
+    <t>TRANSFERRINA</t>
+  </si>
+  <si>
+    <t>TRIGLICERIDEOS</t>
+  </si>
+  <si>
+    <t>CREATININA</t>
+  </si>
+  <si>
+    <t>FOSFORO</t>
+  </si>
+  <si>
+    <t>CAPACIDADE LATENTE DE LIGACAO DE FERRO</t>
+  </si>
+  <si>
+    <t>COLESTEROL TOTAL</t>
+  </si>
+  <si>
+    <t>GLICOSE</t>
+  </si>
+  <si>
+    <t>FOSFATASE ALCALINA</t>
+  </si>
+  <si>
+    <t>GAMA GLUTAMIL TRANSFERASE</t>
+  </si>
+  <si>
+    <t>HDL COLESTEROL</t>
+  </si>
+  <si>
+    <t>ULTRA PCR</t>
+  </si>
+  <si>
+    <t>MAGNESIO</t>
+  </si>
+  <si>
+    <t>POTASSIO</t>
+  </si>
+  <si>
+    <t>CKMB - CREATINOFOSFOQUINASE MB ISOENZIMA</t>
+  </si>
+  <si>
+    <t>PROTEINAS TOTAIS</t>
+  </si>
+  <si>
+    <t>SODIO</t>
+  </si>
+  <si>
+    <t>UREIA</t>
+  </si>
+  <si>
+    <t>LIPASE</t>
+  </si>
+  <si>
+    <t>ALDOLASE</t>
+  </si>
+  <si>
+    <t>FRUTOSAMINA</t>
+  </si>
+  <si>
+    <t>ACIDO FOLICO</t>
+  </si>
+  <si>
+    <t>HIV2 - COBAS</t>
+  </si>
+  <si>
+    <t>AMH - ANTI-MULLERIANO</t>
+  </si>
+  <si>
+    <t>ANDROSTENEDIONA</t>
+  </si>
+  <si>
+    <t>ATG - ANTICORPOS ANTI TIREOGLOBULINA</t>
+  </si>
+  <si>
+    <t>ANTI-TPO (ANTICORPO ANTIPEROXIDASE)</t>
+  </si>
+  <si>
+    <t>CMV IgG Avidity</t>
+  </si>
+  <si>
+    <t>TIREOGLOBULINA</t>
+  </si>
+  <si>
+    <t>ANTI-CCP</t>
+  </si>
+  <si>
+    <t>ESTRADIOL</t>
+  </si>
+  <si>
+    <t>FERRITINA</t>
+  </si>
+  <si>
+    <t>FSH-HORMONIO FOLICULO ESTIMULANTE</t>
+  </si>
+  <si>
+    <t>INSULINA BASAL</t>
+  </si>
+  <si>
+    <t>LH - HORMONIO LUTEINIZANTE</t>
+  </si>
+  <si>
+    <t>PROGESTERONA</t>
+  </si>
+  <si>
+    <t>PSA LIVRE</t>
+  </si>
+  <si>
+    <t>PSA TOTAL</t>
+  </si>
+  <si>
+    <t>VDRL - QT</t>
+  </si>
+  <si>
+    <t>T3L HORMÃ”NIO TRIIODOTIRONINA LIVRE</t>
+  </si>
+  <si>
+    <t>T3 HORMÃ”NIO TRIIODOTIRONINA</t>
+  </si>
+  <si>
+    <t>T4T HORMÃ”NIO TIROXINA</t>
+  </si>
+  <si>
+    <t>TESTOSTERONA TOTAL</t>
+  </si>
+  <si>
+    <t>TSH - TIREOESTIMULANTE</t>
+  </si>
+  <si>
+    <t>VITD25</t>
+  </si>
+  <si>
+    <t>ALFA-1 GLICOPROTEINA ACIDA</t>
+  </si>
+  <si>
+    <t>ACIDO URICO - URINA ISOLADA</t>
+  </si>
+  <si>
+    <t>AMILASE URINA ISOLADA</t>
+  </si>
+  <si>
+    <t>CLORO - AMOSTRA ISOLADA</t>
+  </si>
+  <si>
+    <t>C3 COMPLEMENTO</t>
+  </si>
+  <si>
+    <t>C4 COMPLEMENTO</t>
+  </si>
+  <si>
+    <t>CORTISOL 8 HORAS</t>
+  </si>
+  <si>
+    <t>CREATININA URINARIA ISOLADA</t>
+  </si>
+  <si>
+    <t>FOSFORO URINA ISOLADA</t>
+  </si>
+  <si>
+    <t>MAGNESIO URINA ISOLADA</t>
+  </si>
+  <si>
+    <t>POTASSIO URINA ISOLADA</t>
+  </si>
+  <si>
+    <t>MICROALBUMINA URINA ISOLADA</t>
+  </si>
+  <si>
+    <t>PROTEINA URINARIA</t>
+  </si>
+  <si>
+    <t>PROLACTINA</t>
+  </si>
+  <si>
+    <t>PROTEINA URINA ISOLADA</t>
+  </si>
+  <si>
+    <t>SODIO URINA ISOLADA</t>
+  </si>
+  <si>
+    <t>UREIA URINA ISOLADA</t>
+  </si>
+  <si>
+    <t>ACTH - HORMÃ”NIO ADRENOCORTICOTRÃ“FICO</t>
+  </si>
+  <si>
+    <t>GH - HORMÃ”NIO DE CRESCIMENTO</t>
+  </si>
+  <si>
+    <t>IGFBP3 - PROTEINA LIGADORA - 3 IgF</t>
+  </si>
+  <si>
+    <t>SOMATOMEDINA - IGF-1</t>
+  </si>
+  <si>
+    <t>GLOBULINA LIGADORA DE TIROXINA</t>
+  </si>
+  <si>
+    <t>ALDOSTERONA</t>
+  </si>
+  <si>
+    <t>BORRÃ‰LIA IGG</t>
+  </si>
+  <si>
+    <t>BORRÃ‰LIA IGM</t>
+  </si>
+  <si>
+    <t>CALPROTECTINA</t>
+  </si>
+  <si>
+    <t>CAXUMBA IGG</t>
+  </si>
+  <si>
+    <t>CAXUMBA IGM</t>
+  </si>
+  <si>
+    <t>H. PYLORI FEZES</t>
+  </si>
+  <si>
+    <t>HERPES IGG</t>
+  </si>
+  <si>
+    <t>HERPES IGM</t>
+  </si>
+  <si>
+    <t>MICOPLASMA IGG</t>
+  </si>
+  <si>
+    <t>MICOPLASMA IGM</t>
+  </si>
+  <si>
+    <t>PARVOVÃRUS IGG</t>
+  </si>
+  <si>
+    <t>PARVOVÃRUS IGM</t>
+  </si>
+  <si>
+    <t>SARAMPO IGG</t>
+  </si>
+  <si>
+    <t>SARAMPO IGM</t>
+  </si>
+  <si>
+    <t>VARICELA IGG</t>
+  </si>
+  <si>
+    <t>VARICELA IGM</t>
+  </si>
+  <si>
+    <t>VITAMINA D 1.25</t>
+  </si>
+  <si>
+    <t>ANTI INSULINA</t>
+  </si>
+  <si>
+    <t>ANTI ILHOTA</t>
+  </si>
+  <si>
+    <t>CERULOPLASMINA</t>
+  </si>
+  <si>
+    <t>HAPTOGLOBINA</t>
+  </si>
+  <si>
+    <t>APOA1</t>
+  </si>
+  <si>
+    <t>CPK - CREATINA FOSFOQUINASE</t>
+  </si>
+  <si>
+    <t>CK</t>
+  </si>
+  <si>
+    <t>CALCIO IONICO</t>
+  </si>
+  <si>
+    <t>CISTATINA C</t>
+  </si>
+  <si>
+    <t>KAPPA LIVRE</t>
+  </si>
+  <si>
+    <t>ALFA 1 ANTI-TRIPSINA (SORO)</t>
+  </si>
+  <si>
+    <t>INIBIDOR C1 ESTERASE QUANTITATIVO</t>
+  </si>
+  <si>
+    <t>PRÃ‰-ALBUMINA</t>
+  </si>
+  <si>
+    <t>CAUI</t>
+  </si>
+  <si>
+    <t>CALCIO - URINA ISOLADA</t>
+  </si>
+  <si>
+    <t>AMMO</t>
+  </si>
+  <si>
+    <t>HTLV - QT</t>
+  </si>
+  <si>
+    <t>HTLV_QT</t>
+  </si>
+  <si>
+    <t>HBGLI (c513)</t>
   </si>
 </sst>
 </file>
@@ -3468,6 +3807,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}" name="Equipamentos" displayName="Equipamentos" ref="A1:A90" totalsRowShown="0">
   <autoFilter ref="A1:A90" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}"/>
@@ -3798,7 +4141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9E839D1-D9BB-491F-96EB-30E6182BBB70}">
-  <dimension ref="A1:J278"/>
+  <dimension ref="A1:K278"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -3806,17 +4149,18 @@
     <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
@@ -3830,20 +4174,23 @@
       <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
+        <v>951</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J1" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>245</v>
       </c>
@@ -3862,19 +4209,22 @@
       <c r="F2" t="s">
         <v>247</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2" s="1">
         <v>3.89</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>26.8</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J2" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B3" s="4">
         <v>0.3</v>
@@ -3886,24 +4236,27 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
+        <v>368</v>
+      </c>
+      <c r="F3" t="s">
         <v>369</v>
       </c>
-      <c r="F3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>952</v>
+      </c>
+      <c r="H3" s="1">
         <v>1</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>75</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J3" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B4" s="4">
         <v>0.15</v>
@@ -3920,17 +4273,20 @@
       <c r="F4" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>953</v>
+      </c>
+      <c r="H4" s="1">
         <v>3.4</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>7</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J4" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -3949,17 +4305,20 @@
       <c r="F5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H5" s="1">
         <v>5</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>46</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J5" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
@@ -3978,17 +4337,20 @@
       <c r="F6" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>983</v>
+      </c>
+      <c r="H6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>0.99</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J6" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>114</v>
       </c>
@@ -4007,19 +4369,22 @@
       <c r="F7" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H7" s="1">
         <v>0.09</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>0.3</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B8" s="4">
         <v>6.0999999999999999E-2</v>
@@ -4036,17 +4401,20 @@
       <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>954</v>
+      </c>
+      <c r="H8" s="1">
         <v>3.52</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>4.8099999999999996</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="2" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>236</v>
       </c>
@@ -4065,17 +4433,20 @@
       <c r="F9" t="s">
         <v>238</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>955</v>
+      </c>
+      <c r="H9" s="1">
         <v>1</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>14</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
@@ -4094,19 +4465,22 @@
       <c r="F10" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H10" s="1">
         <v>2.52</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>39.200000000000003</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B11" s="4">
         <v>0.18</v>
@@ -4123,19 +4497,22 @@
       <c r="F11" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H11" s="1">
         <v>90</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>200</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B12" s="4">
         <v>0.2</v>
@@ -4149,17 +4526,20 @@
       <c r="E12" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>540</v>
+      </c>
+      <c r="H12" s="1">
         <v>0.18</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>0.32</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="2" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -4178,19 +4558,22 @@
       <c r="F13" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H13" s="1">
         <v>58</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>155</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B14" s="4">
         <v>0.2</v>
@@ -4204,17 +4587,20 @@
       <c r="E14" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>540</v>
+      </c>
+      <c r="H14" s="1">
         <v>0.46</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>0.8</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="2" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
@@ -4233,17 +4619,20 @@
       <c r="F15" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="1">
         <v>0</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>5.8</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>36</v>
       </c>
@@ -4262,17 +4651,20 @@
       <c r="F16" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>984</v>
+      </c>
+      <c r="H16" s="1">
         <v>0.01</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>2.71</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>242</v>
       </c>
@@ -4291,19 +4683,22 @@
       <c r="F17" t="s">
         <v>244</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>956</v>
+      </c>
+      <c r="H17" s="1">
         <v>33</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <v>193</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B18" s="4">
         <v>0.19400000000000001</v>
@@ -4315,22 +4710,25 @@
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F18" t="s">
-        <v>702</v>
-      </c>
-      <c r="G18" s="1">
+        <v>701</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H18" s="1">
         <v>15</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
         <v>99</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
@@ -4347,19 +4745,22 @@
         <v>42</v>
       </c>
       <c r="F19" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G19" t="s">
         <v>43</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>19</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <v>54</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>44</v>
       </c>
@@ -4378,19 +4779,22 @@
       <c r="F20" t="s">
         <v>46</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" t="s">
+        <v>985</v>
+      </c>
+      <c r="H20" s="1">
         <v>0.19</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
         <v>1.07</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B21" s="4">
         <v>0.3</v>
@@ -4407,19 +4811,22 @@
       <c r="F21" t="s">
         <v>40</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" t="s">
+        <v>957</v>
+      </c>
+      <c r="H21" s="1">
         <v>28</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
         <v>100</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J21" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B22" s="4">
         <v>0.3</v>
@@ -4436,17 +4843,20 @@
       <c r="F22" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="1">
         <v>0</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <v>9.99</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>53</v>
       </c>
@@ -4465,17 +4875,20 @@
       <c r="F23" t="s">
         <v>55</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="1">
         <v>0</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <v>0.99</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>56</v>
       </c>
@@ -4494,17 +4907,20 @@
       <c r="F24" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" t="s">
+        <v>58</v>
+      </c>
+      <c r="H24" s="1">
         <v>1.01</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
         <v>60</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>59</v>
       </c>
@@ -4523,20 +4939,23 @@
       <c r="F25" t="s">
         <v>61</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" s="1">
         <v>0</v>
       </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
         <v>0.89</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>62</v>
       </c>
@@ -4555,17 +4974,20 @@
       <c r="F26" t="s">
         <v>64</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" s="1">
         <v>1.01</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <v>60</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>65</v>
       </c>
@@ -4584,17 +5006,20 @@
       <c r="F27" t="s">
         <v>67</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" t="s">
+        <v>67</v>
+      </c>
+      <c r="H27" s="1">
         <v>1.01</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
         <v>60</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>68</v>
       </c>
@@ -4613,17 +5038,20 @@
       <c r="F28" t="s">
         <v>70</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="1">
         <v>0</v>
       </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
         <v>9.99</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>71</v>
       </c>
@@ -4642,20 +5070,23 @@
       <c r="F29" t="s">
         <v>73</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H29" s="1">
         <v>0</v>
       </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
         <v>0.89</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J29" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>74</v>
       </c>
@@ -4674,17 +5105,20 @@
       <c r="F30" t="s">
         <v>76</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H30" s="1">
         <v>3</v>
       </c>
-      <c r="H30" s="1">
+      <c r="I30" s="1">
         <v>28</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J30" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>77</v>
       </c>
@@ -4701,21 +5135,24 @@
         <v>78</v>
       </c>
       <c r="F31" t="s">
-        <v>79</v>
-      </c>
-      <c r="G31" s="1">
+        <v>950</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H31" s="1">
         <v>2.6</v>
       </c>
-      <c r="H31" s="1">
+      <c r="I31" s="1">
         <v>24.9</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J31" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B32" s="4">
         <v>0.3</v>
@@ -4732,19 +5169,22 @@
       <c r="F32" t="s">
         <v>92</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H32" s="1">
         <v>0</v>
       </c>
-      <c r="H32" s="1">
+      <c r="I32" s="1">
         <v>114</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J32" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B33" s="4">
         <v>0.22</v>
@@ -4761,17 +5201,20 @@
       <c r="F33" t="s">
         <v>94</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33" t="s">
+        <v>987</v>
+      </c>
+      <c r="H33" s="1">
         <v>0</v>
       </c>
-      <c r="H33" s="1">
+      <c r="I33" s="1">
         <v>33</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J33" s="2" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>80</v>
       </c>
@@ -4788,19 +5231,22 @@
         <v>81</v>
       </c>
       <c r="F34" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G34" t="s">
         <v>82</v>
       </c>
-      <c r="G34" s="1">
+      <c r="H34" s="1">
         <v>46</v>
       </c>
-      <c r="H34" s="1">
+      <c r="I34" s="1">
         <v>304</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J34" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>83</v>
       </c>
@@ -4819,17 +5265,20 @@
       <c r="F35" t="s">
         <v>85</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G35" t="s">
+        <v>85</v>
+      </c>
+      <c r="H35" s="1">
         <v>46</v>
       </c>
-      <c r="H35" s="1">
+      <c r="I35" s="1">
         <v>174</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J35" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>86</v>
       </c>
@@ -4845,20 +5294,23 @@
       <c r="E36" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36" t="s">
+        <v>540</v>
+      </c>
+      <c r="H36" s="1">
         <v>0</v>
       </c>
-      <c r="H36" s="1">
+      <c r="I36" s="1">
         <v>6.99</v>
       </c>
-      <c r="I36" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J36" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>89</v>
       </c>
@@ -4874,20 +5326,23 @@
       <c r="E37" t="s">
         <v>90</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" t="s">
+        <v>540</v>
+      </c>
+      <c r="H37" s="1">
         <v>0</v>
       </c>
-      <c r="H37" s="1">
+      <c r="I37" s="1">
         <v>6.99</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J37" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>96</v>
       </c>
@@ -4906,11 +5361,14 @@
       <c r="F38" t="s">
         <v>98</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G38" t="s">
+        <v>988</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>99</v>
       </c>
@@ -4929,11 +5387,14 @@
       <c r="F39" t="s">
         <v>101</v>
       </c>
-      <c r="I39" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G39" t="s">
+        <v>101</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>102</v>
       </c>
@@ -4949,20 +5410,23 @@
       <c r="E40" t="s">
         <v>103</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G40" t="s">
+        <v>540</v>
+      </c>
+      <c r="H40" s="1">
         <v>0</v>
       </c>
-      <c r="H40" s="1">
+      <c r="I40" s="1">
         <v>6.99</v>
       </c>
-      <c r="I40" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J40" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>104</v>
       </c>
@@ -4978,20 +5442,23 @@
       <c r="E41" t="s">
         <v>105</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G41" t="s">
+        <v>540</v>
+      </c>
+      <c r="H41" s="1">
         <v>0</v>
       </c>
-      <c r="H41" s="1">
+      <c r="I41" s="1">
         <v>6.99</v>
       </c>
-      <c r="I41" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J41" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>106</v>
       </c>
@@ -5010,17 +5477,20 @@
       <c r="F42" t="s">
         <v>108</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42" t="s">
+        <v>989</v>
+      </c>
+      <c r="H42" s="1">
         <v>3.5</v>
       </c>
-      <c r="H42" s="1">
+      <c r="I42" s="1">
         <v>77</v>
       </c>
-      <c r="I42" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J42" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>109</v>
       </c>
@@ -5039,19 +5509,22 @@
       <c r="F43" t="s">
         <v>111</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G43" t="s">
+        <v>111</v>
+      </c>
+      <c r="H43" s="1">
         <v>0.12</v>
       </c>
-      <c r="H43" s="1">
+      <c r="I43" s="1">
         <v>0.78</v>
       </c>
-      <c r="I43" s="2" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J43" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B44" s="4">
         <v>0.15</v>
@@ -5065,19 +5538,22 @@
       <c r="E44" t="s">
         <v>112</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G44" t="s">
+        <v>540</v>
+      </c>
+      <c r="H44" s="1">
         <v>0.3</v>
       </c>
-      <c r="H44" s="1">
+      <c r="I44" s="1">
         <v>0.52</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J44" s="2" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B45" s="4">
         <v>0.12</v>
@@ -5091,17 +5567,20 @@
       <c r="E45" t="s">
         <v>113</v>
       </c>
-      <c r="G45" s="1">
+      <c r="G45" t="s">
+        <v>540</v>
+      </c>
+      <c r="H45" s="1">
         <v>0.23</v>
       </c>
-      <c r="H45" s="1">
+      <c r="I45" s="1">
         <v>0.46</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J45" s="2" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>293</v>
       </c>
@@ -5120,19 +5599,22 @@
       <c r="F46" t="s">
         <v>295</v>
       </c>
-      <c r="G46" s="1">
+      <c r="G46" t="s">
+        <v>295</v>
+      </c>
+      <c r="H46" s="1">
         <v>0</v>
       </c>
-      <c r="H46" s="1">
+      <c r="I46" s="1">
         <v>5</v>
       </c>
-      <c r="I46" s="2" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J46" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B47" s="4">
         <v>0.19400000000000001</v>
@@ -5144,22 +5626,25 @@
         <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F47" t="s">
-        <v>701</v>
-      </c>
-      <c r="G47" s="1">
+        <v>700</v>
+      </c>
+      <c r="G47" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H47" s="1">
         <v>0</v>
       </c>
-      <c r="H47" s="1">
+      <c r="I47" s="1">
         <v>650</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J47" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>309</v>
       </c>
@@ -5178,17 +5663,20 @@
       <c r="F48" t="s">
         <v>311</v>
       </c>
-      <c r="G48" s="1">
+      <c r="G48" t="s">
+        <v>958</v>
+      </c>
+      <c r="H48" s="1">
         <v>3</v>
       </c>
-      <c r="H48" s="1">
+      <c r="I48" s="1">
         <v>15</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J48" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>120</v>
       </c>
@@ -5207,17 +5695,20 @@
       <c r="F49" t="s">
         <v>122</v>
       </c>
-      <c r="G49" s="1">
+      <c r="G49" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H49" s="1">
         <v>0</v>
       </c>
-      <c r="H49" s="1">
+      <c r="I49" s="1">
         <v>10</v>
       </c>
-      <c r="I49" s="2" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J49" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>123</v>
       </c>
@@ -5236,19 +5727,22 @@
       <c r="F50" t="s">
         <v>125</v>
       </c>
-      <c r="G50" s="1">
+      <c r="G50" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H50" s="1">
         <v>0</v>
       </c>
-      <c r="H50" s="1">
+      <c r="I50" s="1">
         <v>0.9</v>
       </c>
-      <c r="I50" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J50" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B51" s="4">
         <v>0.155</v>
@@ -5265,17 +5759,20 @@
       <c r="F51" t="s">
         <v>127</v>
       </c>
-      <c r="G51" s="1">
+      <c r="G51" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H51" s="1">
         <v>21</v>
       </c>
-      <c r="H51" s="1">
+      <c r="I51" s="1">
         <v>39</v>
       </c>
-      <c r="I51" s="2" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J51" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>128</v>
       </c>
@@ -5294,17 +5791,20 @@
       <c r="F52" t="s">
         <v>130</v>
       </c>
-      <c r="G52" s="1">
+      <c r="G52" t="s">
+        <v>130</v>
+      </c>
+      <c r="H52" s="1">
         <v>0</v>
       </c>
-      <c r="H52" s="1">
+      <c r="I52" s="1">
         <v>35</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J52" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>131</v>
       </c>
@@ -5323,17 +5823,20 @@
       <c r="F53" t="s">
         <v>133</v>
       </c>
-      <c r="G53" s="1">
+      <c r="G53" t="s">
+        <v>133</v>
+      </c>
+      <c r="H53" s="1">
         <v>0</v>
       </c>
-      <c r="H53" s="1">
+      <c r="I53" s="1">
         <v>28.5</v>
       </c>
-      <c r="I53" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J53" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>134</v>
       </c>
@@ -5352,17 +5855,20 @@
       <c r="F54" t="s">
         <v>136</v>
       </c>
-      <c r="G54" s="1">
+      <c r="G54" t="s">
+        <v>136</v>
+      </c>
+      <c r="H54" s="1">
         <v>0</v>
       </c>
-      <c r="H54" s="1">
+      <c r="I54" s="1">
         <v>34</v>
       </c>
-      <c r="I54" s="2" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J54" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>137</v>
       </c>
@@ -5381,17 +5887,20 @@
       <c r="F55" t="s">
         <v>139</v>
       </c>
-      <c r="G55" s="1">
+      <c r="G55" t="s">
+        <v>139</v>
+      </c>
+      <c r="H55" s="1">
         <v>0</v>
       </c>
-      <c r="H55" s="1">
+      <c r="I55" s="1">
         <v>25</v>
       </c>
-      <c r="I55" s="2" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J55" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>140</v>
       </c>
@@ -5410,19 +5919,22 @@
       <c r="F56" t="s">
         <v>142</v>
       </c>
-      <c r="G56" s="1">
+      <c r="G56" t="s">
+        <v>142</v>
+      </c>
+      <c r="H56" s="1">
         <v>0</v>
       </c>
-      <c r="H56" s="1">
+      <c r="I56" s="1">
         <v>6.9</v>
       </c>
-      <c r="I56" s="2" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J56" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B57" s="4">
         <v>0.3</v>
@@ -5434,24 +5946,27 @@
         <v>9</v>
       </c>
       <c r="E57" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F57" t="s">
-        <v>357</v>
-      </c>
-      <c r="G57" s="1">
+        <v>356</v>
+      </c>
+      <c r="G57" t="s">
+        <v>356</v>
+      </c>
+      <c r="H57" s="1">
         <v>135</v>
       </c>
-      <c r="H57" s="1">
+      <c r="I57" s="1">
         <v>225</v>
       </c>
-      <c r="I57" s="2" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J57" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B58" s="4">
         <v>0.15</v>
@@ -5468,17 +5983,20 @@
       <c r="F58" t="s">
         <v>144</v>
       </c>
-      <c r="G58" s="1">
+      <c r="G58" t="s">
+        <v>959</v>
+      </c>
+      <c r="H58" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="H58" s="1">
+      <c r="I58" s="1">
         <v>9.6</v>
       </c>
-      <c r="I58" s="2" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J58" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>145</v>
       </c>
@@ -5497,17 +6015,20 @@
       <c r="F59" t="s">
         <v>148</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G59" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H59" s="1">
         <v>1</v>
       </c>
-      <c r="H59" s="1">
+      <c r="I59" s="1">
         <v>1.4</v>
       </c>
-      <c r="I59" s="2" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J59" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>149</v>
       </c>
@@ -5526,17 +6047,20 @@
       <c r="F60" t="s">
         <v>151</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G60" t="s">
+        <v>151</v>
+      </c>
+      <c r="H60" s="1">
         <v>0</v>
       </c>
-      <c r="H60" s="1">
+      <c r="I60" s="1">
         <v>14.3</v>
       </c>
-      <c r="I60" s="2" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J60" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>152</v>
       </c>
@@ -5555,19 +6079,22 @@
       <c r="F61" t="s">
         <v>155</v>
       </c>
-      <c r="G61" s="1">
+      <c r="G61" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H61" s="1">
         <v>0</v>
       </c>
-      <c r="H61" s="1">
+      <c r="I61" s="1">
         <v>50</v>
       </c>
-      <c r="I61" s="2" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J61" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B62" s="4">
         <v>0.3</v>
@@ -5579,22 +6106,25 @@
         <v>9</v>
       </c>
       <c r="E62" t="s">
+        <v>359</v>
+      </c>
+      <c r="F62" t="s">
         <v>360</v>
       </c>
-      <c r="F62" t="s">
-        <v>361</v>
-      </c>
-      <c r="G62" s="1">
+      <c r="G62" t="s">
+        <v>960</v>
+      </c>
+      <c r="H62" s="1">
         <v>30</v>
       </c>
-      <c r="H62" s="1">
+      <c r="I62" s="1">
         <v>130</v>
       </c>
-      <c r="I62" s="2" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J62" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>156</v>
       </c>
@@ -5613,20 +6143,20 @@
       <c r="F63" t="s">
         <v>158</v>
       </c>
-      <c r="G63" s="1">
+      <c r="H63" s="1">
         <v>0</v>
       </c>
-      <c r="H63" s="1">
+      <c r="I63" s="1">
         <v>13.99</v>
       </c>
-      <c r="I63" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="J63" s="5" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J63" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>159</v>
       </c>
@@ -5645,20 +6175,20 @@
       <c r="F64" t="s">
         <v>158</v>
       </c>
-      <c r="G64" s="1">
+      <c r="H64" s="1">
         <v>0</v>
       </c>
-      <c r="H64" s="1">
+      <c r="I64" s="1">
         <v>9.99</v>
       </c>
-      <c r="I64" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J64" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>161</v>
       </c>
@@ -5677,20 +6207,20 @@
       <c r="F65" t="s">
         <v>158</v>
       </c>
-      <c r="G65" s="1">
+      <c r="H65" s="1">
         <v>0</v>
       </c>
-      <c r="H65" s="1">
+      <c r="I65" s="1">
         <v>9.99</v>
       </c>
-      <c r="I65" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="J65" s="7" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J65" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>163</v>
       </c>
@@ -5709,20 +6239,23 @@
       <c r="F66" t="s">
         <v>165</v>
       </c>
-      <c r="G66" s="1">
+      <c r="G66" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H66" s="1">
         <v>0</v>
       </c>
-      <c r="H66" s="1">
+      <c r="I66" s="1">
         <v>8.99</v>
       </c>
-      <c r="I66" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J66" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>166</v>
       </c>
@@ -5741,20 +6274,23 @@
       <c r="F67" t="s">
         <v>168</v>
       </c>
-      <c r="G67" s="1">
+      <c r="G67" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H67" s="1">
         <v>0</v>
       </c>
-      <c r="H67" s="1">
+      <c r="I67" s="1">
         <v>0.89</v>
       </c>
-      <c r="I67" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="J67" s="5" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J67" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>169</v>
       </c>
@@ -5773,20 +6309,23 @@
       <c r="F68" t="s">
         <v>169</v>
       </c>
-      <c r="G68" s="1">
+      <c r="G68" t="s">
+        <v>990</v>
+      </c>
+      <c r="H68" s="1">
         <v>0</v>
       </c>
-      <c r="H68" s="1">
+      <c r="I68" s="1">
         <v>6.99</v>
       </c>
-      <c r="I68" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J68" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J68" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>171</v>
       </c>
@@ -5805,17 +6344,20 @@
       <c r="F69" t="s">
         <v>171</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G69" t="s">
+        <v>171</v>
+      </c>
+      <c r="H69" s="1">
         <v>0.3</v>
       </c>
-      <c r="H69" s="1">
+      <c r="I69" s="1">
         <v>3.8</v>
       </c>
-      <c r="I69" s="2" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J69" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>173</v>
       </c>
@@ -5834,17 +6376,20 @@
       <c r="F70" t="s">
         <v>175</v>
       </c>
-      <c r="G70" s="1">
+      <c r="G70" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H70" s="1">
         <v>20</v>
       </c>
-      <c r="H70" s="1">
+      <c r="I70" s="1">
         <v>60</v>
       </c>
-      <c r="I70" s="2" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J70" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>176</v>
       </c>
@@ -5863,17 +6408,20 @@
       <c r="F71" t="s">
         <v>178</v>
       </c>
-      <c r="G71" s="1">
+      <c r="G71" t="s">
+        <v>178</v>
+      </c>
+      <c r="H71" s="1">
         <v>0</v>
       </c>
-      <c r="H71" s="1">
+      <c r="I71" s="1">
         <v>0.99</v>
       </c>
-      <c r="I71" s="2" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J71" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>179</v>
       </c>
@@ -5892,19 +6440,22 @@
       <c r="F72" t="s">
         <v>181</v>
       </c>
-      <c r="G72" s="1">
+      <c r="G72" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H72" s="1">
         <v>0.62</v>
       </c>
-      <c r="H72" s="1">
+      <c r="I72" s="1">
         <v>1.1100000000000001</v>
       </c>
-      <c r="I72" s="2" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J72" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B73" s="4">
         <v>0.25</v>
@@ -5916,24 +6467,27 @@
         <v>6</v>
       </c>
       <c r="E73" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F73" t="s">
-        <v>703</v>
-      </c>
-      <c r="G73" s="1">
+        <v>1059</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H73" s="1">
         <v>100</v>
       </c>
-      <c r="H73" s="1">
+      <c r="I73" s="1">
         <v>300</v>
       </c>
-      <c r="I73" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J73" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B74" s="4">
         <v>0.13</v>
@@ -5950,19 +6504,22 @@
       <c r="F74" t="s">
         <v>185</v>
       </c>
-      <c r="G74" s="1">
+      <c r="G74" t="s">
+        <v>961</v>
+      </c>
+      <c r="H74" s="1">
         <v>98</v>
       </c>
-      <c r="H74" s="1">
+      <c r="I74" s="1">
         <v>107</v>
       </c>
-      <c r="I74" s="2" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J74" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B75" s="4">
         <v>0.1</v>
@@ -5974,22 +6531,25 @@
         <v>6</v>
       </c>
       <c r="E75" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="F75" t="s">
-        <v>705</v>
-      </c>
-      <c r="G75" s="1">
+        <v>703</v>
+      </c>
+      <c r="G75" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H75" s="1">
         <v>110</v>
       </c>
-      <c r="H75" s="1">
+      <c r="I75" s="1">
         <v>250</v>
       </c>
-      <c r="I75" s="2" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J75" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>186</v>
       </c>
@@ -6008,20 +6568,23 @@
       <c r="F76" t="s">
         <v>188</v>
       </c>
-      <c r="G76" s="1">
+      <c r="G76" t="s">
+        <v>188</v>
+      </c>
+      <c r="H76" s="1">
         <v>0</v>
       </c>
-      <c r="H76" s="1">
+      <c r="I76" s="1">
         <v>0.49</v>
       </c>
-      <c r="I76" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="J76" s="5" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J76" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="K76" s="5" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>189</v>
       </c>
@@ -6040,22 +6603,25 @@
       <c r="F77" t="s">
         <v>191</v>
       </c>
-      <c r="G77" s="1">
+      <c r="G77" t="s">
+        <v>191</v>
+      </c>
+      <c r="H77" s="1">
         <v>0</v>
       </c>
-      <c r="H77" s="1">
+      <c r="I77" s="1">
         <v>0.69</v>
       </c>
-      <c r="I77" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="J77" s="5" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J77" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="K77" s="5" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B78" s="4">
         <v>0.4</v>
@@ -6067,24 +6633,27 @@
         <v>9</v>
       </c>
       <c r="E78" t="s">
+        <v>487</v>
+      </c>
+      <c r="F78" t="s">
         <v>488</v>
       </c>
-      <c r="F78" t="s">
-        <v>489</v>
-      </c>
-      <c r="G78" s="1">
+      <c r="G78" t="s">
+        <v>488</v>
+      </c>
+      <c r="H78" s="1">
         <v>5</v>
       </c>
-      <c r="H78" s="1">
+      <c r="I78" s="1">
         <v>41</v>
       </c>
-      <c r="I78" s="2" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J78" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B79" s="4">
         <v>0.2</v>
@@ -6096,24 +6665,27 @@
         <v>9</v>
       </c>
       <c r="E79" t="s">
+        <v>499</v>
+      </c>
+      <c r="F79" t="s">
         <v>500</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
+        <v>962</v>
+      </c>
+      <c r="H79" s="1">
+        <v>200</v>
+      </c>
+      <c r="I79" s="1">
+        <v>360</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="G79" s="1">
-        <v>200</v>
-      </c>
-      <c r="H79" s="1">
-        <v>360</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="B80" s="4">
         <v>0.16</v>
@@ -6125,22 +6697,25 @@
         <v>9</v>
       </c>
       <c r="E80" t="s">
+        <v>502</v>
+      </c>
+      <c r="F80" t="s">
         <v>503</v>
       </c>
-      <c r="F80" t="s">
-        <v>504</v>
-      </c>
-      <c r="G80" s="1">
+      <c r="G80" t="s">
+        <v>963</v>
+      </c>
+      <c r="H80" s="1">
         <v>50</v>
       </c>
-      <c r="H80" s="1">
+      <c r="I80" s="1">
         <v>150</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J80" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>198</v>
       </c>
@@ -6159,17 +6734,20 @@
       <c r="F81" t="s">
         <v>200</v>
       </c>
-      <c r="G81" s="1">
+      <c r="G81" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H81" s="1">
         <v>90</v>
       </c>
-      <c r="H81" s="1">
+      <c r="I81" s="1">
         <v>170</v>
       </c>
-      <c r="I81" s="2" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J81" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>201</v>
       </c>
@@ -6188,17 +6766,20 @@
       <c r="F82" t="s">
         <v>203</v>
       </c>
-      <c r="G82" s="1">
+      <c r="G82" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H82" s="1">
         <v>12</v>
       </c>
-      <c r="H82" s="1">
+      <c r="I82" s="1">
         <v>36</v>
       </c>
-      <c r="I82" s="2" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J82" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>204</v>
       </c>
@@ -6215,19 +6796,22 @@
         <v>206</v>
       </c>
       <c r="F83" t="s">
-        <v>531</v>
-      </c>
-      <c r="G83" s="1">
+        <v>530</v>
+      </c>
+      <c r="G83" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H83" s="1">
         <v>5.27</v>
       </c>
-      <c r="H83" s="1">
+      <c r="I83" s="1">
         <v>22.45</v>
       </c>
-      <c r="I83" s="2" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J83" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>207</v>
       </c>
@@ -6246,19 +6830,22 @@
       <c r="F84" t="s">
         <v>210</v>
       </c>
-      <c r="G84" s="1">
+      <c r="G84" t="s">
+        <v>210</v>
+      </c>
+      <c r="H84" s="1">
         <v>1.5</v>
       </c>
-      <c r="H84" s="1">
+      <c r="I84" s="1">
         <v>20.29</v>
       </c>
-      <c r="I84" s="2" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J84" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B85" s="4">
         <v>0.2</v>
@@ -6275,19 +6862,22 @@
       <c r="F85" t="s">
         <v>214</v>
       </c>
-      <c r="G85" s="1">
+      <c r="G85" t="s">
+        <v>964</v>
+      </c>
+      <c r="H85" s="1">
         <v>0.67</v>
       </c>
-      <c r="H85" s="1">
+      <c r="I85" s="1">
         <v>1.17</v>
       </c>
-      <c r="I85" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J85" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B86" s="4">
         <v>0.25</v>
@@ -6299,24 +6889,27 @@
         <v>9</v>
       </c>
       <c r="E86" t="s">
+        <v>528</v>
+      </c>
+      <c r="F86" t="s">
         <v>529</v>
       </c>
-      <c r="F86" t="s">
-        <v>530</v>
-      </c>
-      <c r="G86" s="1">
+      <c r="G86" t="s">
+        <v>529</v>
+      </c>
+      <c r="H86" s="1">
         <v>80</v>
       </c>
-      <c r="H86" s="1">
+      <c r="I86" s="1">
         <v>120</v>
       </c>
-      <c r="I86" s="2" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J86" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B87" s="4">
         <v>0.3</v>
@@ -6328,22 +6921,25 @@
         <v>6</v>
       </c>
       <c r="E87" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F87" t="s">
-        <v>711</v>
-      </c>
-      <c r="G87" s="1">
+        <v>709</v>
+      </c>
+      <c r="G87" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H87" s="1">
         <v>39</v>
       </c>
-      <c r="H87" s="1">
+      <c r="I87" s="1">
         <v>259</v>
       </c>
-      <c r="I87" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J87" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>217</v>
       </c>
@@ -6362,20 +6958,20 @@
       <c r="F88" t="s">
         <v>217</v>
       </c>
-      <c r="G88" s="1">
+      <c r="H88" s="1">
         <v>0</v>
       </c>
-      <c r="H88" s="1">
+      <c r="I88" s="1">
         <v>9.99</v>
       </c>
-      <c r="I88" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="J88" s="7" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J88" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="K88" s="7" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>219</v>
       </c>
@@ -6394,17 +6990,20 @@
       <c r="F89" t="s">
         <v>221</v>
       </c>
-      <c r="G89" s="1">
+      <c r="G89" t="s">
+        <v>221</v>
+      </c>
+      <c r="H89" s="1">
         <v>0</v>
       </c>
-      <c r="H89" s="1">
+      <c r="I89" s="1">
         <v>200</v>
       </c>
-      <c r="I89" s="2" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J89" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>222</v>
       </c>
@@ -6423,20 +7022,23 @@
       <c r="F90" t="s">
         <v>224</v>
       </c>
-      <c r="G90" s="1">
+      <c r="G90" t="s">
+        <v>224</v>
+      </c>
+      <c r="H90" s="1">
         <v>0</v>
       </c>
-      <c r="H90" s="1">
+      <c r="I90" s="1">
         <v>0.69</v>
       </c>
-      <c r="I90" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J90" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="K90" s="5" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>225</v>
       </c>
@@ -6455,20 +7057,23 @@
       <c r="F91" t="s">
         <v>227</v>
       </c>
-      <c r="G91" s="1">
+      <c r="G91" t="s">
+        <v>227</v>
+      </c>
+      <c r="H91" s="1">
         <v>0</v>
       </c>
-      <c r="H91" s="1">
+      <c r="I91" s="1">
         <v>0.59</v>
       </c>
-      <c r="I91" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="J91" s="5" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J91" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="K91" s="5" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>228</v>
       </c>
@@ -6487,17 +7092,20 @@
       <c r="F92" t="s">
         <v>230</v>
       </c>
-      <c r="G92" s="1">
+      <c r="G92" t="s">
+        <v>991</v>
+      </c>
+      <c r="H92" s="1">
         <v>5</v>
       </c>
-      <c r="H92" s="1">
+      <c r="I92" s="1">
         <v>138</v>
       </c>
-      <c r="I92" s="2" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J92" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>231</v>
       </c>
@@ -6516,17 +7124,20 @@
       <c r="F93" t="s">
         <v>233</v>
       </c>
-      <c r="G93" s="1">
+      <c r="G93" t="s">
+        <v>233</v>
+      </c>
+      <c r="H93" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H93" s="1">
+      <c r="I93" s="1">
         <v>12</v>
       </c>
-      <c r="I93" s="2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J93" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>234</v>
       </c>
@@ -6543,24 +7154,24 @@
         <v>235</v>
       </c>
       <c r="F94" t="s">
-        <v>841</v>
-      </c>
-      <c r="G94" s="1">
+        <v>839</v>
+      </c>
+      <c r="H94" s="1">
         <v>0</v>
       </c>
-      <c r="H94" s="1">
+      <c r="I94" s="1">
         <v>6.99</v>
       </c>
-      <c r="I94" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J94" s="5" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J94" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K94" s="5" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B95" s="4">
         <v>0.2</v>
@@ -6577,17 +7188,20 @@
       <c r="F95" t="s">
         <v>252</v>
       </c>
-      <c r="G95" s="1">
+      <c r="G95" t="s">
+        <v>965</v>
+      </c>
+      <c r="H95" s="1">
         <v>2.5</v>
       </c>
-      <c r="H95" s="1">
+      <c r="I95" s="1">
         <v>4.5</v>
       </c>
-      <c r="I95" s="2" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J95" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>239</v>
       </c>
@@ -6606,17 +7220,20 @@
       <c r="F96" t="s">
         <v>241</v>
       </c>
-      <c r="G96" s="1">
+      <c r="G96" t="s">
+        <v>992</v>
+      </c>
+      <c r="H96" s="1">
         <v>34</v>
       </c>
-      <c r="H96" s="1">
+      <c r="I96" s="1">
         <v>500</v>
       </c>
-      <c r="I96" s="2" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J96" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>117</v>
       </c>
@@ -6635,19 +7252,22 @@
       <c r="F97" t="s">
         <v>119</v>
       </c>
-      <c r="G97" s="1">
+      <c r="G97" t="s">
+        <v>119</v>
+      </c>
+      <c r="H97" s="1">
         <v>0.3</v>
       </c>
-      <c r="H97" s="1">
+      <c r="I97" s="1">
         <v>1.2</v>
       </c>
-      <c r="I97" s="2" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J97" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B98" s="4">
         <v>0.3</v>
@@ -6664,17 +7284,20 @@
       <c r="F98" t="s">
         <v>216</v>
       </c>
-      <c r="G98" s="1">
+      <c r="G98" t="s">
+        <v>966</v>
+      </c>
+      <c r="H98" s="1">
         <v>125</v>
       </c>
-      <c r="H98" s="1">
+      <c r="I98" s="1">
         <v>345</v>
       </c>
-      <c r="I98" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J98" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>195</v>
       </c>
@@ -6693,19 +7316,22 @@
       <c r="F99" t="s">
         <v>197</v>
       </c>
-      <c r="G99" s="1">
+      <c r="G99" t="s">
+        <v>967</v>
+      </c>
+      <c r="H99" s="1">
         <v>100</v>
       </c>
-      <c r="H99" s="1">
+      <c r="I99" s="1">
         <v>199</v>
       </c>
-      <c r="I99" s="2" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J99" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B100" s="4">
         <v>0.3</v>
@@ -6717,24 +7343,27 @@
         <v>6</v>
       </c>
       <c r="E100" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="F100" t="s">
+        <v>711</v>
+      </c>
+      <c r="G100" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H100" s="1">
+        <v>40</v>
+      </c>
+      <c r="I100" s="1">
+        <v>150</v>
+      </c>
+      <c r="J100" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="G100" s="1">
-        <v>40</v>
-      </c>
-      <c r="H100" s="1">
-        <v>150</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B101" s="4">
         <v>0.13</v>
@@ -6751,17 +7380,20 @@
       <c r="F101" t="s">
         <v>272</v>
       </c>
-      <c r="G101" s="1">
+      <c r="G101" t="s">
+        <v>968</v>
+      </c>
+      <c r="H101" s="1">
         <v>70</v>
       </c>
-      <c r="H101" s="1">
+      <c r="I101" s="1">
         <v>99</v>
       </c>
-      <c r="I101" s="2" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J101" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>256</v>
       </c>
@@ -6780,19 +7412,22 @@
       <c r="F102" t="s">
         <v>256</v>
       </c>
-      <c r="G102" s="1">
+      <c r="G102" t="s">
+        <v>993</v>
+      </c>
+      <c r="H102" s="1">
         <v>25.8</v>
       </c>
-      <c r="H102" s="1">
+      <c r="I102" s="1">
         <v>134.80000000000001</v>
       </c>
-      <c r="I102" s="2" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J102" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B103" s="4">
         <v>0.12</v>
@@ -6806,17 +7441,20 @@
       <c r="E103" t="s">
         <v>258</v>
       </c>
-      <c r="G103" s="1">
+      <c r="G103" t="s">
+        <v>540</v>
+      </c>
+      <c r="H103" s="1">
         <v>0.63</v>
       </c>
-      <c r="H103" s="1">
+      <c r="I103" s="1">
         <v>1.51</v>
       </c>
-      <c r="I103" s="2" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J103" s="2" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>259</v>
       </c>
@@ -6835,17 +7473,20 @@
       <c r="F104" t="s">
         <v>262</v>
       </c>
-      <c r="G104" s="1">
+      <c r="G104" t="s">
+        <v>262</v>
+      </c>
+      <c r="H104" s="1">
         <v>13</v>
       </c>
-      <c r="H104" s="1">
+      <c r="I104" s="1">
         <v>115</v>
       </c>
-      <c r="I104" s="2" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J104" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>248</v>
       </c>
@@ -6864,17 +7505,20 @@
       <c r="F105" t="s">
         <v>250</v>
       </c>
-      <c r="G105" s="1">
+      <c r="G105" t="s">
+        <v>969</v>
+      </c>
+      <c r="H105" s="1">
         <v>40</v>
       </c>
-      <c r="H105" s="1">
+      <c r="I105" s="1">
         <v>129</v>
       </c>
-      <c r="I105" s="2" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J105" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>265</v>
       </c>
@@ -6893,17 +7537,20 @@
       <c r="F106" t="s">
         <v>265</v>
       </c>
-      <c r="G106" s="1">
+      <c r="G106" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H106" s="1">
         <v>0</v>
       </c>
-      <c r="H106" s="1">
+      <c r="I106" s="1">
         <v>3</v>
       </c>
-      <c r="I106" s="2" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J106" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>267</v>
       </c>
@@ -6919,20 +7566,23 @@
       <c r="E107" t="s">
         <v>268</v>
       </c>
-      <c r="G107" s="1">
+      <c r="G107" t="s">
+        <v>540</v>
+      </c>
+      <c r="H107" s="1">
         <v>0</v>
       </c>
-      <c r="H107" s="1">
+      <c r="I107" s="1">
         <v>6.99</v>
       </c>
-      <c r="I107" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J107" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J107" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K107" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>269</v>
       </c>
@@ -6948,22 +7598,25 @@
       <c r="E108" t="s">
         <v>270</v>
       </c>
-      <c r="G108" s="1">
+      <c r="G108" t="s">
+        <v>540</v>
+      </c>
+      <c r="H108" s="1">
         <v>0</v>
       </c>
-      <c r="H108" s="1">
+      <c r="I108" s="1">
         <v>6.99</v>
       </c>
-      <c r="I108" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J108" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J108" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K108" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B109" s="4">
         <v>0.12</v>
@@ -6972,7 +7625,7 @@
         <v>0.06</v>
       </c>
       <c r="D109" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E109" t="s">
         <v>271</v>
@@ -6980,17 +7633,20 @@
       <c r="F109" t="s">
         <v>272</v>
       </c>
-      <c r="G109" s="1">
+      <c r="G109" t="s">
+        <v>968</v>
+      </c>
+      <c r="H109" s="1">
         <v>70</v>
       </c>
-      <c r="H109" s="1">
+      <c r="I109" s="1">
         <v>99</v>
       </c>
-      <c r="I109" s="2" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J109" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>263</v>
       </c>
@@ -7009,19 +7665,22 @@
       <c r="F110" t="s">
         <v>263</v>
       </c>
-      <c r="G110" s="1">
+      <c r="G110" t="s">
+        <v>970</v>
+      </c>
+      <c r="H110" s="1">
         <v>0</v>
       </c>
-      <c r="H110" s="1">
+      <c r="I110" s="1">
         <v>60</v>
       </c>
-      <c r="I110" s="2" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J110" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B111" s="4">
         <v>0.15</v>
@@ -7038,17 +7697,20 @@
       <c r="F111" t="s">
         <v>272</v>
       </c>
-      <c r="G111" s="1">
+      <c r="G111" t="s">
+        <v>968</v>
+      </c>
+      <c r="H111" s="1">
         <v>0</v>
       </c>
-      <c r="H111" s="1">
+      <c r="I111" s="1">
         <v>500</v>
       </c>
-      <c r="I111" s="2" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J111" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>273</v>
       </c>
@@ -7067,17 +7729,20 @@
       <c r="F112" t="s">
         <v>275</v>
       </c>
-      <c r="G112" s="1">
+      <c r="G112" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H112" s="1">
         <v>0.01</v>
       </c>
-      <c r="H112" s="1">
+      <c r="I112" s="1">
         <v>0.89</v>
       </c>
-      <c r="I112" s="2" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J112" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>276</v>
       </c>
@@ -7096,19 +7761,22 @@
       <c r="F113" t="s">
         <v>278</v>
       </c>
-      <c r="G113" s="1">
+      <c r="G113" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H113" s="1">
         <v>30</v>
       </c>
-      <c r="H113" s="1">
+      <c r="I113" s="1">
         <v>200</v>
       </c>
-      <c r="I113" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J113" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D114" t="s">
         <v>11</v>
@@ -7116,13 +7784,16 @@
       <c r="E114" t="s">
         <v>280</v>
       </c>
-      <c r="I114" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G114" t="s">
+        <v>540</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B115" s="4">
         <v>0.125</v>
@@ -7136,13 +7807,16 @@
       <c r="E115" t="s">
         <v>282</v>
       </c>
-      <c r="I115" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G115" t="s">
+        <v>540</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B116" s="4">
         <v>0.12</v>
@@ -7156,13 +7830,16 @@
       <c r="E116" t="s">
         <v>282</v>
       </c>
-      <c r="I116" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G116" t="s">
+        <v>540</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B117" s="4">
         <v>7.0000000000000001E-3</v>
@@ -7176,13 +7853,16 @@
       <c r="E117" t="s">
         <v>283</v>
       </c>
-      <c r="I117" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G117" t="s">
+        <v>540</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B118" s="4">
         <v>0.22</v>
@@ -7196,13 +7876,16 @@
       <c r="E118" t="s">
         <v>284</v>
       </c>
-      <c r="I118" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G118" t="s">
+        <v>540</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B119" s="4">
         <v>0.15</v>
@@ -7216,13 +7899,16 @@
       <c r="E119" t="s">
         <v>285</v>
       </c>
-      <c r="I119" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G119" t="s">
+        <v>540</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B120" s="4">
         <v>0.05</v>
@@ -7239,17 +7925,17 @@
       <c r="F120" t="s">
         <v>290</v>
       </c>
-      <c r="G120" s="1">
+      <c r="H120" s="1">
         <v>4.2</v>
       </c>
-      <c r="H120" s="1">
+      <c r="I120" s="1">
         <v>5.6</v>
       </c>
-      <c r="I120" s="2" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J120" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>286</v>
       </c>
@@ -7268,19 +7954,22 @@
       <c r="F121" t="s">
         <v>288</v>
       </c>
-      <c r="G121" s="1">
+      <c r="G121" t="s">
+        <v>288</v>
+      </c>
+      <c r="H121" s="1">
         <v>0</v>
       </c>
-      <c r="H121" s="1">
+      <c r="I121" s="1">
         <v>0.99</v>
       </c>
-      <c r="I121" s="2" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J121" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B122" s="4">
         <v>0.186</v>
@@ -7297,17 +7986,20 @@
       <c r="F122" t="s">
         <v>292</v>
       </c>
-      <c r="G122" s="1">
+      <c r="G122" t="s">
+        <v>292</v>
+      </c>
+      <c r="H122" s="1">
         <v>0</v>
       </c>
-      <c r="H122" s="1">
+      <c r="I122" s="1">
         <v>0.9</v>
       </c>
-      <c r="I122" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J122" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>296</v>
       </c>
@@ -7326,19 +8018,22 @@
       <c r="F123" t="s">
         <v>296</v>
       </c>
-      <c r="G123" s="1">
+      <c r="G123" t="s">
+        <v>971</v>
+      </c>
+      <c r="H123" s="1">
         <v>40</v>
       </c>
-      <c r="H123" s="1">
+      <c r="I123" s="1">
         <v>60</v>
       </c>
-      <c r="I123" s="2" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J123" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B124" s="4">
         <v>0.22</v>
@@ -7352,13 +8047,16 @@
       <c r="E124" t="s">
         <v>298</v>
       </c>
-      <c r="I124" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G124" t="s">
+        <v>540</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B125" s="4">
         <v>0.11</v>
@@ -7372,11 +8070,14 @@
       <c r="E125" t="s">
         <v>300</v>
       </c>
-      <c r="I125" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G125" t="s">
+        <v>540</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>301</v>
       </c>
@@ -7395,17 +8096,20 @@
       <c r="F126" t="s">
         <v>303</v>
       </c>
-      <c r="G126" s="1">
+      <c r="G126" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H126" s="1">
         <v>0</v>
       </c>
-      <c r="H126" s="1">
+      <c r="I126" s="1">
         <v>0.9</v>
       </c>
-      <c r="I126" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J126" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>304</v>
       </c>
@@ -7424,17 +8128,20 @@
       <c r="F127" t="s">
         <v>306</v>
       </c>
-      <c r="G127" s="1">
+      <c r="G127" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H127" s="1">
         <v>0</v>
       </c>
-      <c r="H127" s="1">
+      <c r="I127" s="1">
         <v>0.9</v>
       </c>
-      <c r="I127" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J127" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>307</v>
       </c>
@@ -7453,19 +8160,22 @@
       <c r="F128" t="s">
         <v>307</v>
       </c>
-      <c r="G128" s="1">
+      <c r="G128" t="s">
+        <v>307</v>
+      </c>
+      <c r="H128" s="1">
         <v>0</v>
       </c>
-      <c r="H128" s="1">
+      <c r="I128" s="1">
         <v>0.99</v>
       </c>
-      <c r="I128" s="2" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J128" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B129" s="4">
         <v>0.16</v>
@@ -7477,22 +8187,25 @@
         <v>9</v>
       </c>
       <c r="E129" t="s">
+        <v>398</v>
+      </c>
+      <c r="F129" t="s">
         <v>399</v>
       </c>
-      <c r="F129" t="s">
-        <v>400</v>
-      </c>
-      <c r="G129" s="1">
+      <c r="G129" t="s">
+        <v>972</v>
+      </c>
+      <c r="H129" s="1">
         <v>0.15</v>
       </c>
-      <c r="H129" s="1">
+      <c r="I129" s="1">
         <v>5</v>
       </c>
-      <c r="I129" s="2" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J129" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>312</v>
       </c>
@@ -7509,15 +8222,18 @@
         <v>313</v>
       </c>
       <c r="F130" t="s">
-        <v>314</v>
-      </c>
-      <c r="I130" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1063</v>
+      </c>
+      <c r="G130" t="s">
+        <v>1062</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B131" s="4">
         <v>0.17</v>
@@ -7529,24 +8245,27 @@
         <v>9</v>
       </c>
       <c r="E131" t="s">
+        <v>336</v>
+      </c>
+      <c r="F131" t="s">
         <v>337</v>
       </c>
-      <c r="F131" t="s">
-        <v>338</v>
-      </c>
-      <c r="G131" s="1">
+      <c r="G131" t="s">
+        <v>337</v>
+      </c>
+      <c r="H131" s="1">
         <v>40</v>
       </c>
-      <c r="H131" s="1">
+      <c r="I131" s="1">
         <v>350</v>
       </c>
-      <c r="I131" s="2" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J131" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B132" s="4">
         <v>0.35</v>
@@ -7558,15 +8277,18 @@
         <v>15</v>
       </c>
       <c r="E132" t="s">
+        <v>319</v>
+      </c>
+      <c r="G132" t="s">
+        <v>540</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A133" s="3" t="s">
-        <v>321</v>
       </c>
       <c r="B133" s="4">
         <v>0.35</v>
@@ -7578,15 +8300,18 @@
         <v>15</v>
       </c>
       <c r="E133" t="s">
+        <v>321</v>
+      </c>
+      <c r="G133" t="s">
+        <v>540</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="I133" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" s="3" t="s">
-        <v>323</v>
       </c>
       <c r="B134" s="4">
         <v>0.22</v>
@@ -7598,15 +8323,18 @@
         <v>15</v>
       </c>
       <c r="E134" t="s">
+        <v>323</v>
+      </c>
+      <c r="G134" t="s">
+        <v>540</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="I134" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
-        <v>325</v>
       </c>
       <c r="B135" s="4">
         <v>0.2</v>
@@ -7618,24 +8346,27 @@
         <v>11</v>
       </c>
       <c r="E135" t="s">
+        <v>325</v>
+      </c>
+      <c r="F135" t="s">
         <v>326</v>
       </c>
-      <c r="F135" t="s">
-        <v>327</v>
-      </c>
-      <c r="G135" s="1">
+      <c r="G135" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H135" s="1">
         <v>3.4</v>
       </c>
-      <c r="H135" s="1">
+      <c r="I135" s="1">
         <v>6.8</v>
       </c>
-      <c r="I135" s="2" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J135" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B136" s="4">
         <v>0.17</v>
@@ -7647,24 +8378,27 @@
         <v>9</v>
       </c>
       <c r="E136" t="s">
+        <v>339</v>
+      </c>
+      <c r="F136" t="s">
         <v>340</v>
       </c>
-      <c r="F136" t="s">
-        <v>341</v>
-      </c>
-      <c r="G136" s="1">
+      <c r="G136" t="s">
+        <v>340</v>
+      </c>
+      <c r="H136" s="1">
         <v>650</v>
       </c>
-      <c r="H136" s="1">
+      <c r="I136" s="1">
         <v>1600</v>
       </c>
-      <c r="I136" s="2" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J136" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B137" s="4">
         <v>0.12</v>
@@ -7676,21 +8410,24 @@
         <v>9</v>
       </c>
       <c r="E137" t="s">
+        <v>328</v>
+      </c>
+      <c r="G137" t="s">
+        <v>540</v>
+      </c>
+      <c r="H137" s="1">
+        <v>405</v>
+      </c>
+      <c r="I137" s="1">
+        <v>1011</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="G137" s="1">
-        <v>405</v>
-      </c>
-      <c r="H137" s="1">
-        <v>1011</v>
-      </c>
-      <c r="I137" s="2" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" s="3" t="s">
-        <v>330</v>
       </c>
       <c r="B138" s="4">
         <v>0.15</v>
@@ -7702,21 +8439,24 @@
         <v>9</v>
       </c>
       <c r="E138" t="s">
+        <v>330</v>
+      </c>
+      <c r="G138" t="s">
+        <v>540</v>
+      </c>
+      <c r="H138" s="1">
+        <v>169</v>
+      </c>
+      <c r="I138" s="1">
+        <v>786</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
         <v>331</v>
-      </c>
-      <c r="G138" s="1">
-        <v>169</v>
-      </c>
-      <c r="H138" s="1">
-        <v>786</v>
-      </c>
-      <c r="I138" s="2" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" s="3" t="s">
-        <v>332</v>
       </c>
       <c r="B139" s="4">
         <v>0.15</v>
@@ -7728,21 +8468,24 @@
         <v>9</v>
       </c>
       <c r="E139" t="s">
+        <v>332</v>
+      </c>
+      <c r="G139" t="s">
+        <v>540</v>
+      </c>
+      <c r="H139" s="1">
+        <v>11</v>
+      </c>
+      <c r="I139" s="1">
+        <v>85</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="G139" s="1">
-        <v>11</v>
-      </c>
-      <c r="H139" s="1">
-        <v>85</v>
-      </c>
-      <c r="I139" s="2" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" s="3" t="s">
-        <v>334</v>
       </c>
       <c r="B140" s="4">
         <v>0.12</v>
@@ -7754,21 +8497,24 @@
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>335</v>
-      </c>
-      <c r="G140" s="1">
+        <v>334</v>
+      </c>
+      <c r="G140" t="s">
+        <v>540</v>
+      </c>
+      <c r="H140" s="1">
         <v>3</v>
       </c>
-      <c r="H140" s="1">
+      <c r="I140" s="1">
         <v>201</v>
       </c>
-      <c r="I140" s="2" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J140" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B141" s="4">
         <v>0.17</v>
@@ -7780,24 +8526,27 @@
         <v>9</v>
       </c>
       <c r="E141" t="s">
+        <v>342</v>
+      </c>
+      <c r="F141" t="s">
         <v>343</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
+        <v>343</v>
+      </c>
+      <c r="H141" s="1">
+        <v>50</v>
+      </c>
+      <c r="I141" s="1">
+        <v>300</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="G141" s="1">
-        <v>50</v>
-      </c>
-      <c r="H141" s="1">
-        <v>300</v>
-      </c>
-      <c r="I141" s="2" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="s">
-        <v>345</v>
       </c>
       <c r="B142" s="4">
         <v>0.157</v>
@@ -7809,24 +8558,27 @@
         <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F142" t="s">
         <v>79</v>
       </c>
-      <c r="G142" s="1">
+      <c r="G142" t="s">
+        <v>994</v>
+      </c>
+      <c r="H142" s="1">
         <v>2.6</v>
       </c>
-      <c r="H142" s="1">
+      <c r="I142" s="1">
         <v>24.9</v>
       </c>
-      <c r="I142" s="2" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J142" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B143" s="4">
         <v>0.3</v>
@@ -7838,24 +8590,27 @@
         <v>15</v>
       </c>
       <c r="E143" t="s">
-        <v>348</v>
-      </c>
-      <c r="G143" s="1">
+        <v>347</v>
+      </c>
+      <c r="G143" t="s">
+        <v>540</v>
+      </c>
+      <c r="H143" s="1">
         <v>0</v>
       </c>
-      <c r="H143" s="1">
+      <c r="I143" s="1">
         <v>6.99</v>
       </c>
-      <c r="I143" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J143" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J143" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K143" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B144" s="4">
         <v>0.11</v>
@@ -7867,24 +8622,27 @@
         <v>9</v>
       </c>
       <c r="E144" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F144" t="s">
-        <v>845</v>
-      </c>
-      <c r="G144" s="1">
+        <v>843</v>
+      </c>
+      <c r="G144" t="s">
+        <v>843</v>
+      </c>
+      <c r="H144" s="1">
         <v>170</v>
       </c>
-      <c r="H144" s="1">
+      <c r="I144" s="1">
         <v>370</v>
       </c>
-      <c r="I144" s="2" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J144" s="2" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B145" s="4">
         <v>0.2</v>
@@ -7896,24 +8654,27 @@
         <v>9</v>
       </c>
       <c r="E145" t="s">
+        <v>349</v>
+      </c>
+      <c r="F145" t="s">
         <v>350</v>
       </c>
-      <c r="F145" t="s">
+      <c r="G145" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H145" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="I145" s="1">
+        <v>22.4</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
         <v>351</v>
-      </c>
-      <c r="G145" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="H145" s="1">
-        <v>22.4</v>
-      </c>
-      <c r="I145" s="2" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="3" t="s">
-        <v>352</v>
       </c>
       <c r="B146" s="4">
         <v>0.3</v>
@@ -7925,24 +8686,27 @@
         <v>15</v>
       </c>
       <c r="E146" t="s">
-        <v>353</v>
-      </c>
-      <c r="G146" s="1">
+        <v>352</v>
+      </c>
+      <c r="G146" t="s">
+        <v>540</v>
+      </c>
+      <c r="H146" s="1">
         <v>0</v>
       </c>
-      <c r="H146" s="1">
+      <c r="I146" s="1">
         <v>6.99</v>
       </c>
-      <c r="I146" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J146" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J146" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K146" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B147" s="4">
         <v>0.12</v>
@@ -7954,24 +8718,27 @@
         <v>9</v>
       </c>
       <c r="E147" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F147" t="s">
-        <v>846</v>
-      </c>
-      <c r="G147" s="1">
+        <v>844</v>
+      </c>
+      <c r="G147" t="s">
+        <v>844</v>
+      </c>
+      <c r="H147" s="1">
         <v>90</v>
       </c>
-      <c r="H147" s="1">
+      <c r="I147" s="1">
         <v>210</v>
       </c>
-      <c r="I147" s="2" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J147" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B148" s="4">
         <v>0.2</v>
@@ -7983,24 +8750,24 @@
         <v>9</v>
       </c>
       <c r="E148" t="s">
+        <v>354</v>
+      </c>
+      <c r="F148" t="s">
         <v>355</v>
       </c>
-      <c r="F148" t="s">
-        <v>356</v>
-      </c>
-      <c r="G148" s="1">
+      <c r="H148" s="1">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H148" s="1">
+      <c r="I148" s="1">
         <v>27</v>
       </c>
-      <c r="I148" s="2" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J148" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B149" s="4">
         <v>0.25</v>
@@ -8012,24 +8779,27 @@
         <v>9</v>
       </c>
       <c r="E149" t="s">
+        <v>373</v>
+      </c>
+      <c r="F149" t="s">
         <v>374</v>
       </c>
-      <c r="F149" t="s">
-        <v>375</v>
-      </c>
-      <c r="G149" s="1">
+      <c r="G149" t="s">
+        <v>973</v>
+      </c>
+      <c r="H149" s="1">
         <v>1.7</v>
       </c>
-      <c r="H149" s="1">
+      <c r="I149" s="1">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I149" s="2" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J149" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B150" s="4">
         <v>0.3</v>
@@ -8041,24 +8811,27 @@
         <v>9</v>
       </c>
       <c r="E150" t="s">
+        <v>484</v>
+      </c>
+      <c r="F150" t="s">
         <v>485</v>
       </c>
-      <c r="F150" t="s">
-        <v>486</v>
-      </c>
-      <c r="G150" s="1">
+      <c r="G150" t="s">
+        <v>485</v>
+      </c>
+      <c r="H150" s="1">
         <v>5</v>
       </c>
-      <c r="H150" s="1">
+      <c r="I150" s="1">
         <v>40</v>
       </c>
-      <c r="I150" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J150" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B151" s="4">
         <v>0.14000000000000001</v>
@@ -8070,22 +8843,25 @@
         <v>9</v>
       </c>
       <c r="E151" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F151" t="s">
-        <v>362</v>
-      </c>
-      <c r="G151" s="1">
+        <v>361</v>
+      </c>
+      <c r="G151" t="s">
+        <v>995</v>
+      </c>
+      <c r="H151" s="1">
         <v>1.7</v>
       </c>
-      <c r="H151" s="1">
+      <c r="I151" s="1">
         <v>8.6</v>
       </c>
-      <c r="I151" s="2" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J151" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>192</v>
       </c>
@@ -8104,19 +8880,22 @@
       <c r="F152" t="s">
         <v>194</v>
       </c>
-      <c r="G152" s="1">
+      <c r="G152" t="s">
+        <v>194</v>
+      </c>
+      <c r="H152" s="1">
         <v>76</v>
       </c>
-      <c r="H152" s="1">
+      <c r="I152" s="1">
         <v>152</v>
       </c>
-      <c r="I152" s="2" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J152" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B153" s="4">
         <v>0.3</v>
@@ -8128,24 +8907,27 @@
         <v>6</v>
       </c>
       <c r="E153" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="F153" t="s">
+        <v>714</v>
+      </c>
+      <c r="G153" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H153" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I153" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="J153" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="G153" s="1">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="H153" s="1">
-        <v>13.8</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B154" s="4">
         <v>0.25</v>
@@ -8157,24 +8939,27 @@
         <v>9</v>
       </c>
       <c r="E154" t="s">
+        <v>371</v>
+      </c>
+      <c r="F154" t="s">
         <v>372</v>
       </c>
-      <c r="F154" t="s">
-        <v>373</v>
-      </c>
-      <c r="G154" s="1">
+      <c r="G154" t="s">
+        <v>372</v>
+      </c>
+      <c r="H154" s="1">
         <v>0.5</v>
       </c>
-      <c r="H154" s="1">
+      <c r="I154" s="1">
         <v>1.2</v>
       </c>
-      <c r="I154" s="2" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J154" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B155" s="4">
         <v>0.1</v>
@@ -8186,24 +8971,27 @@
         <v>9</v>
       </c>
       <c r="E155" t="s">
+        <v>403</v>
+      </c>
+      <c r="F155" t="s">
         <v>404</v>
       </c>
-      <c r="F155" t="s">
-        <v>405</v>
-      </c>
-      <c r="G155" s="1">
+      <c r="G155" t="s">
+        <v>974</v>
+      </c>
+      <c r="H155" s="1">
         <v>3.5</v>
       </c>
-      <c r="H155" s="1">
+      <c r="I155" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="I155" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J155" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B156" s="4">
         <v>0.1</v>
@@ -8215,24 +9003,27 @@
         <v>6</v>
       </c>
       <c r="E156" t="s">
+        <v>717</v>
+      </c>
+      <c r="F156" t="s">
+        <v>718</v>
+      </c>
+      <c r="G156" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H156" s="1">
+        <v>17</v>
+      </c>
+      <c r="I156" s="1">
+        <v>164</v>
+      </c>
+      <c r="J156" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="F156" t="s">
-        <v>720</v>
-      </c>
-      <c r="G156" s="1">
-        <v>17</v>
-      </c>
-      <c r="H156" s="1">
-        <v>164</v>
-      </c>
-      <c r="I156" s="2" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B157" s="4">
         <v>0.2</v>
@@ -8244,24 +9035,27 @@
         <v>6</v>
       </c>
       <c r="E157" t="s">
+        <v>376</v>
+      </c>
+      <c r="F157" t="s">
         <v>377</v>
       </c>
-      <c r="F157" t="s">
+      <c r="G157" t="s">
+        <v>1017</v>
+      </c>
+      <c r="H157" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I157" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
         <v>378</v>
-      </c>
-      <c r="G157" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="H157" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="I157" s="2" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A158" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="B158" s="4">
         <v>0.3</v>
@@ -8273,24 +9067,27 @@
         <v>15</v>
       </c>
       <c r="E158" t="s">
+        <v>379</v>
+      </c>
+      <c r="G158" t="s">
+        <v>540</v>
+      </c>
+      <c r="H158" s="1">
+        <v>0</v>
+      </c>
+      <c r="I158" s="1">
+        <v>3.49</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="K158" s="5" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
         <v>380</v>
-      </c>
-      <c r="G158" s="1">
-        <v>0</v>
-      </c>
-      <c r="H158" s="1">
-        <v>3.49</v>
-      </c>
-      <c r="I158" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="J158" s="5" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A159" s="3" t="s">
-        <v>381</v>
       </c>
       <c r="B159" s="4">
         <v>0.36</v>
@@ -8302,24 +9099,27 @@
         <v>9</v>
       </c>
       <c r="E159" t="s">
+        <v>381</v>
+      </c>
+      <c r="F159" t="s">
         <v>382</v>
       </c>
-      <c r="F159" t="s">
+      <c r="G159" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H159" s="1">
+        <v>0</v>
+      </c>
+      <c r="I159" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
         <v>383</v>
-      </c>
-      <c r="G159" s="1">
-        <v>0</v>
-      </c>
-      <c r="H159" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="I159" s="2" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A160" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="B160" s="4">
         <v>0.3</v>
@@ -8331,24 +9131,27 @@
         <v>9</v>
       </c>
       <c r="E160" t="s">
+        <v>384</v>
+      </c>
+      <c r="F160" t="s">
         <v>385</v>
       </c>
-      <c r="F160" t="s">
+      <c r="G160" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H160" s="1">
+        <v>0</v>
+      </c>
+      <c r="I160" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
         <v>386</v>
-      </c>
-      <c r="G160" s="1">
-        <v>0</v>
-      </c>
-      <c r="H160" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="I160" s="2" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" s="3" t="s">
-        <v>387</v>
       </c>
       <c r="B161" s="4">
         <v>0.155</v>
@@ -8360,24 +9163,27 @@
         <v>15</v>
       </c>
       <c r="E161" t="s">
+        <v>387</v>
+      </c>
+      <c r="F161" t="s">
         <v>388</v>
       </c>
-      <c r="F161" t="s">
+      <c r="G161" t="s">
+        <v>388</v>
+      </c>
+      <c r="H161" s="1">
+        <v>14</v>
+      </c>
+      <c r="I161" s="1">
+        <v>46</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
         <v>389</v>
-      </c>
-      <c r="G161" s="1">
-        <v>14</v>
-      </c>
-      <c r="H161" s="1">
-        <v>46</v>
-      </c>
-      <c r="I161" s="2" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A162" s="3" t="s">
-        <v>390</v>
       </c>
       <c r="B162" s="4">
         <v>0.18</v>
@@ -8389,24 +9195,27 @@
         <v>15</v>
       </c>
       <c r="E162" t="s">
+        <v>390</v>
+      </c>
+      <c r="F162" t="s">
         <v>391</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
+        <v>391</v>
+      </c>
+      <c r="H162" s="1">
+        <v>17.3</v>
+      </c>
+      <c r="I162" s="1">
+        <v>74.099999999999994</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="G162" s="1">
-        <v>17.3</v>
-      </c>
-      <c r="H162" s="1">
-        <v>74.099999999999994</v>
-      </c>
-      <c r="I162" s="2" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="B163" s="4">
         <v>0.33</v>
@@ -8418,27 +9227,30 @@
         <v>9</v>
       </c>
       <c r="E163" t="s">
+        <v>393</v>
+      </c>
+      <c r="F163" t="s">
         <v>394</v>
       </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H163" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I163" s="1">
+        <v>1.99</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="K163" s="5" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
         <v>395</v>
-      </c>
-      <c r="G163" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="H163" s="1">
-        <v>1.99</v>
-      </c>
-      <c r="I163" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="J163" s="5" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="3" t="s">
-        <v>396</v>
       </c>
       <c r="B164" s="4">
         <v>0.4</v>
@@ -8450,25 +9262,28 @@
         <v>9</v>
       </c>
       <c r="E164" t="s">
+        <v>396</v>
+      </c>
+      <c r="F164" t="s">
         <v>397</v>
       </c>
-      <c r="F164" t="s">
-        <v>398</v>
-      </c>
-      <c r="G164" s="1">
+      <c r="G164" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H164" s="1">
         <v>0</v>
       </c>
-      <c r="H164" s="1">
+      <c r="I164" s="1">
         <v>0.89</v>
       </c>
-      <c r="I164" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="J164" s="5" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J164" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="K164" s="5" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>182</v>
       </c>
@@ -8487,19 +9302,22 @@
       <c r="F165" t="s">
         <v>182</v>
       </c>
-      <c r="G165" s="1">
+      <c r="G165" t="s">
+        <v>975</v>
+      </c>
+      <c r="H165" s="1">
         <v>1</v>
       </c>
-      <c r="H165" s="1">
+      <c r="I165" s="1">
         <v>25</v>
       </c>
-      <c r="I165" s="2" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J165" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B166" s="4">
         <v>0.13</v>
@@ -8511,24 +9329,27 @@
         <v>15</v>
       </c>
       <c r="E166" t="s">
+        <v>401</v>
+      </c>
+      <c r="F166" t="s">
         <v>402</v>
       </c>
-      <c r="F166" t="s">
-        <v>403</v>
-      </c>
-      <c r="G166" s="1">
+      <c r="G166" t="s">
+        <v>402</v>
+      </c>
+      <c r="H166" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H166" s="1">
+      <c r="I166" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I166" s="2" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J166" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B167" s="4">
         <v>0.25</v>
@@ -8540,24 +9361,27 @@
         <v>6</v>
       </c>
       <c r="E167" t="s">
+        <v>416</v>
+      </c>
+      <c r="F167" t="s">
         <v>417</v>
       </c>
-      <c r="F167" t="s">
-        <v>418</v>
-      </c>
-      <c r="G167" s="1">
+      <c r="G167" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H167" s="1">
         <v>15</v>
       </c>
-      <c r="H167" s="1">
+      <c r="I167" s="1">
         <v>45</v>
       </c>
-      <c r="I167" s="2" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J167" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B168" s="4">
         <v>0.12</v>
@@ -8569,24 +9393,27 @@
         <v>9</v>
       </c>
       <c r="E168" t="s">
+        <v>418</v>
+      </c>
+      <c r="F168" t="s">
         <v>419</v>
       </c>
-      <c r="F168" t="s">
-        <v>420</v>
-      </c>
-      <c r="G168" s="1">
+      <c r="G168" t="s">
+        <v>976</v>
+      </c>
+      <c r="H168" s="1">
         <v>6.4</v>
       </c>
-      <c r="H168" s="1">
+      <c r="I168" s="1">
         <v>8.3000000000000007</v>
       </c>
-      <c r="I168" s="2" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J168" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B169" s="4">
         <v>0.3</v>
@@ -8598,24 +9425,27 @@
         <v>15</v>
       </c>
       <c r="E169" t="s">
+        <v>406</v>
+      </c>
+      <c r="G169" t="s">
+        <v>540</v>
+      </c>
+      <c r="H169" s="1">
+        <v>0</v>
+      </c>
+      <c r="I169" s="1">
+        <v>1.99</v>
+      </c>
+      <c r="J169" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="K169" s="7" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="G169" s="1">
-        <v>0</v>
-      </c>
-      <c r="H169" s="1">
-        <v>1.99</v>
-      </c>
-      <c r="I169" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="J169" s="7" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A170" s="3" t="s">
-        <v>408</v>
       </c>
       <c r="B170" s="4">
         <v>0.2</v>
@@ -8627,24 +9457,27 @@
         <v>9</v>
       </c>
       <c r="E170" t="s">
+        <v>408</v>
+      </c>
+      <c r="F170" t="s">
         <v>409</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H170" s="1">
+        <v>20</v>
+      </c>
+      <c r="I170" s="1">
+        <v>40</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="G170" s="1">
-        <v>20</v>
-      </c>
-      <c r="H170" s="1">
-        <v>40</v>
-      </c>
-      <c r="I170" s="2" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A171" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="B171" s="4">
         <v>0.14000000000000001</v>
@@ -8656,24 +9489,27 @@
         <v>9</v>
       </c>
       <c r="E171" t="s">
+        <v>411</v>
+      </c>
+      <c r="F171" t="s">
         <v>412</v>
       </c>
-      <c r="F171" t="s">
+      <c r="G171" t="s">
+        <v>996</v>
+      </c>
+      <c r="H171" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="I171" s="1">
+        <v>15</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
         <v>413</v>
-      </c>
-      <c r="G171" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="H171" s="1">
-        <v>15</v>
-      </c>
-      <c r="I171" s="2" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A172" s="3" t="s">
-        <v>414</v>
       </c>
       <c r="B172" s="4">
         <v>0.13</v>
@@ -8685,24 +9521,27 @@
         <v>9</v>
       </c>
       <c r="E172" t="s">
+        <v>414</v>
+      </c>
+      <c r="F172" t="s">
         <v>415</v>
       </c>
-      <c r="F172" t="s">
-        <v>416</v>
-      </c>
-      <c r="G172" s="1">
+      <c r="G172" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H172" s="1">
         <v>2.1</v>
       </c>
-      <c r="H172" s="1">
+      <c r="I172" s="1">
         <v>17.7</v>
       </c>
-      <c r="I172" s="2" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J172" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B173" s="4">
         <v>0.4</v>
@@ -8714,22 +9553,25 @@
         <v>6</v>
       </c>
       <c r="E173" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="F173" t="s">
-        <v>723</v>
-      </c>
-      <c r="G173" s="1">
+        <v>721</v>
+      </c>
+      <c r="G173" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H173" s="1">
         <v>1</v>
       </c>
-      <c r="H173" s="1">
+      <c r="I173" s="1">
         <v>15</v>
       </c>
-      <c r="I173" s="2" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J173" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>195</v>
       </c>
@@ -8748,19 +9590,22 @@
       <c r="F174" t="s">
         <v>197</v>
       </c>
-      <c r="G174" s="1">
+      <c r="G174" t="s">
+        <v>967</v>
+      </c>
+      <c r="H174" s="1">
         <v>100</v>
       </c>
-      <c r="H174" s="1">
+      <c r="I174" s="1">
         <v>199</v>
       </c>
-      <c r="I174" s="2" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J174" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B175" s="4">
         <v>0.05</v>
@@ -8772,24 +9617,27 @@
         <v>9</v>
       </c>
       <c r="E175" t="s">
+        <v>455</v>
+      </c>
+      <c r="F175" t="s">
         <v>456</v>
       </c>
-      <c r="F175" t="s">
-        <v>457</v>
-      </c>
-      <c r="G175" s="1">
+      <c r="G175" t="s">
+        <v>977</v>
+      </c>
+      <c r="H175" s="1">
         <v>136</v>
       </c>
-      <c r="H175" s="1">
+      <c r="I175" s="1">
         <v>145</v>
       </c>
-      <c r="I175" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J175" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B176" s="4">
         <v>0.2</v>
@@ -8801,24 +9649,27 @@
         <v>9</v>
       </c>
       <c r="E176" t="s">
+        <v>421</v>
+      </c>
+      <c r="F176" t="s">
         <v>422</v>
       </c>
-      <c r="F176" t="s">
+      <c r="G176" t="s">
+        <v>997</v>
+      </c>
+      <c r="H176" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="I176" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="J176" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="G176" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="H176" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="I176" s="2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A177" s="3" t="s">
-        <v>424</v>
       </c>
       <c r="B177" s="4">
         <v>0.17</v>
@@ -8830,24 +9681,27 @@
         <v>9</v>
       </c>
       <c r="E177" t="s">
+        <v>424</v>
+      </c>
+      <c r="F177" t="s">
         <v>425</v>
       </c>
-      <c r="F177" t="s">
+      <c r="G177" t="s">
+        <v>998</v>
+      </c>
+      <c r="H177" s="1">
+        <v>0</v>
+      </c>
+      <c r="I177" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="J177" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="G177" s="1">
-        <v>0</v>
-      </c>
-      <c r="H177" s="1">
-        <v>0.06</v>
-      </c>
-      <c r="I177" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A178" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="B178" s="4">
         <v>0.42</v>
@@ -8859,18 +9713,18 @@
         <v>15</v>
       </c>
       <c r="E178" t="s">
+        <v>427</v>
+      </c>
+      <c r="F178" t="s">
         <v>428</v>
       </c>
-      <c r="F178" t="s">
+      <c r="J178" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
         <v>429</v>
-      </c>
-      <c r="I178" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A179" s="3" t="s">
-        <v>430</v>
       </c>
       <c r="B179" s="4">
         <v>0.3</v>
@@ -8882,24 +9736,27 @@
         <v>15</v>
       </c>
       <c r="E179" t="s">
+        <v>430</v>
+      </c>
+      <c r="G179" t="s">
+        <v>540</v>
+      </c>
+      <c r="H179" s="1">
+        <v>0</v>
+      </c>
+      <c r="I179" s="1">
+        <v>6.99</v>
+      </c>
+      <c r="J179" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K179" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="G179" s="1">
-        <v>0</v>
-      </c>
-      <c r="H179" s="1">
-        <v>6.99</v>
-      </c>
-      <c r="I179" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J179" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A180" s="3" t="s">
-        <v>432</v>
       </c>
       <c r="B180" s="4">
         <v>0.3</v>
@@ -8911,24 +9768,27 @@
         <v>15</v>
       </c>
       <c r="E180" t="s">
+        <v>432</v>
+      </c>
+      <c r="G180" t="s">
+        <v>540</v>
+      </c>
+      <c r="H180" s="1">
+        <v>0</v>
+      </c>
+      <c r="I180" s="1">
+        <v>6.99</v>
+      </c>
+      <c r="J180" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K180" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="G180" s="1">
-        <v>0</v>
-      </c>
-      <c r="H180" s="1">
-        <v>6.99</v>
-      </c>
-      <c r="I180" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J180" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181" s="3" t="s">
-        <v>434</v>
       </c>
       <c r="B181" s="4">
         <v>0.23</v>
@@ -8937,27 +9797,30 @@
         <v>0.115</v>
       </c>
       <c r="D181" t="s">
+        <v>434</v>
+      </c>
+      <c r="E181" t="s">
         <v>435</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>436</v>
       </c>
-      <c r="F181" t="s">
+      <c r="G181" t="s">
+        <v>436</v>
+      </c>
+      <c r="H181" s="1">
+        <v>0</v>
+      </c>
+      <c r="I181" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="J181" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="G181" s="1">
-        <v>0</v>
-      </c>
-      <c r="H181" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="I181" s="2" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A182" s="3" t="s">
-        <v>438</v>
       </c>
       <c r="B182" s="4">
         <v>0.222</v>
@@ -8966,30 +9829,33 @@
         <v>0.111</v>
       </c>
       <c r="D182" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E182" t="s">
+        <v>438</v>
+      </c>
+      <c r="F182" t="s">
         <v>439</v>
       </c>
-      <c r="F182" t="s">
+      <c r="G182" t="s">
+        <v>439</v>
+      </c>
+      <c r="H182" s="1">
+        <v>0</v>
+      </c>
+      <c r="I182" s="1">
+        <v>0.79</v>
+      </c>
+      <c r="J182" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="K182" s="5" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="G182" s="1">
-        <v>0</v>
-      </c>
-      <c r="H182" s="1">
-        <v>0.79</v>
-      </c>
-      <c r="I182" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J182" s="5" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A183" s="3" t="s">
-        <v>441</v>
       </c>
       <c r="B183" s="4">
         <v>0.3</v>
@@ -9001,27 +9867,30 @@
         <v>9</v>
       </c>
       <c r="E183" t="s">
+        <v>441</v>
+      </c>
+      <c r="F183" t="s">
         <v>442</v>
       </c>
-      <c r="F183" t="s">
+      <c r="G183" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H183" s="1">
+        <v>0</v>
+      </c>
+      <c r="I183" s="1">
+        <v>13.49</v>
+      </c>
+      <c r="J183" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="K183" s="5" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="G183" s="1">
-        <v>0</v>
-      </c>
-      <c r="H183" s="1">
-        <v>13.49</v>
-      </c>
-      <c r="I183" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="J183" s="5" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A184" s="3" t="s">
-        <v>444</v>
       </c>
       <c r="B184" s="4">
         <v>0.3</v>
@@ -9033,27 +9902,30 @@
         <v>9</v>
       </c>
       <c r="E184" t="s">
+        <v>444</v>
+      </c>
+      <c r="F184" t="s">
         <v>445</v>
       </c>
-      <c r="F184" t="s">
+      <c r="G184" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H184" s="1">
+        <v>0</v>
+      </c>
+      <c r="I184" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="J184" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="K184" s="5" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="G184" s="1">
-        <v>0</v>
-      </c>
-      <c r="H184" s="1">
-        <v>0.89</v>
-      </c>
-      <c r="I184" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="J184" s="5" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A185" s="3" t="s">
-        <v>447</v>
       </c>
       <c r="B185" s="4">
         <v>0.3</v>
@@ -9065,24 +9937,27 @@
         <v>15</v>
       </c>
       <c r="E185" t="s">
+        <v>447</v>
+      </c>
+      <c r="G185" t="s">
+        <v>540</v>
+      </c>
+      <c r="H185" s="1">
+        <v>0</v>
+      </c>
+      <c r="I185" s="1">
+        <v>6.99</v>
+      </c>
+      <c r="J185" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K185" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="G185" s="1">
-        <v>0</v>
-      </c>
-      <c r="H185" s="1">
-        <v>6.99</v>
-      </c>
-      <c r="I185" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J185" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A186" s="3" t="s">
-        <v>449</v>
       </c>
       <c r="B186" s="4">
         <v>0.16</v>
@@ -9094,24 +9969,27 @@
         <v>11</v>
       </c>
       <c r="E186" t="s">
+        <v>449</v>
+      </c>
+      <c r="F186" t="s">
+        <v>448</v>
+      </c>
+      <c r="G186" t="s">
+        <v>448</v>
+      </c>
+      <c r="H186" s="1">
+        <v>34.5</v>
+      </c>
+      <c r="I186" s="1">
+        <v>568.9</v>
+      </c>
+      <c r="J186" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="F186" t="s">
-        <v>449</v>
-      </c>
-      <c r="G186" s="1">
-        <v>34.5</v>
-      </c>
-      <c r="H186" s="1">
-        <v>568.9</v>
-      </c>
-      <c r="I186" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A187" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="B187" s="4">
         <v>0.16</v>
@@ -9123,24 +10001,27 @@
         <v>9</v>
       </c>
       <c r="E187" t="s">
+        <v>451</v>
+      </c>
+      <c r="F187" t="s">
         <v>452</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
+        <v>450</v>
+      </c>
+      <c r="H187" s="1">
+        <v>20.6</v>
+      </c>
+      <c r="I187" s="1">
+        <v>76.7</v>
+      </c>
+      <c r="J187" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
         <v>453</v>
-      </c>
-      <c r="G187" s="1">
-        <v>20.6</v>
-      </c>
-      <c r="H187" s="1">
-        <v>76.7</v>
-      </c>
-      <c r="I187" s="2" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A188" s="3" t="s">
-        <v>454</v>
       </c>
       <c r="B188" s="4">
         <v>0.3</v>
@@ -9152,24 +10033,27 @@
         <v>15</v>
       </c>
       <c r="E188" t="s">
-        <v>455</v>
-      </c>
-      <c r="G188" s="1">
+        <v>454</v>
+      </c>
+      <c r="G188" t="s">
+        <v>540</v>
+      </c>
+      <c r="H188" s="1">
         <v>0</v>
       </c>
-      <c r="H188" s="1">
+      <c r="I188" s="1">
         <v>6.99</v>
       </c>
-      <c r="I188" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J188" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J188" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K188" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B189" s="4">
         <v>0.1</v>
@@ -9181,24 +10065,27 @@
         <v>6</v>
       </c>
       <c r="E189" t="s">
+        <v>722</v>
+      </c>
+      <c r="F189" t="s">
+        <v>723</v>
+      </c>
+      <c r="G189" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H189" s="1">
+        <v>18</v>
+      </c>
+      <c r="I189" s="1">
+        <v>301</v>
+      </c>
+      <c r="J189" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="F189" t="s">
-        <v>725</v>
-      </c>
-      <c r="G189" s="1">
-        <v>18</v>
-      </c>
-      <c r="H189" s="1">
-        <v>301</v>
-      </c>
-      <c r="I189" s="2" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B190" s="4">
         <v>0.18</v>
@@ -9210,24 +10097,27 @@
         <v>9</v>
       </c>
       <c r="E190" t="s">
+        <v>510</v>
+      </c>
+      <c r="F190" t="s">
         <v>511</v>
       </c>
-      <c r="F190" t="s">
-        <v>512</v>
-      </c>
-      <c r="G190" s="1">
+      <c r="G190" t="s">
+        <v>978</v>
+      </c>
+      <c r="H190" s="1">
         <v>16.600000000000001</v>
       </c>
-      <c r="H190" s="1">
+      <c r="I190" s="1">
         <v>48.5</v>
       </c>
-      <c r="I190" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J190" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B191" s="4">
         <v>0.16</v>
@@ -9239,24 +10129,27 @@
         <v>9</v>
       </c>
       <c r="E191" t="s">
+        <v>458</v>
+      </c>
+      <c r="F191" t="s">
         <v>459</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H191" s="1">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="I191" s="1">
+        <v>225</v>
+      </c>
+      <c r="J191" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="G191" s="1">
-        <v>40.200000000000003</v>
-      </c>
-      <c r="H191" s="1">
-        <v>225</v>
-      </c>
-      <c r="I191" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A192" s="3" t="s">
-        <v>461</v>
       </c>
       <c r="B192" s="4">
         <v>0.186</v>
@@ -9268,24 +10161,27 @@
         <v>15</v>
       </c>
       <c r="E192" t="s">
+        <v>461</v>
+      </c>
+      <c r="F192" t="s">
         <v>462</v>
       </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
+        <v>999</v>
+      </c>
+      <c r="H192" s="1">
+        <v>0</v>
+      </c>
+      <c r="I192" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="J192" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="G192" s="1">
-        <v>0</v>
-      </c>
-      <c r="H192" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="I192" s="2" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A193" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="B193" s="4">
         <v>0.15</v>
@@ -9297,24 +10193,27 @@
         <v>9</v>
       </c>
       <c r="E193" t="s">
+        <v>464</v>
+      </c>
+      <c r="F193" t="s">
         <v>465</v>
       </c>
-      <c r="F193" t="s">
+      <c r="G193" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H193" s="1">
+        <v>2.04</v>
+      </c>
+      <c r="I193" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J193" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="G193" s="1">
-        <v>2.04</v>
-      </c>
-      <c r="H193" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I193" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A194" s="3" t="s">
-        <v>467</v>
       </c>
       <c r="B194" s="4">
         <v>0.24</v>
@@ -9326,24 +10225,27 @@
         <v>9</v>
       </c>
       <c r="E194" t="s">
+        <v>467</v>
+      </c>
+      <c r="F194" t="s">
         <v>468</v>
       </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
+        <v>468</v>
+      </c>
+      <c r="H194" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="I194" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="J194" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A195" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="G194" s="1">
-        <v>0.31</v>
-      </c>
-      <c r="H194" s="1">
-        <v>0.95</v>
-      </c>
-      <c r="I194" s="2" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A195" s="3" t="s">
-        <v>470</v>
       </c>
       <c r="B195" s="4">
         <v>0.15</v>
@@ -9355,24 +10257,27 @@
         <v>9</v>
       </c>
       <c r="E195" t="s">
+        <v>470</v>
+      </c>
+      <c r="F195" t="s">
         <v>471</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H195" s="1">
+        <v>80</v>
+      </c>
+      <c r="I195" s="1">
+        <v>200</v>
+      </c>
+      <c r="J195" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="G195" s="1">
-        <v>80</v>
-      </c>
-      <c r="H195" s="1">
-        <v>200</v>
-      </c>
-      <c r="I195" s="2" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A196" s="3" t="s">
-        <v>473</v>
       </c>
       <c r="B196" s="4">
         <v>0.12</v>
@@ -9384,24 +10289,27 @@
         <v>9</v>
       </c>
       <c r="E196" t="s">
+        <v>473</v>
+      </c>
+      <c r="F196" t="s">
         <v>474</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
+        <v>474</v>
+      </c>
+      <c r="H196" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="I196" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="J196" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="G196" s="1">
-        <v>0.77</v>
-      </c>
-      <c r="H196" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="I196" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A197" s="3" t="s">
-        <v>476</v>
       </c>
       <c r="B197" s="4">
         <v>0.15</v>
@@ -9413,24 +10321,27 @@
         <v>9</v>
       </c>
       <c r="E197" t="s">
+        <v>476</v>
+      </c>
+      <c r="F197" t="s">
         <v>477</v>
       </c>
-      <c r="F197" t="s">
+      <c r="G197" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H197" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I197" s="1">
+        <v>12.1</v>
+      </c>
+      <c r="J197" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="s">
         <v>478</v>
-      </c>
-      <c r="G197" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="H197" s="1">
-        <v>12.1</v>
-      </c>
-      <c r="I197" s="2" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A198" s="3" t="s">
-        <v>479</v>
       </c>
       <c r="B198" s="4">
         <v>0.192</v>
@@ -9442,24 +10353,27 @@
         <v>11</v>
       </c>
       <c r="E198" t="s">
+        <v>479</v>
+      </c>
+      <c r="F198" t="s">
+        <v>478</v>
+      </c>
+      <c r="G198" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H198" s="1">
+        <v>13</v>
+      </c>
+      <c r="I198" s="1">
+        <v>39</v>
+      </c>
+      <c r="J198" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="s">
         <v>480</v>
-      </c>
-      <c r="F198" t="s">
-        <v>479</v>
-      </c>
-      <c r="G198" s="1">
-        <v>13</v>
-      </c>
-      <c r="H198" s="1">
-        <v>39</v>
-      </c>
-      <c r="I198" s="2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A199" s="3" t="s">
-        <v>481</v>
       </c>
       <c r="B199" s="4">
         <v>0.35</v>
@@ -9471,24 +10385,27 @@
         <v>9</v>
       </c>
       <c r="E199" t="s">
+        <v>481</v>
+      </c>
+      <c r="F199" t="s">
         <v>482</v>
       </c>
-      <c r="F199" t="s">
-        <v>483</v>
-      </c>
-      <c r="G199" s="1">
+      <c r="G199" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H199" s="1">
         <v>193</v>
       </c>
-      <c r="H199" s="1">
+      <c r="I199" s="1">
         <v>740</v>
       </c>
-      <c r="I199" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J199" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B200" s="4">
         <v>0.2</v>
@@ -9500,22 +10417,25 @@
         <v>9</v>
       </c>
       <c r="E200" t="s">
+        <v>481</v>
+      </c>
+      <c r="F200" t="s">
         <v>482</v>
       </c>
-      <c r="F200" t="s">
-        <v>483</v>
-      </c>
-      <c r="G200" s="1">
+      <c r="G200" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H200" s="1">
         <v>193</v>
       </c>
-      <c r="H200" s="1">
+      <c r="I200" s="1">
         <v>740</v>
       </c>
-      <c r="I200" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J200" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>211</v>
       </c>
@@ -9532,21 +10452,24 @@
         <v>212</v>
       </c>
       <c r="F201" t="s">
-        <v>211</v>
-      </c>
-      <c r="G201" s="1">
+        <v>1052</v>
+      </c>
+      <c r="G201" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H201" s="1">
         <v>39</v>
       </c>
-      <c r="H201" s="1">
+      <c r="I201" s="1">
         <v>308</v>
       </c>
-      <c r="I201" s="2" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J201" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B202" s="4">
         <v>0.12</v>
@@ -9563,19 +10486,22 @@
       <c r="F202" t="s">
         <v>19</v>
       </c>
-      <c r="G202" s="1">
+      <c r="G202" t="s">
+        <v>954</v>
+      </c>
+      <c r="H202" s="1">
         <v>3.5</v>
       </c>
-      <c r="H202" s="1">
+      <c r="I202" s="1">
         <v>5.2</v>
       </c>
-      <c r="I202" s="2" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J202" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B203" s="4">
         <v>0.2</v>
@@ -9587,24 +10513,27 @@
         <v>15</v>
       </c>
       <c r="E203" t="s">
+        <v>490</v>
+      </c>
+      <c r="F203" t="s">
         <v>491</v>
       </c>
-      <c r="F203" t="s">
+      <c r="G203" t="s">
+        <v>491</v>
+      </c>
+      <c r="H203" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="I203" s="1">
+        <v>77</v>
+      </c>
+      <c r="J203" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="s">
         <v>492</v>
-      </c>
-      <c r="G203" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="H203" s="1">
-        <v>77</v>
-      </c>
-      <c r="I203" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A204" s="3" t="s">
-        <v>493</v>
       </c>
       <c r="B204" s="4">
         <v>0.23</v>
@@ -9613,30 +10542,33 @@
         <v>0.115</v>
       </c>
       <c r="D204" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E204" t="s">
+        <v>493</v>
+      </c>
+      <c r="F204" t="s">
         <v>494</v>
       </c>
-      <c r="F204" t="s">
+      <c r="G204" t="s">
+        <v>494</v>
+      </c>
+      <c r="H204" s="1">
+        <v>0</v>
+      </c>
+      <c r="I204" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="J204" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="K204" s="5" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="G204" s="1">
-        <v>0</v>
-      </c>
-      <c r="H204" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="I204" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="J204" s="5" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A205" s="3" t="s">
-        <v>496</v>
       </c>
       <c r="B205" s="4">
         <v>0.153</v>
@@ -9645,28 +10577,31 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="D205" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E205" t="s">
+        <v>496</v>
+      </c>
+      <c r="F205" t="s">
         <v>497</v>
       </c>
-      <c r="F205" t="s">
-        <v>498</v>
-      </c>
-      <c r="G205" s="1">
+      <c r="G205" t="s">
+        <v>497</v>
+      </c>
+      <c r="H205" s="1">
         <v>0</v>
       </c>
-      <c r="H205" s="1">
+      <c r="I205" s="1">
         <v>0.79</v>
       </c>
-      <c r="I205" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J205" s="5" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J205" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="K205" s="5" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>95</v>
       </c>
@@ -9680,24 +10615,27 @@
         <v>15</v>
       </c>
       <c r="E206" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="F206" t="s">
         <v>95</v>
       </c>
-      <c r="G206" s="1">
+      <c r="G206" t="s">
+        <v>95</v>
+      </c>
+      <c r="H206" s="1">
         <v>0</v>
       </c>
-      <c r="H206" s="1">
+      <c r="I206" s="1">
         <v>1.75</v>
       </c>
-      <c r="I206" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J206" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B207" s="4">
         <v>0.25</v>
@@ -9709,22 +10647,25 @@
         <v>9</v>
       </c>
       <c r="E207" t="s">
+        <v>364</v>
+      </c>
+      <c r="F207" t="s">
         <v>365</v>
       </c>
-      <c r="F207" t="s">
-        <v>366</v>
-      </c>
-      <c r="G207" s="1">
+      <c r="G207" t="s">
+        <v>979</v>
+      </c>
+      <c r="H207" s="1">
         <v>13</v>
       </c>
-      <c r="H207" s="1">
+      <c r="I207" s="1">
         <v>60</v>
       </c>
-      <c r="I207" s="2" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J207" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>20</v>
       </c>
@@ -9743,19 +10684,22 @@
       <c r="F208" t="s">
         <v>22</v>
       </c>
-      <c r="G208" s="1">
+      <c r="G208" t="s">
+        <v>980</v>
+      </c>
+      <c r="H208" s="1">
         <v>0</v>
       </c>
-      <c r="H208" s="1">
+      <c r="I208" s="1">
         <v>7.6</v>
       </c>
-      <c r="I208" s="2" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J208" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B209" s="4">
         <v>0.11</v>
@@ -9767,24 +10711,27 @@
         <v>9</v>
       </c>
       <c r="E209" t="s">
+        <v>505</v>
+      </c>
+      <c r="F209" t="s">
+        <v>504</v>
+      </c>
+      <c r="G209" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H209" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="I209" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="J209" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A210" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="F209" t="s">
-        <v>505</v>
-      </c>
-      <c r="G209" s="1">
-        <v>0.27</v>
-      </c>
-      <c r="H209" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="I209" s="2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A210" s="3" t="s">
-        <v>507</v>
       </c>
       <c r="B210" s="4">
         <v>0.3</v>
@@ -9796,27 +10743,27 @@
         <v>15</v>
       </c>
       <c r="E210" t="s">
+        <v>507</v>
+      </c>
+      <c r="F210" t="s">
+        <v>858</v>
+      </c>
+      <c r="H210" s="1">
+        <v>0</v>
+      </c>
+      <c r="I210" s="1">
+        <v>6.99</v>
+      </c>
+      <c r="J210" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K210" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A211" s="3" t="s">
         <v>508</v>
-      </c>
-      <c r="F210" t="s">
-        <v>860</v>
-      </c>
-      <c r="G210" s="1">
-        <v>0</v>
-      </c>
-      <c r="H210" s="1">
-        <v>6.99</v>
-      </c>
-      <c r="I210" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J210" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A211" s="3" t="s">
-        <v>509</v>
       </c>
       <c r="B211" s="4">
         <v>0.3</v>
@@ -9828,25 +10775,25 @@
         <v>15</v>
       </c>
       <c r="E211" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F211" t="s">
-        <v>861</v>
-      </c>
-      <c r="G211" s="1">
+        <v>859</v>
+      </c>
+      <c r="H211" s="1">
         <v>0</v>
       </c>
-      <c r="H211" s="1">
+      <c r="I211" s="1">
         <v>6.99</v>
       </c>
-      <c r="I211" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="J211" s="6" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J211" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K211" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>47</v>
       </c>
@@ -9865,19 +10812,22 @@
       <c r="F212" t="s">
         <v>49</v>
       </c>
-      <c r="G212" s="1">
+      <c r="G212" t="s">
+        <v>49</v>
+      </c>
+      <c r="H212" s="1">
         <v>20</v>
       </c>
-      <c r="H212" s="1">
+      <c r="I212" s="1">
         <v>200</v>
       </c>
-      <c r="I212" s="2" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J212" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B213" s="4">
         <v>0.221</v>
@@ -9889,24 +10839,27 @@
         <v>6</v>
       </c>
       <c r="E213" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F213" t="s">
-        <v>728</v>
-      </c>
-      <c r="G213" s="1">
+        <v>726</v>
+      </c>
+      <c r="G213" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H213" s="1">
         <v>12</v>
       </c>
-      <c r="H213" s="1">
+      <c r="I213" s="1">
         <v>20</v>
       </c>
-      <c r="I213" s="2" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J213" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B214" s="4">
         <v>0.3</v>
@@ -9918,24 +10871,27 @@
         <v>9</v>
       </c>
       <c r="E214" t="s">
+        <v>513</v>
+      </c>
+      <c r="F214" t="s">
         <v>514</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H214" s="1">
+        <v>0</v>
+      </c>
+      <c r="I214" s="1">
+        <v>150</v>
+      </c>
+      <c r="J214" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A215" s="3" t="s">
         <v>515</v>
-      </c>
-      <c r="G214" s="1">
-        <v>0</v>
-      </c>
-      <c r="H214" s="1">
-        <v>150</v>
-      </c>
-      <c r="I214" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A215" s="3" t="s">
-        <v>516</v>
       </c>
       <c r="B215" s="4">
         <v>0.3</v>
@@ -9947,27 +10903,30 @@
         <v>9</v>
       </c>
       <c r="E215" t="s">
+        <v>516</v>
+      </c>
+      <c r="F215" t="s">
         <v>517</v>
       </c>
-      <c r="F215" t="s">
+      <c r="G215" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H215" s="1">
+        <v>0</v>
+      </c>
+      <c r="I215" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="J215" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="K215" s="5" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A216" s="3" t="s">
         <v>518</v>
-      </c>
-      <c r="G215" s="1">
-        <v>0</v>
-      </c>
-      <c r="H215" s="1">
-        <v>0.89</v>
-      </c>
-      <c r="I215" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="J215" s="5" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A216" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="B216" s="4">
         <v>0.2</v>
@@ -9979,24 +10938,27 @@
         <v>11</v>
       </c>
       <c r="E216" t="s">
+        <v>519</v>
+      </c>
+      <c r="F216" t="s">
         <v>520</v>
       </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
+        <v>520</v>
+      </c>
+      <c r="H216" s="1">
+        <v>197</v>
+      </c>
+      <c r="I216" s="1">
+        <v>771</v>
+      </c>
+      <c r="J216" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A217" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="G216" s="1">
-        <v>197</v>
-      </c>
-      <c r="H216" s="1">
-        <v>771</v>
-      </c>
-      <c r="I216" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A217" s="3" t="s">
-        <v>522</v>
       </c>
       <c r="B217" s="4">
         <v>0.25</v>
@@ -10008,24 +10970,27 @@
         <v>11</v>
       </c>
       <c r="E217" t="s">
+        <v>522</v>
+      </c>
+      <c r="F217" t="s">
         <v>523</v>
       </c>
-      <c r="F217" t="s">
+      <c r="G217" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H217" s="1">
+        <v>20</v>
+      </c>
+      <c r="I217" s="1">
+        <v>100</v>
+      </c>
+      <c r="J217" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A218" s="3" t="s">
         <v>524</v>
-      </c>
-      <c r="G217" s="1">
-        <v>20</v>
-      </c>
-      <c r="H217" s="1">
-        <v>100</v>
-      </c>
-      <c r="I217" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A218" s="3" t="s">
-        <v>525</v>
       </c>
       <c r="B218" s="4">
         <v>0.3</v>
@@ -10037,22 +11002,25 @@
         <v>9</v>
       </c>
       <c r="E218" t="s">
+        <v>525</v>
+      </c>
+      <c r="F218" t="s">
         <v>526</v>
       </c>
-      <c r="F218" t="s">
-        <v>527</v>
-      </c>
-      <c r="G218" s="1">
+      <c r="G218" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H218" s="1">
         <v>19.899999999999999</v>
       </c>
-      <c r="H218" s="1">
+      <c r="I218" s="1">
         <v>79.3</v>
       </c>
-      <c r="I218" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J218" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
         <v>253</v>
       </c>
@@ -10071,19 +11039,22 @@
       <c r="F219" t="s">
         <v>255</v>
       </c>
-      <c r="G219" s="1">
+      <c r="G219" t="s">
+        <v>981</v>
+      </c>
+      <c r="H219" s="1">
         <v>205</v>
       </c>
-      <c r="H219" s="1">
+      <c r="I219" s="1">
         <v>285</v>
       </c>
-      <c r="I219" s="2" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J219" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B220" s="4">
         <v>5.5E-2</v>
@@ -10095,25 +11066,25 @@
         <v>299</v>
       </c>
       <c r="E220" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="G220" s="1">
+        <v>774</v>
+      </c>
+      <c r="H220" s="1">
         <v>4</v>
       </c>
-      <c r="H220" s="1">
+      <c r="I220" s="1">
         <v>5.5</v>
       </c>
-      <c r="I220" s="2" t="str">
-        <f>_xlfn.CONCAT(G220, " - ", H220)</f>
+      <c r="J220" s="2" t="str">
+        <f>_xlfn.CONCAT(H220, " - ", I220)</f>
         <v>4 - 5,5</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B221" s="4">
         <v>0.12</v>
@@ -10125,25 +11096,25 @@
         <v>299</v>
       </c>
       <c r="E221" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="G221" s="1">
+        <v>775</v>
+      </c>
+      <c r="H221" s="1">
         <v>4</v>
       </c>
-      <c r="H221" s="1">
+      <c r="I221" s="1">
         <v>12</v>
       </c>
-      <c r="I221" s="2" t="str">
-        <f t="shared" ref="I221:I242" si="0">_xlfn.CONCAT(G221, " - ", H221)</f>
+      <c r="J221" s="2" t="str">
+        <f t="shared" ref="J221:J242" si="0">_xlfn.CONCAT(H221, " - ", I221)</f>
         <v>4 - 12</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B222" s="4">
         <v>0.17499999999999999</v>
@@ -10155,25 +11126,25 @@
         <v>299</v>
       </c>
       <c r="E222" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="G222" s="1">
+        <v>776</v>
+      </c>
+      <c r="H222" s="1">
         <v>1.48</v>
       </c>
-      <c r="H222">
+      <c r="I222">
         <v>7.7</v>
       </c>
-      <c r="I222" s="2" t="str">
+      <c r="J222" s="2" t="str">
         <f t="shared" si="0"/>
         <v>1,48 - 7,7</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B223" s="4">
         <v>0.17599999999999999</v>
@@ -10185,25 +11156,25 @@
         <v>299</v>
       </c>
       <c r="E223" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="G223" s="1">
+        <v>777</v>
+      </c>
+      <c r="H223" s="1">
         <v>0.74</v>
       </c>
-      <c r="H223" s="1">
+      <c r="I223" s="1">
         <v>5.5</v>
       </c>
-      <c r="I223" s="2" t="str">
+      <c r="J223" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0,74 - 5,5</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B224" s="4">
         <v>0.27900000000000003</v>
@@ -10215,25 +11186,25 @@
         <v>299</v>
       </c>
       <c r="E224" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="G224" s="1">
+        <v>778</v>
+      </c>
+      <c r="H224" s="1">
         <v>0.37</v>
       </c>
-      <c r="H224" s="1">
+      <c r="I224" s="1">
         <v>1.5</v>
       </c>
-      <c r="I224" s="2" t="str">
+      <c r="J224" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0,37 - 1,5</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B225" s="4">
         <v>0.29699999999999999</v>
@@ -10245,25 +11216,25 @@
         <v>299</v>
       </c>
       <c r="E225" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="G225" s="1">
+        <v>779</v>
+      </c>
+      <c r="H225" s="1">
         <v>0</v>
       </c>
-      <c r="H225" s="1">
+      <c r="I225" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="I225" s="2" t="str">
+      <c r="J225" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0 - 0,55</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B226" s="4">
         <v>0.27300000000000002</v>
@@ -10275,25 +11246,25 @@
         <v>299</v>
       </c>
       <c r="E226" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="G226" s="1">
+        <v>780</v>
+      </c>
+      <c r="H226" s="1">
         <v>0</v>
       </c>
-      <c r="H226" s="1">
+      <c r="I226" s="1">
         <v>200</v>
       </c>
-      <c r="I226" s="2" t="str">
+      <c r="J226" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0 - 200</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B227" s="4">
         <v>0.13439999999999999</v>
@@ -10305,25 +11276,25 @@
         <v>299</v>
       </c>
       <c r="E227" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="G227" s="1">
+        <v>781</v>
+      </c>
+      <c r="H227" s="1">
         <v>130</v>
       </c>
-      <c r="H227" s="1">
+      <c r="I227" s="1">
         <v>550</v>
       </c>
-      <c r="I227" s="2" t="str">
+      <c r="J227" s="2" t="str">
         <f t="shared" si="0"/>
         <v>130 - 550</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B228" s="4">
         <v>0.14979999999999999</v>
@@ -10335,25 +11306,25 @@
         <v>299</v>
       </c>
       <c r="E228" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="G228" s="1">
+        <v>782</v>
+      </c>
+      <c r="H228" s="1">
         <v>0.9</v>
       </c>
-      <c r="H228" s="1">
+      <c r="I228" s="1">
         <v>11.2</v>
       </c>
-      <c r="I228" s="2" t="str">
+      <c r="J228" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0,9 - 11,2</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B229" s="4">
         <v>0.22800000000000001</v>
@@ -10365,25 +11336,25 @@
         <v>299</v>
       </c>
       <c r="E229" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="G229" s="1">
+        <v>783</v>
+      </c>
+      <c r="H229" s="1">
         <v>0.59</v>
       </c>
-      <c r="H229" s="1">
+      <c r="I229" s="1">
         <v>2.37</v>
       </c>
-      <c r="I229" s="2" t="str">
+      <c r="J229" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0,59 - 2,37</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B230" s="4">
         <v>0.627</v>
@@ -10395,25 +11366,25 @@
         <v>299</v>
       </c>
       <c r="E230" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="G230" s="1">
+        <v>784</v>
+      </c>
+      <c r="H230" s="1">
         <v>1.57</v>
       </c>
-      <c r="H230" s="1">
+      <c r="I230" s="1">
         <v>16.88</v>
       </c>
-      <c r="I230" s="2" t="str">
+      <c r="J230" s="2" t="str">
         <f t="shared" si="0"/>
         <v>1,57 - 16,88</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B231" s="4">
         <v>5.8000000000000003E-2</v>
@@ -10425,25 +11396,25 @@
         <v>299</v>
       </c>
       <c r="E231" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="G231" s="1">
+        <v>785</v>
+      </c>
+      <c r="H231" s="1">
         <v>13</v>
       </c>
-      <c r="H231" s="1">
+      <c r="I231" s="1">
         <v>18</v>
       </c>
-      <c r="I231" s="2" t="str">
+      <c r="J231" s="2" t="str">
         <f t="shared" si="0"/>
         <v>13 - 18</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B232" s="4">
         <v>7.5200000000000003E-2</v>
@@ -10455,25 +11426,25 @@
         <v>299</v>
       </c>
       <c r="E232" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="G232" s="1">
+        <v>786</v>
+      </c>
+      <c r="H232" s="1">
         <v>30.6</v>
       </c>
-      <c r="H232" s="1">
+      <c r="I232" s="1">
         <v>36.6</v>
       </c>
-      <c r="I232" s="2" t="str">
+      <c r="J232" s="2" t="str">
         <f t="shared" si="0"/>
         <v>30,6 - 36,6</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B233" s="4">
         <v>0.15</v>
@@ -10485,25 +11456,25 @@
         <v>299</v>
       </c>
       <c r="E233" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="G233" s="1">
+        <v>787</v>
+      </c>
+      <c r="H233" s="1">
         <v>0</v>
       </c>
-      <c r="H233" s="1">
+      <c r="I233" s="1">
         <v>3</v>
       </c>
-      <c r="I233" s="2" t="str">
+      <c r="J233" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0 - 3</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B234" s="4">
         <v>0.2979</v>
@@ -10515,17 +11486,17 @@
         <v>299</v>
       </c>
       <c r="E234" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="G234"/>
+        <v>788</v>
+      </c>
       <c r="H234"/>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I234"/>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B235" s="4">
         <v>5.8000000000000003E-2</v>
@@ -10537,25 +11508,25 @@
         <v>299</v>
       </c>
       <c r="E235" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="G235" s="1">
+        <v>789</v>
+      </c>
+      <c r="H235" s="1">
         <v>36</v>
       </c>
-      <c r="H235" s="1">
+      <c r="I235" s="1">
         <v>54</v>
       </c>
-      <c r="I235" s="2" t="str">
+      <c r="J235" s="2" t="str">
         <f t="shared" si="0"/>
         <v>36 - 54</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B236" s="4">
         <v>0.06</v>
@@ -10567,25 +11538,25 @@
         <v>299</v>
       </c>
       <c r="E236" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="G236" s="1">
+        <v>790</v>
+      </c>
+      <c r="H236" s="1">
         <v>80</v>
       </c>
-      <c r="H236" s="1">
+      <c r="I236" s="1">
         <v>98</v>
       </c>
-      <c r="I236" s="2" t="str">
+      <c r="J236" s="2" t="str">
         <f t="shared" si="0"/>
         <v>80 - 98</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B237" s="4">
         <v>5.5E-2</v>
@@ -10597,25 +11568,25 @@
         <v>299</v>
       </c>
       <c r="E237" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="G237" s="1">
+        <v>791</v>
+      </c>
+      <c r="H237" s="1">
         <v>26.8</v>
       </c>
-      <c r="H237" s="1">
+      <c r="I237" s="1">
         <v>32.9</v>
       </c>
-      <c r="I237" s="2" t="str">
+      <c r="J237" s="2" t="str">
         <f t="shared" si="0"/>
         <v>26,8 - 32,9</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B238" s="4">
         <v>7.4999999999999997E-2</v>
@@ -10627,25 +11598,25 @@
         <v>299</v>
       </c>
       <c r="E238" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="G238" s="1">
+        <v>792</v>
+      </c>
+      <c r="H238" s="1">
         <v>30</v>
       </c>
-      <c r="H238" s="1">
+      <c r="I238" s="1">
         <v>36.5</v>
       </c>
-      <c r="I238" s="2" t="str">
+      <c r="J238" s="2" t="str">
         <f t="shared" si="0"/>
         <v>30 - 36,5</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B239" s="4">
         <v>4.5600000000000002E-2</v>
@@ -10657,25 +11628,25 @@
         <v>299</v>
       </c>
       <c r="E239" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="G239" s="1">
+        <v>793</v>
+      </c>
+      <c r="H239" s="1">
         <v>11</v>
       </c>
-      <c r="H239" s="1">
+      <c r="I239" s="1">
         <v>16</v>
       </c>
-      <c r="I239" s="2" t="str">
+      <c r="J239" s="2" t="str">
         <f t="shared" si="0"/>
         <v>11 - 16</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B240" s="4">
         <v>0.16</v>
@@ -10687,25 +11658,25 @@
         <v>299</v>
       </c>
       <c r="E240" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="G240" s="1">
+        <v>795</v>
+      </c>
+      <c r="H240" s="1">
         <v>130</v>
       </c>
-      <c r="H240" s="1">
+      <c r="I240" s="1">
         <v>550</v>
       </c>
-      <c r="I240" s="2" t="str">
+      <c r="J240" s="2" t="str">
         <f t="shared" si="0"/>
         <v>130 - 550</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B241" s="4">
         <v>8.7999999999999995E-2</v>
@@ -10717,25 +11688,25 @@
         <v>299</v>
       </c>
       <c r="E241" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="G241" s="1">
+        <v>794</v>
+      </c>
+      <c r="H241" s="1">
         <v>6.8</v>
       </c>
-      <c r="H241" s="1">
+      <c r="I241" s="1">
         <v>12.6</v>
       </c>
-      <c r="I241" s="2" t="str">
+      <c r="J241" s="2" t="str">
         <f t="shared" si="0"/>
         <v>6,8 - 12,6</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>290</v>
+        <v>1064</v>
       </c>
       <c r="B242" s="4">
         <v>0.05</v>
@@ -10747,28 +11718,31 @@
         <v>299</v>
       </c>
       <c r="E242" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="G242" s="1">
+      <c r="G242" t="s">
+        <v>290</v>
+      </c>
+      <c r="H242" s="1">
         <v>0</v>
       </c>
-      <c r="H242" s="1">
+      <c r="I242" s="1">
         <v>5.69</v>
       </c>
-      <c r="I242" s="2" t="str">
+      <c r="J242" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0 - 5,69</v>
       </c>
-      <c r="J242" s="5" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K242" s="5" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B243" s="8">
         <v>0.15</v>
@@ -10779,13 +11753,16 @@
       <c r="D243" t="s">
         <v>15</v>
       </c>
-      <c r="G243"/>
+      <c r="G243" t="s">
+        <v>540</v>
+      </c>
       <c r="H243"/>
       <c r="I243"/>
-    </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J243"/>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B244" s="8">
         <v>5.3999999999999999E-2</v>
@@ -10796,13 +11773,16 @@
       <c r="D244" t="s">
         <v>15</v>
       </c>
-      <c r="G244"/>
+      <c r="G244" t="s">
+        <v>540</v>
+      </c>
       <c r="H244"/>
       <c r="I244"/>
-    </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J244"/>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B245" s="8">
         <v>0.21179999999999999</v>
@@ -10811,13 +11791,16 @@
       <c r="D245" t="s">
         <v>15</v>
       </c>
-      <c r="G245"/>
+      <c r="G245" t="s">
+        <v>540</v>
+      </c>
       <c r="H245"/>
       <c r="I245"/>
-    </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J245"/>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B246" s="8">
         <v>6.4000000000000001E-2</v>
@@ -10828,13 +11811,16 @@
       <c r="D246" t="s">
         <v>15</v>
       </c>
-      <c r="G246"/>
+      <c r="G246" t="s">
+        <v>540</v>
+      </c>
       <c r="H246"/>
       <c r="I246"/>
-    </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J246"/>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B247" s="8">
         <v>0.2</v>
@@ -10845,13 +11831,16 @@
       <c r="D247" t="s">
         <v>15</v>
       </c>
-      <c r="G247"/>
+      <c r="G247" t="s">
+        <v>540</v>
+      </c>
       <c r="H247"/>
       <c r="I247"/>
-    </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J247"/>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B248" s="8">
         <v>0.16</v>
@@ -10862,13 +11851,16 @@
       <c r="D248" t="s">
         <v>15</v>
       </c>
-      <c r="G248"/>
+      <c r="G248" t="s">
+        <v>540</v>
+      </c>
       <c r="H248"/>
       <c r="I248"/>
-    </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J248"/>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B249" s="8">
         <v>0.25</v>
@@ -10879,13 +11871,16 @@
       <c r="D249" t="s">
         <v>15</v>
       </c>
-      <c r="G249"/>
+      <c r="G249" t="s">
+        <v>540</v>
+      </c>
       <c r="H249"/>
       <c r="I249"/>
-    </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J249"/>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B250" s="8">
         <v>0.13</v>
@@ -10896,13 +11891,16 @@
       <c r="D250" t="s">
         <v>15</v>
       </c>
-      <c r="G250"/>
+      <c r="G250" t="s">
+        <v>540</v>
+      </c>
       <c r="H250"/>
       <c r="I250"/>
-    </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J250"/>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B251" s="8">
         <v>0.28000000000000003</v>
@@ -10913,13 +11911,16 @@
       <c r="D251" t="s">
         <v>15</v>
       </c>
-      <c r="G251"/>
+      <c r="G251" t="s">
+        <v>540</v>
+      </c>
       <c r="H251"/>
       <c r="I251"/>
-    </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J251"/>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B252" s="8">
         <v>0.13</v>
@@ -10930,13 +11931,16 @@
       <c r="D252" t="s">
         <v>15</v>
       </c>
-      <c r="G252"/>
+      <c r="G252" t="s">
+        <v>540</v>
+      </c>
       <c r="H252"/>
       <c r="I252"/>
-    </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J252"/>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B253" s="8">
         <v>0.17</v>
@@ -10947,13 +11951,16 @@
       <c r="D253" t="s">
         <v>15</v>
       </c>
-      <c r="G253"/>
+      <c r="G253" t="s">
+        <v>540</v>
+      </c>
       <c r="H253"/>
       <c r="I253"/>
-    </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J253"/>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B254" s="8">
         <v>0.15</v>
@@ -10964,13 +11971,16 @@
       <c r="D254" t="s">
         <v>15</v>
       </c>
-      <c r="G254"/>
+      <c r="G254" t="s">
+        <v>540</v>
+      </c>
       <c r="H254"/>
       <c r="I254"/>
-    </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J254"/>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B255" s="8">
         <v>0.16800000000000001</v>
@@ -10981,13 +11991,16 @@
       <c r="D255" t="s">
         <v>15</v>
       </c>
-      <c r="G255"/>
+      <c r="G255" t="s">
+        <v>540</v>
+      </c>
       <c r="H255"/>
       <c r="I255"/>
-    </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J255"/>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B256" s="8">
         <v>0.1784</v>
@@ -10998,13 +12011,16 @@
       <c r="D256" t="s">
         <v>15</v>
       </c>
-      <c r="G256"/>
+      <c r="G256" t="s">
+        <v>540</v>
+      </c>
       <c r="H256"/>
       <c r="I256"/>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J256"/>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B257" s="8">
         <v>0.2056</v>
@@ -11015,13 +12031,16 @@
       <c r="D257" t="s">
         <v>15</v>
       </c>
-      <c r="G257"/>
+      <c r="G257" t="s">
+        <v>540</v>
+      </c>
       <c r="H257"/>
       <c r="I257"/>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J257"/>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B258" s="8">
         <v>0.24060000000000001</v>
@@ -11032,13 +12051,16 @@
       <c r="D258" t="s">
         <v>15</v>
       </c>
-      <c r="G258"/>
+      <c r="G258" t="s">
+        <v>540</v>
+      </c>
       <c r="H258"/>
       <c r="I258"/>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J258"/>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B259" s="8">
         <v>0.25</v>
@@ -11049,13 +12071,16 @@
       <c r="D259" t="s">
         <v>15</v>
       </c>
-      <c r="G259"/>
+      <c r="G259" t="s">
+        <v>540</v>
+      </c>
       <c r="H259"/>
       <c r="I259"/>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J259"/>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B260" s="8">
         <v>0.22</v>
@@ -11066,13 +12091,16 @@
       <c r="D260" t="s">
         <v>15</v>
       </c>
-      <c r="G260"/>
+      <c r="G260" t="s">
+        <v>540</v>
+      </c>
       <c r="H260"/>
       <c r="I260"/>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J260"/>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B261" s="8">
         <v>0.22</v>
@@ -11083,13 +12111,16 @@
       <c r="D261" t="s">
         <v>15</v>
       </c>
-      <c r="G261"/>
+      <c r="G261" t="s">
+        <v>540</v>
+      </c>
       <c r="H261"/>
       <c r="I261"/>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J261"/>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B262" s="8">
         <v>0.22</v>
@@ -11100,13 +12131,16 @@
       <c r="D262" t="s">
         <v>15</v>
       </c>
-      <c r="G262"/>
+      <c r="G262" t="s">
+        <v>540</v>
+      </c>
       <c r="H262"/>
       <c r="I262"/>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J262"/>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B263" s="8">
         <v>0.22</v>
@@ -11117,13 +12151,16 @@
       <c r="D263" t="s">
         <v>15</v>
       </c>
-      <c r="G263"/>
+      <c r="G263" t="s">
+        <v>540</v>
+      </c>
       <c r="H263"/>
       <c r="I263"/>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J263"/>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B264" s="8">
         <v>0.2</v>
@@ -11134,13 +12171,16 @@
       <c r="D264" t="s">
         <v>15</v>
       </c>
-      <c r="G264"/>
+      <c r="G264" t="s">
+        <v>540</v>
+      </c>
       <c r="H264"/>
       <c r="I264"/>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J264"/>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B265" s="8">
         <v>0.2</v>
@@ -11151,13 +12191,16 @@
       <c r="D265" t="s">
         <v>15</v>
       </c>
-      <c r="G265"/>
+      <c r="G265" t="s">
+        <v>540</v>
+      </c>
       <c r="H265"/>
       <c r="I265"/>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J265"/>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B266" s="8">
         <v>0.18</v>
@@ -11168,13 +12211,16 @@
       <c r="D266" t="s">
         <v>15</v>
       </c>
-      <c r="G266"/>
+      <c r="G266" t="s">
+        <v>540</v>
+      </c>
       <c r="H266"/>
       <c r="I266"/>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J266"/>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B267" s="8">
         <v>0.26</v>
@@ -11185,13 +12231,16 @@
       <c r="D267" t="s">
         <v>15</v>
       </c>
-      <c r="G267"/>
+      <c r="G267" t="s">
+        <v>540</v>
+      </c>
       <c r="H267"/>
       <c r="I267"/>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J267"/>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B268" s="8">
         <v>0.08</v>
@@ -11202,13 +12251,16 @@
       <c r="D268" t="s">
         <v>15</v>
       </c>
-      <c r="G268"/>
+      <c r="G268" t="s">
+        <v>540</v>
+      </c>
       <c r="H268"/>
       <c r="I268"/>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J268"/>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B269" s="8">
         <v>0.35</v>
@@ -11219,13 +12271,16 @@
       <c r="D269" t="s">
         <v>15</v>
       </c>
-      <c r="G269"/>
+      <c r="G269" t="s">
+        <v>540</v>
+      </c>
       <c r="H269"/>
       <c r="I269"/>
-    </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J269"/>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B270" s="8">
         <v>0.3</v>
@@ -11236,13 +12291,16 @@
       <c r="D270" t="s">
         <v>15</v>
       </c>
-      <c r="G270"/>
+      <c r="G270" t="s">
+        <v>540</v>
+      </c>
       <c r="H270"/>
       <c r="I270"/>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J270"/>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B271" s="8">
         <v>0.3</v>
@@ -11253,47 +12311,50 @@
       <c r="D271" t="s">
         <v>15</v>
       </c>
-      <c r="G271"/>
+      <c r="G271" t="s">
+        <v>540</v>
+      </c>
       <c r="H271"/>
       <c r="I271"/>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G272"/>
+      <c r="J271"/>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H272"/>
       <c r="I272"/>
-    </row>
-    <row r="273" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G273"/>
+      <c r="J272"/>
+    </row>
+    <row r="273" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H273"/>
       <c r="I273"/>
-    </row>
-    <row r="274" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G274"/>
+      <c r="J273"/>
+    </row>
+    <row r="274" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H274"/>
       <c r="I274"/>
-    </row>
-    <row r="275" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G275"/>
+      <c r="J274"/>
+    </row>
+    <row r="275" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H275"/>
       <c r="I275"/>
-    </row>
-    <row r="276" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G276"/>
+      <c r="J275"/>
+    </row>
+    <row r="276" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H276"/>
       <c r="I276"/>
-    </row>
-    <row r="277" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G277"/>
+      <c r="J276"/>
+    </row>
+    <row r="277" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H277"/>
       <c r="I277"/>
-    </row>
-    <row r="278" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G278"/>
+      <c r="J277"/>
+    </row>
+    <row r="278" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H278"/>
       <c r="I278"/>
+      <c r="J278"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I219" xr:uid="{F9E839D1-D9BB-491F-96EB-30E6182BBB70}"/>
+  <autoFilter ref="A1:J278" xr:uid="{F9E839D1-D9BB-491F-96EB-30E6182BBB70}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -11308,27 +12369,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -11338,322 +12399,322 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
@@ -11668,37 +12729,37 @@
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
@@ -11713,47 +12774,47 @@
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
   </sheetData>

--- a/Base de Dados.xlsx
+++ b/Base de Dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcello.coutinho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6511D44D-3039-4DA1-8FA1-FF3723B63099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F67F410-B814-4180-9D6E-C9ED47500288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{052EBD17-0308-4E6D-95A6-CA02714B48B2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{052EBD17-0308-4E6D-95A6-CA02714B48B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Base de Dados" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base de Dados'!$A$1:$K$271</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Equipamentos!$A$5:$A$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Equipamentos!$A$5:$A$87</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="1082">
   <si>
     <t>Bias MÃ¡ximo</t>
   </si>
@@ -3266,6 +3266,24 @@
   </si>
   <si>
     <t>TEXTO-AT</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 5_1_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 5_1_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 5_2_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 5_2_2</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 5_3_1</t>
+  </si>
+  <si>
+    <t>Cobas IMUNO 5_3_2</t>
   </si>
 </sst>
 </file>
@@ -3827,25 +3845,7 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3869,15 +3869,11 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}" name="Equipamentos" displayName="Equipamentos" ref="A1:A90" totalsRowShown="0">
-  <autoFilter ref="A1:A90" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A90">
-    <sortCondition ref="A1:A90"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}" name="Equipamentos" displayName="Equipamentos" ref="A1:A96" totalsRowShown="0">
+  <autoFilter ref="A1:A96" xr:uid="{5D082453-A0EE-4D67-9F8E-E41BF491A8AB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A96">
+    <sortCondition ref="A1:A96"/>
   </sortState>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{1B9AEB56-1EBB-4F60-AF89-FB7F0CA8B355}" name="Equipamentos"/>
@@ -11140,7 +11136,7 @@
         <v>5.5</v>
       </c>
       <c r="J220" s="2" t="str">
-        <f>_xlfn.CONCAT(H220, " - ", I220)</f>
+        <f t="shared" ref="J220:J233" si="0">_xlfn.CONCAT(H220, " - ", I220)</f>
         <v>4 - 5,5</v>
       </c>
     </row>
@@ -11170,7 +11166,7 @@
         <v>12</v>
       </c>
       <c r="J221" s="2" t="str">
-        <f>_xlfn.CONCAT(H221, " - ", I221)</f>
+        <f t="shared" si="0"/>
         <v>4 - 12</v>
       </c>
     </row>
@@ -11200,7 +11196,7 @@
         <v>7.7</v>
       </c>
       <c r="J222" s="2" t="str">
-        <f>_xlfn.CONCAT(H222, " - ", I222)</f>
+        <f t="shared" si="0"/>
         <v>1,48 - 7,7</v>
       </c>
     </row>
@@ -11230,7 +11226,7 @@
         <v>5.5</v>
       </c>
       <c r="J223" s="2" t="str">
-        <f>_xlfn.CONCAT(H223, " - ", I223)</f>
+        <f t="shared" si="0"/>
         <v>0,74 - 5,5</v>
       </c>
     </row>
@@ -11260,7 +11256,7 @@
         <v>1.5</v>
       </c>
       <c r="J224" s="2" t="str">
-        <f>_xlfn.CONCAT(H224, " - ", I224)</f>
+        <f t="shared" si="0"/>
         <v>0,37 - 1,5</v>
       </c>
     </row>
@@ -11290,7 +11286,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="J225" s="2" t="str">
-        <f>_xlfn.CONCAT(H225, " - ", I225)</f>
+        <f t="shared" si="0"/>
         <v>0 - 0,55</v>
       </c>
     </row>
@@ -11320,7 +11316,7 @@
         <v>200</v>
       </c>
       <c r="J226" s="2" t="str">
-        <f>_xlfn.CONCAT(H226, " - ", I226)</f>
+        <f t="shared" si="0"/>
         <v>0 - 200</v>
       </c>
     </row>
@@ -11350,7 +11346,7 @@
         <v>550</v>
       </c>
       <c r="J227" s="2" t="str">
-        <f>_xlfn.CONCAT(H227, " - ", I227)</f>
+        <f t="shared" si="0"/>
         <v>130 - 550</v>
       </c>
     </row>
@@ -11380,7 +11376,7 @@
         <v>11.2</v>
       </c>
       <c r="J228" s="2" t="str">
-        <f>_xlfn.CONCAT(H228, " - ", I228)</f>
+        <f t="shared" si="0"/>
         <v>0,9 - 11,2</v>
       </c>
     </row>
@@ -11410,7 +11406,7 @@
         <v>2.37</v>
       </c>
       <c r="J229" s="2" t="str">
-        <f>_xlfn.CONCAT(H229, " - ", I229)</f>
+        <f t="shared" si="0"/>
         <v>0,59 - 2,37</v>
       </c>
     </row>
@@ -11440,7 +11436,7 @@
         <v>16.88</v>
       </c>
       <c r="J230" s="2" t="str">
-        <f>_xlfn.CONCAT(H230, " - ", I230)</f>
+        <f t="shared" si="0"/>
         <v>1,57 - 16,88</v>
       </c>
     </row>
@@ -11470,7 +11466,7 @@
         <v>18</v>
       </c>
       <c r="J231" s="2" t="str">
-        <f>_xlfn.CONCAT(H231, " - ", I231)</f>
+        <f t="shared" si="0"/>
         <v>13 - 18</v>
       </c>
     </row>
@@ -11500,7 +11496,7 @@
         <v>36.6</v>
       </c>
       <c r="J232" s="2" t="str">
-        <f>_xlfn.CONCAT(H232, " - ", I232)</f>
+        <f t="shared" si="0"/>
         <v>30,6 - 36,6</v>
       </c>
     </row>
@@ -11530,7 +11526,7 @@
         <v>3</v>
       </c>
       <c r="J233" s="2" t="str">
-        <f>_xlfn.CONCAT(H233, " - ", I233)</f>
+        <f t="shared" si="0"/>
         <v>0 - 3</v>
       </c>
     </row>
@@ -11582,7 +11578,7 @@
         <v>54</v>
       </c>
       <c r="J235" s="2" t="str">
-        <f>_xlfn.CONCAT(H235, " - ", I235)</f>
+        <f t="shared" ref="J235:J242" si="1">_xlfn.CONCAT(H235, " - ", I235)</f>
         <v>36 - 54</v>
       </c>
     </row>
@@ -11612,7 +11608,7 @@
         <v>98</v>
       </c>
       <c r="J236" s="2" t="str">
-        <f>_xlfn.CONCAT(H236, " - ", I236)</f>
+        <f t="shared" si="1"/>
         <v>80 - 98</v>
       </c>
     </row>
@@ -11642,7 +11638,7 @@
         <v>32.9</v>
       </c>
       <c r="J237" s="2" t="str">
-        <f>_xlfn.CONCAT(H237, " - ", I237)</f>
+        <f t="shared" si="1"/>
         <v>26,8 - 32,9</v>
       </c>
     </row>
@@ -11672,7 +11668,7 @@
         <v>36.5</v>
       </c>
       <c r="J238" s="2" t="str">
-        <f>_xlfn.CONCAT(H238, " - ", I238)</f>
+        <f t="shared" si="1"/>
         <v>30 - 36,5</v>
       </c>
     </row>
@@ -11702,7 +11698,7 @@
         <v>16</v>
       </c>
       <c r="J239" s="2" t="str">
-        <f>_xlfn.CONCAT(H239, " - ", I239)</f>
+        <f t="shared" si="1"/>
         <v>11 - 16</v>
       </c>
     </row>
@@ -11732,7 +11728,7 @@
         <v>550</v>
       </c>
       <c r="J240" s="2" t="str">
-        <f>_xlfn.CONCAT(H240, " - ", I240)</f>
+        <f t="shared" si="1"/>
         <v>130 - 550</v>
       </c>
     </row>
@@ -11762,7 +11758,7 @@
         <v>12.6</v>
       </c>
       <c r="J241" s="2" t="str">
-        <f>_xlfn.CONCAT(H241, " - ", I241)</f>
+        <f t="shared" si="1"/>
         <v>6,8 - 12,6</v>
       </c>
     </row>
@@ -11795,7 +11791,7 @@
         <v>5.69</v>
       </c>
       <c r="J242" s="2" t="str">
-        <f>_xlfn.CONCAT(H242, " - ", I242)</f>
+        <f t="shared" si="1"/>
         <v>0 - 5,69</v>
       </c>
       <c r="K242" s="5" t="s">
@@ -12417,13 +12413,16 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K271" xr:uid="{F9E839D1-D9BB-491F-96EB-30E6182BBB70}"/>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4341AA7A-BE9E-402B-8B8E-1C6E7BF75419}">
-  <dimension ref="A1:A90"/>
+  <dimension ref="A1:A96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -12751,131 +12750,161 @@
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>893</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>894</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>895</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>896</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>897</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>898</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>279</v>
+        <v>893</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>146</v>
+        <v>894</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>757</v>
+        <v>895</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>758</v>
+        <v>896</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>749</v>
+        <v>897</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>751</v>
+        <v>898</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>750</v>
+        <v>279</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>752</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>50</v>
+        <v>758</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>749</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>754</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
         <v>772</v>
       </c>
     </row>
